--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD4D2A1-218C-4982-BCEA-37AB0A8980C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391265F8-4D4C-4529-8EB0-F7C737A9E767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
     <sheet name="Transcripts" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="152">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7094,6 +7094,12 @@
 Darius: You know, I the Weaponizing the power of male *****. Right. You know, I, it's like I've seen men willing to walk across hot coals barefoot to get, you know, to *** ****. It's so, and so that, and you know, they're pretty women, so they're harmless. And then the cops, how long did the cops hang up on people calling to try to report them? Right. it's just the entire premise of this was them believing that no one would take male victims seriously. Yeah. Yes.
 Jordan: Do you? Okay, so it might be for actor. I don't know. So there's a portion of interview where she, you can almost hear Constance Wu's character like bargaining almost like an addict where she's like, no, you have to understand like, We didn't think we were doing anything wrong. We're like, you have to understand these were guys who, would have, co</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VzrFB2-GMt0&amp;t=2s</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pVgVo-IvEVQ&amp;t=963s</t>
+  </si>
 </sst>
 </file>
 
@@ -7166,7 +7172,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7191,6 +7197,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7207,10 +7214,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7658,7 +7661,7 @@
         <v>115</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -7772,8 +7775,8 @@
       <c r="E12" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F12" t="s">
-        <v>40</v>
+      <c r="F12" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="391.5" x14ac:dyDescent="0.25">
@@ -8289,7 +8292,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F38" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{8E5B87CC-F717-4172-93E2-C446A611ADD5}"/>
   </hyperlinks>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391265F8-4D4C-4529-8EB0-F7C737A9E767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D54EE90-1627-4543-962C-53513D15E940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="155">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7100,6 +7100,326 @@
   <si>
     <t>https://www.youtube.com/watch?v=pVgVo-IvEVQ&amp;t=963s</t>
   </si>
+  <si>
+    <t>Knives Out</t>
+  </si>
+  <si>
+    <t>Transcript
+00:00:00 Jordan
+Welcome back to Out the Trunk with Jordan and Darius, the podcast where two friends went in the bar, started talking and never stopped. This is our movie review segment. My name is Jordan. That's Jordan to be riding on all socials.
+00:00:10 Darius
+And I'm Darius. That's Steve's all up in the area on all socials.
+00:00:13 Jordan
+And today we're gonna be reviewing Knives Out. So I'm gonna toss it to you for Act 1.
+00:00:17 Darius
+Act 1 we got. as I lose my notes. Act one, the family gathering. Following the patriarch's suspicious death, family members assemble for police questioning. An eccentric Southern detective quietly observes their conflicting stories, quickly realizing everyone has a hidden motive. Nothing unravels a family like a good old estate fight. I think, you know, Chadwick's estate just got settled. I think he passed six years ago. Take off success. The state is at war right now.
+00:00:51 Jordan
+Oh, damn, I didn't know that.
+00:00:53 Darius
+You know, write your wills, people. You never know when your time is up. And if you're going to be with that woman and she got your kids, marry her and write a will. So people ain't fighting over your stuff when you're gone.
+00:01:08 Jordan
+And so your kids get your stuff.
+00:01:10 Darius
+Yeah, just, you know, if you care about what goes where, the only way to ensure that goes where is if you write it down. Because if you don't write it down, the government decides what happens with it. And it's a long, protracted fight. So nothing unravels a family like a good old estate fight. So what you got back on, man?
+00:01:32 Jordan
+I thought it was crazy how they, everybody had their own little like lie to tell Marta where like, because she was obviously very close with the old guy. I can't remember his first name. I'm blanking. And they all were like, I wanted you to be at the funeral. You had my vote. And it's like the fact that they even voted on whether or not the person who cared for him till the very end, whether or not they could attend the funeral was crazy, but a great testament to the elitism that, you know, is themed throughout the movie. I thought that was a great way of showing their character and also showing without telling.
+00:02:05 Darius
+That's also just like they were their aloofness. Like you could tell they really weren't like involved with their elderly father's care. Correct. if they just thought, they probably thought she was just like, his housekeeper, Right?
+00:02:21 Jordan
+Because there's that one scene where the one son, he's like, is talking and he just hands her a plate to like, to go wash the dishes as if she's a maid.
+00:02:31 Darius
+Yeah. And you know, she turned out being the closest person to him, as we will find out later. So what happens is she believe she's accidentally overdosed him because she grabbed the wrong what's his face with morphine instead of his other thing. And he cares for her so much that he's accepted his fate and decides to plan a way for her to get away from it and it looked like a suicide. He actually commits suicide believing that he was going to die anyway. I set all that up so this makes sense. During the course of her alibi, she has to climb up a Building like to the third floor of a building with just her hands. No, that is a freaky feat of athleticism. Yeah, I just want people to know that is very, very, very difficult. Yes. And so she we are dealing with an Olympian and so good for her.
+00:03:24 Jordan
+Yeah, that's why. Because that's equivalent to like 30 pull ups.
+00:03:28 Darius
+Wait, I mean, under high stress with no workout gear in the middle of the night.
+00:03:34 Jordan
+It's cold as hell. You're in Massachusetts.
+00:03:37 Darius
+And it's probably wet. Yeah. And so first question, is this supposed to be a new spin on the Clue?
+00:03:48 Jordan
+Yeah, so it's basically a modern version of Clue in the old Agatha Christie murder novels with, they've remade a lot of those too, actually. I can't remember the name of the detective I'm blanking right now, but he was a French detective as well. He was a French detective, very eccentric. It's pretty similar to that. So yeah, it's supposed to be basically a modern take on that.
+00:04:10 Darius
+Okay. Is Daniel Craig supposed to be British in this movie or they just say don't worry about it?
+00:04:17 Jordan
+Yeah, they just said don't worry about it. He's supposed to be like a southern dude.
+00:04:21 Darius
+You know, I wish more people would do that because no accent is bad than like, I would rather you not try a bad accent and just be yourself. I will suspend belief, but don't do a bad accent. People, it can work and sometimes they're important, but actually it can be distracting if the accent's bad. So I would rather suspend belief on an accident and let you just focus on the acting than to have a bad accent. So I applaud them for doing that because he was British as hell in this movie. He was more British in this than Bond.
+00:04:54 Jordan
+Oh no, he's Southern in this movie. He's doing like the, almost like I call it like the Golden Girl, Southern Draw. Well, he did a good job of it.
+00:05:03 Darius
+Because he sounds like he's, eating beans and toast for breakfast.
+00:05:09 Jordan
+But they're very similar. So I'm not mad at it.
+00:05:12 Darius
+What you got for act one? What else you got?
+00:05:14 Jordan
+So one of my favorite scenes is the cutaway scenes where he's interviewing the family members. I think he's pretty much just interviewing the kids, the older guys' kids and their spouses. And she's like, he's like, you know, you all have done really well for yourself. You're self-made. He's talking to Jamie Lee Curtis and then she's like, even your brother. And she's like, well, I mean, Desi though. And she's like, I mean, my dad just kind of gives him a book twice a year and lets him publish it. Like, you know, it's not serious. And then he's like, oh, so he just, you know, whatever. And then she's like, you think you can get me, you're gonna get me to **** talk to my brother to police? I would never do that. I'm not an idiot. And then they cut to her husband being like, he don't run ****.
+00:05:55 Darius
+Any sort of like wealthy patriarch, if they got, how many kids you have 4.
+00:06:00 Jordan
+Three.
+00:06:01 Darius
+Yeah.
+00:06:01 Jordan
+I think, three. Yeah. 41 died and then he had the wife.
+00:06:05 Darius
+At least one of them is going to be a Hunter Biden, a fail son. And so like you just, at least one of them is going to be a **** **. And so, you know, you just got to hope you keep it to like there's with second generation wealthy kids, at least one's a **** **. One's got to be the Hunter Biden. And so, it stayed true to the patterns. And so you just got to hope that if the dad owned the football team, that's like you end up with a lot of like bad sports owners because the rich guy buys a football team, but he got rich doing something else. And like the football team is the only thing you can run and not **** **. And you can **** ** on the field, but you won't lose money. And so they always give that to the fail son. And so you end up with like, it's like, run the Knicks, James Dolan. Like, the Knicks will always make, like, I'm not going to get you anywhere near where you can **** ** the money. And so, and so like, Jim Ursa, hey, take the calls. The Colts could go oh and 17 and we'll still make money. So I don't actually care.
+00:07:09 Jordan
+Rest in peace, Jim Mercy.
+00:07:11 Darius
+Yeah, RIP. But you know, so always like you have to be careful with that in sports. And so you could point out the fail son. Yeah, that's true. So what else you got for act one?
+00:07:21 Jordan
+That's true. What did I have here?
+00:07:26 Darius
+Oh, yeah.
+00:07:26 Jordan
+So the widower, the blonde with the long hair and the daughter, that is some crazy ****. Just like just Stealing half $1,000,000 from your father-in-law over the span of four years is crazy. I don't know how she thought she would get away with it for that long.
+00:07:46 Darius
+And you would not.
+00:07:46 Jordan
+I mean, you're just asking for it at that point.
+00:07:48 Darius
+You would not believe how many people take advantage of their elderly family members trust. It's like financially. It's sad, but like, you know, just it. I can only say but so much, but it happens A lot.
+00:08:09 Jordan
+Got you.
+00:08:10 Darius
+So not that was also very realistic. And a lot of times they don't even think what they're doing is wrong. they just think that, that's felt out. So this is my payment, my back pain, whatever. And it's just like, no, that's fraud.
+00:08:29 Jordan
+Yeah, no, yeah. A big fraud too, because what are you spending $100,000 on? that's true. That's true. I will say that I kind of felt bad for her kid though. The fact that he was cutting her off because she didn't have anything to do with it as far as the story was told.
+00:08:47 Darius
+Yeah.
+00:08:48 Jordan
+So I didn't kind of feel bad for the grandkid.
+00:08:51 Darius
+Yeah, you do feel, yeah, the grandkids for sure. The adults, not really, but.
+00:08:56 Jordan
+Yeah.
+00:08:58 Darius
+That's all I have for actual woman. What you got? What else you got?
+00:09:03 Jordan
+That's all I got for. the affairs uncovered too. So I wanted to ask you, do you, because later on in the movie, Chris Evans' character talks about how his father was essentially masculinated by the mother because of the prenup and not having his own access to the bread, I guess, or whatever the case may be. Do you think that resentment caused him to cheat, or do you just think he was like an *******?
+00:09:21 Darius
+I think people cheat because they want to *** **** not really, tickets. I think people do ad hoc explanations, but cheating is often just Opportunity meets, I don't know, what's the word? Presentation. Yeah. cheating is often a crime of opportunity, if you will. So I don't think there's a way to keep someone from cheating on you. Now, obviously there are extraordinary circumstances, you know, but by and large, if someone's going to cheat on you, there's very little you can do about that to prevent it. Heading into act 2, unraveling the web. The detective enlists the writers devoted nurse to help navigate the family's deceit. Meanwhile, the reading of the will drops a massive bombshell that turns the entire household upside down. The bombshell being that he left everything for his caretaker, devoted nurse, whose name is escaping me at this point. You know, I get why. I think if you're going to do that, it's your state. You could do it.
+00:10:25 Jordan
+I get why they were ******.
+00:10:26 Darius
+I'm not going to lie. Heads up, maybe, you know, like.
+00:10:29 Jordan
+Yeah, The heads, yeah, heads up would have been.
+00:10:32 Darius
+Also, she's happy age. There's a there's a problematic that happens. That **** looks crazy. Paw Paw 70 years old, granny been gone. This young thing shows up and all of a sudden he's rewriting the will. And it's a question of like, Is he like cognitively capable of doing this? Is he, clearly, so obviously we know they weren't sleeping together or anything like that. It was one of the family members brought that up, but it's like that happens too, where it's like on his deathbed, this woman half his age shows up. Now all of a sudden the will has changed. Yeah, I have. Yeah, I'd be ****** too. I get it. More than ****** that can go to court. You know, it just depends. Again, estates get nasty. But I don't like overly transactional people and this family is full of them. None of them seem to care that the dad is dead. Yeah, you're right.
+00:11:24 Jordan
+I feel like only one person cried over his two people cried over him in the movie, Jamie Lee Curtis and Anna de Armas. I feel like those only character be actors slash characters who cried over him dying, which is kind of crazy.
+00:11:35 Darius
+Yeah, this is not, you know, I don't know how he ended up with like 4 sociopaths for children, 3 sociopaths for children, but here we are. What you got, Frank, too.
+00:11:47 Jordan
+He definitely created a lot of monsters. I will say that Chris Evans, this is the first one he took after he finished with Avengers Endgame, or finished with Marvel, basically. And he was ******* phenomenal in this movie. How he acted in that scene was so perfect because he was like, you're not supposed to like him, but you do kind of like him because he was just so, just didn't give a **** you know, which is always endearing to people. And just the fact that he let them sit there and try to, finger wag him. And the second that they found out they were getting that money, they lost their **** too. I thought that scene was brilliantly written and perfectly acted.
+00:12:24 Darius
+Well, let me ask you this. Better Marvel lead gets to have, gets to do an actual good movie, movie. We've reviewed them both now. The judge or Knives Out, the judge being Robert Downey Jr., Knives Out being Chris Evans.
+00:12:42 Jordan
+Evans. Which movie is better or which performance is better?
+00:12:45 Darius
+Yes, both.
+00:12:47 Jordan
+Okay, I think Knives Out is a better movie. I would say RDJ's performance, I'd say his performance was better just because he was in the movie more often. Like Chris Evans is only basically in the second-half of the movie. But in terms of just departures, in terms of what we know them for and what it did for showing their range, I'd say I think Chris Evans' role was more challenging.
+00:13:13 Darius
+I agree with that. I think The Judge is a better movie. I think Robert Downey Jr. is a more talented actor. But if I'm just in a silo, what Chris Evans I didn't expect this of him. I expected that around Downey Jr. So maybe this is grading on a curve, but I would agree with Chris Evans to answer that question. So that was my question, man. What questions you got for me?
+00:13:43 Jordan
+Okay. so there's a scene in this act where she's talking with Harlan and she's, I think they were outside on the deck playing go or playing a game or something like that. And they're talking about the affair or something like that. And he's like, you know, I think I do need to let Walt run his own publishing company like you suggested. And I do think I need to cut Ransom off like you suggested and all that. He kept saying that she made all these suggestions about what he should do with his heirs, basically. And I know that Marta is the protagonist in the movie and these people are awful. But I do kind of feel like on some level she was manipulative with him, like on the sneak. Because you're just like kind of suddenly planting all these spiders in his ears, so to speak, about what he should do. And you're just like eliminating family members one by one. Until it's just you.
+00:14:30 Darius
+Yeah, but so I mean, obviously that's that can be that can go left. But she could also just be the fresh set of eyes, telling him his blind spots with these people. Because I mean, if she's in the day, was she telling him anything wrong? Was any of it inaccurate?
+00:14:47 Jordan
+No, she was right. Yeah, she was right.
+00:14:48 Darius
+So, you know, like if someone else explaining your behavior, you're like truthfully explaining your behavior, is embarrassing to you. Maybe don't do the behavior. Like don't blame them for talking about it. Like maybe you could, you know, one should behave in a way that if they talked about you, it wouldn't be embarrassing. And so obviously you can't rewrite, you know, go back and pass and change it. But certainly, certainly there's an element of she's trying to isolate him. But unless she's telling something false, it's hard to get too upset with her about it, you know?
+00:15:25 Jordan
+Yeah, that's failure. That's valid. What was I going to say? Okay, so there's this movie does a great job of like showing kind of the behind the scenes of like classism and like I'd say performative progressivism, if you will, where it's kind of like the one dad, the one character, one dad character where he's like, oh, your kid's a Nazi, right? You know, and so he's taking this kind of progressive stance and then goes on to say like, I know they're in cages and it's sad, but the parents didn't put him in that position, And then he's like, he brings Marta to the room and he's like, hey, look, you're one of the good ones. You came over here the right way. And if you notice, every time they mention where she's from, it's a different country.
+00:16:14 Darius
+Yeah.
+00:16:14 Jordan
+Because none of them actually know where she's from.
+00:16:17 Darius
+Well, she's just, she's an NPC to them, right? She's not a human being. And so, Yeah, it's a lot of these family members give, what is it? I would have voted Obama a third time if I could.
+00:16:30 Jordan
+Third term. Yeah. Get out, Bob. Yeah.
+00:16:32 Darius
+Yeah. It's I have a lot to say about that, that, you know, I don't want to derail the pod, but I have a particular disdain for that sort of performative progressivism. Yeah. It's like sloganeering and silly marches, but when it's table stakes, like, it's different. Correct.
+00:16:54 Jordan
+So yeah, it's like the people you knew in 2020 who like posted like pro-Trump **** and then they posted the black little Instagram square for Black Lives Matter that one day.
+00:17:09 Darius
+Ushers has always been ushers wouldn't be gushers without the black community. Popeye's stands with the black community. It just don't even get me started. Everything about 2020 was quite silly. So what else we got cracked before we derail this whole thing?
+00:17:26 Jordan
+Right. What else is it? Oh yeah, so the diner scene is also one of my favorite scenes in the movie where he's like, Chris Evans is like playing it so perfect where he's like, man, I had this clarity and I realized like I needed to take care of myself for once and grow up. you deserve that money. **** my family. And then he gives her the beans and he's like, all right, well, now I know you can't lie. So what the **** happened?
+00:17:56 Darius
+I didn't catch that gimmick until I watched an hour of it yesterday that football came on and I watched an hour of it before we recorded. And I guess the break got me fresh eyes and I was like, oh, every time she lies, she vomits. Yeah. So I integrated the first the bean scene was later. That is diabolical feeding someone. Yeah, bro. And then making them to make them throw up. You know, beans are tough. I have not yet, but. It's tough.
+00:18:29 Jordan
+That's not a pleasant thing to throw up.
+00:18:30 Darius
+No, no. And sausage. I'm into it. Listen, man, beans and sausage is legit. That's basically red beans and rice. Just, you know, Cajun. But, you know.
+00:18:42 Jordan
+Yeah, true. True.
+00:18:43 Darius
+What else you got for act two?
+00:18:49 Jordan
+I mean, that scene where Harlan, where Harlan realizes that he has to kill himself was devastating. Like, because, like, imagine, like, you just feel so stressed. Like when she When she realizes that the vials are switched, she's like, oh my God. And then when she can't find the thing, it's like, you know what, you look for something you really, really need and you know what's in there, but it's not in there. She acted that perfectly. Ann Armas is a phenomenal actress. And I feel like because she's so beautiful, you kind of don't realize it all the time. And she acted her *** off in this movie.
+00:19:19 Darius
+Is that real though? It can't be that easy to administer a deadly dose of morphine. There has to be more failsafes than that, right?
+00:19:26 Jordan
+I would hope so. I'm going to guess.
+00:19:28 Darius
+Can't be like grabbing the wrong pen, like, oh, *** **** I hope not. I really hope there's more like fail safes and checks and balances because people are human and it can't just be as simple as like, this one looks good.
+00:19:44 Jordan
+Yeah. Hopefully they have like different color caps or something. I don't know.
+00:19:48 Darius
+I am certain that there are more controls in place in like formal medical settings and that's a little Hollywood magic.
+00:19:54 Jordan
+Yeah, I would hope so. I feel like a lot more people would die from that.
+00:19:58 Darius
+Yeah. Like, again, I don't know this, but it just has to be. Like, the way, if you've had a job before, you know that there's more barriers to prevent human error than this. Right, Yeah.
+00:20:12 Jordan
+Because even like.
+00:20:13 Darius
+With way lower stakes, you know, like.
+00:20:15 Jordan
+Correct. Like, I do currently slash almost formerly, I do like referral processing and you can't even submit a referral if certain information is like not on the form. You know what I mean? Correct.
+00:20:27 Darius
+So the idea that just like you could just have morphine in your left pocket and this is my right pocket and let's just hope I pulled the left.
+00:20:34 Jordan
+**** I switched the pants.
+00:20:36 Darius
+Yeah, and it was just like, now he's dead. Like that just doesn't feel accurate. But you know. No, So yeah, I'm with it. I'm with it. And it doesn't. It doesn't strange strain credulity that a very rich man would have a nurse who has less than strict access to high ed drugs. And so that's how we lost **** Prince and Mike Jack.
+00:20:59 Jordan
+We lost both of them today.
+00:21:03 Darius
+Yeah, it's you know, it's kind of obviously like the opiate crisis has been covered ad nauseam, but like it almost feels like under discussed that we lost like both Prince and Mike Jackson to drug addiction. We just kind of treat it like they accidental deaths and not the same way.
+00:21:21 Jordan
+We do treat it like, we do.
+00:21:23 Darius
+We just treat it like it's just something that happened instead of just like, man, they were junkies and they died getting high. And so, we don't treat it like overdose, like the guy from the wires, like Michael K. Williams or DMX?
+00:21:40 Jordan
+Michael K. Williams.
+00:21:41 Darius
+We treat those like overdoses in a way we don't treat Prince and Mike Jack because we want to venerate them a little differently. Right.
+00:21:48 Jordan
+Yeah, I think that's one of those things because they're just so great. No one's except the fact that, they died how they died, unfortunately. And also like, I mean, I never like most pop stars, you kind of hear about them having drug problems. We never really heard about that with them. So it was pretty shocking to find out. Yeah, well, that's how they left us, you know.
+00:22:09 Darius
+Mike, it was it was rumors because the surgeries and different things like that and the Apparently he had overdosed like the week before on a plane and got a good Narcan overdose, a good Narcan shot and got back right. But he had hip surgery because they'd been dancing on the heels on stage for 30 years and they gave him drugs to help with the pain and the pain goes away and the drugs stay.
+00:22:41 Jordan
+Yeah, that **** is highly addictive.
+00:22:44 Darius
+So you got anything else for Act 2? We're white off around a little bit.
+00:22:50 Jordan
+Yeah. I did like the fact that they, because he is the patriarch of the family, but I liked the way they showed that he at the end, he was just very much an old man filled with regret. And him cutting him out of the will was just him trying to basically, I guess, cleanse himself essentially of the disservice that he felt he'd done to his children by crippling them, so to speak. Cause I feel like only one of them was really, could really stand on her own. I mean, granted, she got a loan from her dad, but she built something on her own, which is what he wanted for his kids. Although that concept to me is always kind of a bit annoying where the whole thing is like, I get you want your kids to build their own **** but if you build a company and you build a life for yourself, you want your children to have a better one. Yeah.
+00:23:32 Darius
+Well, I mean.
+00:23:33 Jordan
+You had, so I never understood the whole get it out the mud thing.
+00:23:37 Darius
+Get it out the mud, no. But a man should stand on his own too. And, you know, if you like, if you run an empire, you know, like, you just can't be on my payroll doing nothing. Like, like, just say, like, you have to, okay, well, what part of the company do you like? Okay, well, we'll get you an internship there. And obviously we gonna make sure you write, you know, but you just can't be, you know, 40 years old with an allowance from your dad. You have to have some sort of self. You have to be able to sustain yourself in some way. I'm not going to make you start from scratch like me. And if you want to join the family business, of course, we're going to nepotism this thing. But what part, okay, I own a real estate portfolio. Do you like to handle the repairs? Do you like to do this? Do you want to deal with the banks? What do you like? We'll get you in that area and we'll get you right. But I understand not wanting, you know, grown adult children on an allowance. And so I There's a way to do it. It's definitely difficult. Like, the, like I said, the NFL owners like give your kid the football team. That's something they can do. You know, it's just like it's a task and right?
+00:24:52 Jordan
+You can't **** that up.
+00:24:53 Darius
+You can **** it up on the field, but you know. I see both sides of it. I do. Act 3, the donut hole. As the killer frantically scrambles to cover their tracks, the detective pieces together the final clues. A clever trap brings the truth to light, restoring order to the estate. I would hereby like to establish a movie board that has to review and approve all applications for movies that want to be longer than 2 hours. I will be on that board and I would you it would make Harvard jealous how low my acceptance rate would be. It starts to drag. I was like, man, there's no reason for this to be longer than 2 hours. Movie directors, if you're listening, you're not. But one day you will be. Please. under two hours, unless you have a really, really good reason. And the reason you're thinking probably isn't good enough. Like, it's just, movies should not be longer than two hours unless they have like some, this is a standard murder mystery. Hour 45, we good. We don't really like the characters are fine. It's a good movie.
+00:26:08 Jordan
+But it's a fun movie.
+00:26:09 Darius
+It's a good fun regular movie. And those should not be as long as it's as long as Goodfellas. Like why isn't this long?
+00:26:19 Jordan
+Yeah. Okay. So do you think, okay, so you think that the first act was too long or the third act was too long?
+00:26:24 Darius
+The third act was too long. By then it's so obvious Chris Evans is the actual killer. Because at a certain point, like the way he comes in late, the way his star is so much bigger than the rest of them, like the twist is from a mile away. And you know she's not the killer. And it's just like, All right, let's just, okay, land the plane. We like, we know what's going on here. And they just keep adding scenes and adding scenes. And I just, this did not need to be longer than two hours. It was a good movie though.
+00:26:52 Jordan
+I enjoyed it. Yeah, it is. I really like this movie. That's true that the twitch you do kind of see coming. I like, I think. What I love about this movie is figuring out how he just how he did it. Because I really watch it. I was like, how the **** did he do this? Like, I couldn't figure it out, you know, because he's hardly ever in the movie. You hardly see him, you know, yes, he has a motive, but everybody has a motive, pretty much aside from like the niece, the grandkids, basically. And because he did such a good, Chris Evans did such a good job of seeing as though he's turning over a new leaf, you do want to believe that he did, you know. But yeah, I thought I like that. I like the reveal scene though, because it's a tough scene to pull off because it's like a 10 minute scene with no shots. It's just straight dialogue. I was there. And Daniel Craig just ripped that ****. Like it's like 10 pages of dialogue, you know, to memorize, you know?
+00:27:48 Darius
+It was good. It just, you know, just.
+00:27:51 Jordan
+They did circle the block a little bit. Yeah.
+00:27:53 Darius
+It's hard to spin his wheels a little bit. I enjoyed it though. It's I wish more movies were made like this. Hollywood doesn't really do whodunits anymore. Yeah. And sometimes I just want to watch 2 detectives solve a mystery. Like we reviewed 7th and like, you know, just like let's solve a mystery. And you don't really get that anymore. You get, we're getting back into like, you know, low stakes drama movies, but I've been, you could just, you know, get two good actors, they're cops and they have to solve a murder. And it's weird.
+00:28:25 Jordan
+Yeah, me too.
+00:28:26 Darius
+It used to be good.
+00:28:27 Jordan
+Yeah, I don't know what happened. It feels like, I don't know if it's because people, it feels like murder mystery books are not as popular as it used to be maybe. I don't know. I mean, if audience, if you want to suggest some, like feel free. We'd love to hear, you know, get some recommendations. But like, I mean, for me growing up, like I love like Nancy Drew and the Hardy Boys and all that, well, Wishbone and all that kind of, all those book series and stuff. So like growing up, you watched a lot of whodunits and you know, the classics of course, Clue and all that. And it feels like one day they just went away. I don't know. I don't know what happened.
+00:28:55 Darius
+Just like, you know. Whodunits, buddy cop movies. Like you said, this movie's fun. It's good.
+00:29:02 Jordan
+Yeah.
+00:29:03 Darius
+And we need more of that. But like, I just, I can't even remember the last one. **** Knives Out 2. What was the last of?
+00:29:13 Jordan
+Knives Out 3.
+00:29:14 Darius
+There's a third? There's a third.
+00:29:19 Jordan
+Yeah, it's the third one. It's really good.
+00:29:21 Darius
+It's the first time I've seen any of them.
+00:29:23 Jordan
+It's got like a really dark tone. Okay, the third one is on it's on Netflix. The second and third one are both on Netflix.
+00:29:30 Darius
+All right, check them out, man. What else you got, Factory?
+00:29:37 Jordan
+Oh yeah, so I want to ask you, do you believe there is such a thing as a perfect crime? This one comes pretty close. So I want to see what you thought about that. If there's if there's ever.
+00:29:47 Darius
+We still ain't figured out who killed Biggie. True.
+00:29:53 Jordan
+We think we know who he is.
+00:29:55 Darius
+Yeah. I mean, what is it? Something like 40% of murders go unsolved.
+00:30:02 Jordan
+Yeah.
+00:30:02 Darius
+You know, so to answer your it's hard to say. It's like perfect because, you know, right. More people get away with it than you'd like to believe, even because like, yeah, even if the cops know who did it, they have to prove who did it. And like, it's right, you know, if it's not, you know, a domestic issue where it's obvious the husband did it or, you know, you know, that's why serial killers used to be so prevalent. It's because it's actually hard to solve a crime when someone just randomly kills somebody. Right. And, you know, for DNA and things like that. It's like, well, what do you go with? They're not there unless you catch them in the act. You know, they left. Right. You know, we didn't you know, we can't. If they're not a criminal already, their DNA isn't even in the database. So if they leave some DNA, it's just true. It's just a profile until they get a reference to something else. And it's like, you know, if you don't have it on camera or you didn't catch them in the act, it's actually, it's a tough puzzle to solve. But yeah, I mean, he damn near did it. He damn near got away with the perfect crime. And he ended it by trying to stab her with a plastic knife. Talk about a bad luck.
+00:31:20 Jordan
+No, seriously.
+00:31:22 Darius
+Really? I grabbed a plastic knife. I can't even go out with a bang.
+00:31:25 Jordan
+No, I can't even go out and kill the person who was taking my inheritance.
+00:31:28 Darius
+Yeah, all of it. Like 50 M's, wasn't it?
+00:31:31 Jordan
+Like, yeah, 60, I think. And that's not even including like the house and **** I don't think. Yeah, man. Do you think any of the relatives deserved their inheritance or an inheritance?
+00:31:48 Darius
+Wow, that's tough to answer. I don't like deserve is, they're his children, there's progeny. Only one, like most of them could stand on their own 2 feet. Does anyone deserve an inheritance? Like it's not really a deserved thing. You know, like you get it because that's your, that's your parents and they have money left over and what else are you going to do with the money? It should go to their children. But.
+00:32:09 Jordan
+Yeah.
+00:32:09 Darius
+No one. I mean, how does one</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: The Reading of the Will | Act 2: The Family Fractures | Act 3: The Donut Hole Mystery&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius break down Knives Out, examining the Thrombey family&amp;#39;s inheritance battle, Marta&amp;#39;s role in the household, Benoit Blanc&amp;#39;s investigation, and the class commentary hidden beneath the murder mystery.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 covers the opening mystery, family entitlement, writing a will, and how inheritance fights reveal character. Act 2 explores Chris Evans&amp;#39; performance, transactional family relationships, performative politics, and Marta&amp;#39;s influence on Harlan. Act 3 examines the final reveal, the &amp;quot;donut hole&amp;quot; explanation, perfect crimes, whether the family deserved the inheritance, and the movie&amp;#39;s overall rating.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Do the Thrombey relatives deserve an inheritance simply because they are Harlan&amp;#39;s children?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The family&amp;#39;s treatment of Marta reveals that they never truly saw her as a person. They saw her as useful until their money was threatened.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; If someone truthfully describing your behavior embarrasses you, the problem isn&amp;#39;t the description. The problem is the behavior.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Should wealthy parents leave inheritances to their children, or should every generation be expected to build its own success?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Inheritance&lt;/li&gt;
+      &lt;li&gt;family entitlement&lt;/li&gt;
+      &lt;li&gt;class dynamics&lt;/li&gt;
+      &lt;li&gt;performative progressivism&lt;/li&gt;
+      &lt;li&gt;truth and deception&lt;/li&gt;
+      &lt;li&gt;self-reliance&lt;/li&gt;
+      &lt;li&gt;loyalty&lt;/li&gt;
+      &lt;li&gt;moral accountability&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
 </sst>
 </file>
 
@@ -7172,7 +7492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7197,7 +7517,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7214,6 +7533,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7533,7 +7856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -7775,7 +8098,7 @@
       <c r="E12" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" t="s">
         <v>151</v>
       </c>
     </row>
@@ -8289,6 +8612,23 @@
       </c>
       <c r="E38" s="9" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="4">
+        <v>2019</v>
+      </c>
+      <c r="C39" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="D39" s="8">
+        <v>3</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -8303,7 +8643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -8611,6 +8951,14 @@
         <v>149</v>
       </c>
     </row>
+    <row r="39" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D54EE90-1627-4543-962C-53513D15E940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3255083-B0DE-4C06-95AC-BEB1FE66C88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
     <sheet name="Transcripts" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$F$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$F$39</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="155">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=5fwB5UbSvsQ</t>
-  </si>
-  <si>
-    <t>Coming Soon!</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=mpGwWlpbttw</t>
@@ -7420,6 +7417,9 @@
   &lt;/div&gt;
 &lt;/section&gt;</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=c-h3YS2Mp10&amp;t=19s</t>
+  </si>
 </sst>
 </file>
 
@@ -7492,7 +7492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7517,6 +7517,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7533,10 +7534,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7869,22 +7866,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -7901,7 +7898,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>1</v>
@@ -7921,7 +7918,7 @@
         <v>2.5</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
         <v>37</v>
@@ -7941,7 +7938,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F4" t="s">
         <v>38</v>
@@ -7961,7 +7958,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
@@ -7981,10 +7978,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -7996,10 +7993,10 @@
       </c>
       <c r="C7" s="8"/>
       <c r="E7" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8016,10 +8013,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8036,10 +8033,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8056,10 +8053,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8076,10 +8073,10 @@
         <v>3</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8096,10 +8093,10 @@
         <v>5</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="391.5" x14ac:dyDescent="0.25">
@@ -8116,10 +8113,10 @@
         <v>3.5</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="405" x14ac:dyDescent="0.25">
@@ -8136,10 +8133,10 @@
         <v>2</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8156,10 +8153,10 @@
         <v>3</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8176,10 +8173,10 @@
         <v>3</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="405" x14ac:dyDescent="0.25">
@@ -8191,10 +8188,10 @@
       </c>
       <c r="C17" s="8"/>
       <c r="E17" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8211,10 +8208,10 @@
         <v>3</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8231,10 +8228,10 @@
         <v>4</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8251,10 +8248,10 @@
         <v>5</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8271,10 +8268,10 @@
         <v>3.5</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8291,10 +8288,10 @@
         <v>4</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8311,10 +8308,10 @@
         <v>5</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8331,10 +8328,10 @@
         <v>5</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8351,10 +8348,7 @@
         <v>2.5</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8371,10 +8365,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F26" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8391,10 +8385,10 @@
         <v>2.5</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8411,10 +8405,10 @@
         <v>2.5</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8431,10 +8425,10 @@
         <v>5</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8451,10 +8445,10 @@
         <v>2</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8471,10 +8465,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8491,10 +8485,10 @@
         <v>4</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8511,10 +8505,10 @@
         <v>2.5</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="F33" t="s">
-        <v>40</v>
+        <v>141</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8531,10 +8525,10 @@
         <v>3.5</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8551,10 +8545,10 @@
         <v>3</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="405" x14ac:dyDescent="0.25">
@@ -8571,10 +8565,10 @@
         <v>4</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
@@ -8591,15 +8585,15 @@
         <v>4</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B38" s="4">
         <v>2019</v>
@@ -8611,12 +8605,12 @@
         <v>3.5</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B39" s="4">
         <v>2019</v>
@@ -8628,11 +8622,11 @@
         <v>3</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F38" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" xr:uid="{8E5B87CC-F717-4172-93E2-C446A611ADD5}"/>
   </hyperlinks>
@@ -8652,10 +8646,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8663,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8671,7 +8665,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8679,7 +8673,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8687,7 +8681,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8695,7 +8689,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8703,7 +8697,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8711,7 +8705,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8719,7 +8713,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8727,7 +8721,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8735,7 +8729,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8743,7 +8737,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8751,7 +8745,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8759,7 +8753,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8767,7 +8761,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8775,7 +8769,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -8788,7 +8782,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8796,7 +8790,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8804,7 +8798,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8812,7 +8806,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8820,7 +8814,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8828,7 +8822,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8836,7 +8830,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8844,7 +8838,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8852,7 +8846,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8860,7 +8854,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8868,7 +8862,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8876,7 +8870,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8884,7 +8878,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8892,7 +8886,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8900,7 +8894,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8908,7 +8902,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8916,7 +8910,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8924,7 +8918,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8932,7 +8926,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -8940,23 +8934,23 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3255083-B0DE-4C06-95AC-BEB1FE66C88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EDCBC4-A91B-449B-8618-89F067AAE858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="158">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7420,6 +7420,203 @@
   <si>
     <t>https://www.youtube.com/watch?v=c-h3YS2Mp10&amp;t=19s</t>
   </si>
+  <si>
+    <t>Whiplash</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: The Invitation | Act 2: The Pressure | Act 3: The Reckoning&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius break down Whiplash, examining Andrew’s obsessive pursuit of greatness, Fletcher’s brutal teaching methods, the competitive world of elite music, and the line between demanding leadership and abuse.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 introduces Andrew’s talent, Fletcher’s eye for excellence, the film’s dark humor, and the competitive hierarchy inside the conservatory. Act 2 follows practice turning into obsession as Andrew sacrifices relationships, health, and stability for the drum chair. Act 3 expands the debate beyond the movie, asking whether greatness requires discomfort, whether results can justify destructive methods, and why the final performance lands so powerfully.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Can greatness be achieved without cruelty, obsession, and extreme discomfort?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Fletcher sometimes pushes Andrew because Fletcher recognizes Andrew’s potential, but Fletcher also uses humiliation and control simply because nobody can stop Fletcher.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Andrew reaches extraordinary heights because Andrew refuses to settle for “good enough,” but the movie forces the audience to confront the trade-offs behind that excellence.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Do Fletcher’s results justify Fletcher’s methods, or does successful abuse remain abuse?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;The cost of greatness&lt;/li&gt;
+      &lt;li&gt;discipline versus abuse&lt;/li&gt;
+      &lt;li&gt;obsession&lt;/li&gt;
+      &lt;li&gt;competition&lt;/li&gt;
+      &lt;li&gt;leadership&lt;/li&gt;
+      &lt;li&gt;sacrifice&lt;/li&gt;
+      &lt;li&gt;validation&lt;/li&gt;
+      &lt;li&gt;excellence versus “good enough”&lt;/li&gt;
+      &lt;li&gt;artistic ambition&lt;/li&gt;
+      &lt;li&gt;results versus methods&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Jordan: Welcome back to Out the Trunk with Jordan and Darius. My name is Jordan. That's Jordan to be riding on all socials.
+Darius: And I'm Darius. That's these all up in the area on all socials. And.
+Jordan: Today we're going to be talking whiplash. This movie came out in 2014. Let's get into it.
+Darius: All right, I wasn't excused that being that fast. Act one, the invitation. A driven first-year drummer enters a prestigious music school and catches the attention of a demanding conductor whose approval could change everything if the opportunity is worth the cost. Just going to start off with a real quick question. Is Miles Teller still with us? Where is he at?
+Jordan: Yeah, I thought the same thing because he was so ******* good in this movie. He's a really, really good actor. And I feel like I haven't seen anything in a long, actually, he was in the Michael Jackson movie for a little bit. He played the label exec who got him free from his dad. I think he's supposed to be in something coming up soon. Let me see if I can find it. Cause yeah, he's dope as ****. He's in like, he's in a lot of movies that I love.
+Darius: My overarching point though is that he should just be there. What happened to like?
+Jordan: He really, really should be.
+Darius: He trolls in movies where he has 10 lines is not where we thought this was going 10 years ago.
+Jordan: No, for sure. I thought he was going to be like. up there with Chalamet and Austin Butler and whoever else.
+Darius: I am, Pattinson, we forget that these are people and they have personal things and, maybe you just had something happen. I don't want to speculate, but, these are not avatars that we can just move on. Like sometimes people just don't want to, things happen. My point is, everybody with superstar potential doesn't have it realized, so But he is phenomenal in this. And I was when I first saw this, I thought we'd see a lot more of them.
+Jordan: Me too. Me too. I thought because he was in the Divergent series. He was really, really good in that. Loved him in that awkward moment. I really thought he was kind of on the way out of here, you know?
+Darius: Two night stand with the. Yeah, I was. He was great in that.
+Jordan: Yeah, I think it was Anna Kendrick was in that movie.
+Darius: She. They have changed their name since then, so I don't actually know what the new name is.
+Jordan: Oh, was it the actor from The Odyssey that played?
+Darius: No, but similar situation. Okay, gotcha.
+Jordan: Okay.
+Darius: So.
+Jordan: Yeah. I love that movie too. He did The Spectacular Now with Shailene Woodley. That one was really good.
+Darius: Fantastic for I'm sure he wants to forget about.
+Jordan: Yeah, we all forgot about that movie.
+Darius: Didn't they try it again with the... Anyways, let's get back on track. What else you got back on, man?
+Jordan: I want to say that if you have a dark, exquisite sense of humor, this is the movie for you. Because this movie, I think this movie is absolutely hilarious. I don't know if it's supposed to be funny, but JK Simmons was absolutely hilarious and terrifying in this movie. Like the one liners he has, I don't know how he got through those readings. Honestly, I'd have been like cracking up.
+Darius: He won an Academy Award for this, right?
+Jordan: Yeah, he won an Oscar for this.
+Darius: Yeah, he deserved it. He was absolutely menacing, to say the least, but he definitely had some, we'll call it sophomoric homophobic humor.
+Jordan: Yeah. No, he was just.
+Darius: Using old school inappropriate insults to convey a lack of masculinity. So, The movie did the thing where they're just like, oh, we don't have any women. Let's just give him a pointless girlfriend B plot arc that like, why?
+Jordan: Yeah.
+Darius: I'm not a woman, but like, I imagine women watch that and I was like, just do nothing.
+Jordan: Right. Yeah. Because it just gets me insulting. It's like, to me, it's almost like, people say like friends was racist because there was no black people.
+Darius: Yeah.
+Jordan: I'd rather there be no black people than them be a token or the disposable love interest or the black best friend or the, you know what I mean?
+Darius: Yeah, just like, you know, just you have someone in there like making hip hop jokes. It's just like, no. Right. Especially during the 90s, we had our fill of any kind of show we wanted. That's their business over there. I wasn't watching that **** no way. So I was we had we had living single. We had Martin. We had Wayne Brothers.
+Jordan: Martin Fresh Prince.
+Darius: Fresh Prince. Yeah. Smart guy. Sister.
+Jordan: Living single.
+Darius: Whatever you wanted. There was something for you.
+Jordan: Yeah. They could have Jackson. We had everything. Yeah, literally.
+Darius: You know, so get rid of the like, don't do the pointless girlfriend B plot. She was literally just an empty plot. Yeah. There's just nothing.
+Jordan: Yeah.
+Darius: So right.
+Jordan: She's just a vehicle for his obsession. Yeah, I love the way they introduced JK Simmons' character as like a spectral figure, like where he's like behind the door listening on the first day of class and everyone's like, oh **** he's listening. And then when he walked away, they're like, oh, we suck.
+Darius: You think of his humor, man, when he walks into the, we'll call it like junior varsity, or that's a better word. I don't know what it's called. Yeah. And he, you know, totally takes over that guy's class. He's like, going to, nope, nope, to see if you're here for it because you're pretty, nope. No, you are. But he knew the dude on the drums. Miles Teller's character was him. And you could tell. Yeah, that was like immediate because he's a genius. He's a genius conductor and right. He could spot the talent from a mile away. And so I thought that was really cool how it was. There's a lot of game recognized game in that in that exchange, even though, like, he's hard. Yeah. But. He was hard on him, but the other people he was just dismissive about. Right. Because he didn't give a ****. Yeah. And we're talking about people who got into this, you know, prestigious school. So even on junior varsity, you still good. And you know, so he just he knew he was him. So what else you got?
+Jordan: Yeah, I like that. I like that, too. One of my favorites is when he sees him the night before, when he's practicing up late by himself and he's he's like, Oh, I'm sorry. He said, Why did you stop playing? Would you think I came? You're here to play music? What are you doing? And then he's like, and he started playing. He's like, did I ask you to be a monkey?
+Darius: But he was there practicing alone after everybody else went home.
+Jordan: And so after everybody else went home, yeah, he was he was he was with him shooting in the gym.
+Darius: And you notice he was the only conductor still there. And so we never like the movie never actually shows how dedicated to it JK Simmons is in like explicit terms. But there's subtle nods to it, like the fact that he's there late all the time or the fact that literally at 9am on the dot he walks in. That's the precision of someone who has mastered, you know, who knows his tempo. Routine.
+Jordan: Yes, he was not rushing nor dragging.
+Darius: He walked in when that second hit the dot. And I like that the movie didn't do a scene showing his obsession. It just was subtle about it. And so Spoiler alert, this is, I enjoyed how well crafted this was. Spoiler my rating.
+Jordan: This is literally, literally a beautiful film. The way it's shot, the cinematography, the lighting, the shading, the color grade, the storytelling, the acting, the music is great. And I'm not a big jazz person. I'm for the blues. But as a former band kid, this movie was ******* phenomenal. Luckily, I never had a professor act like a conductor act like that. Granted, we were 12, so he probably would have gotten fired pretty quick. But it is a realistic portrayal of, you know, conductors. They do do they go hard as **** you know, for their craft. One of my favorite scenes is where he says, be there at 6 a.m. first day for core practice. And first of all, he's late. He wakes up at 603. So you already ****** ** for one. And he gets there and he waits for three hours before everyone else gets there. I almost wonder if he had been on time, if the professor would have been there waiting for him.
+Darius: That's a good question that I don't have a good answer to. But I will say that I'm more sympathetic to the drive for excellence. Than multiple who watch this movie, but that's just * **** **** telling someone to show up three hours early.
+Jordan: No, **** *** bro. Yeah, for real.
+Darius: That accomplishes nothing. It's just to be a controlling ********.
+Jordan: Correct, because there is a lot of that in this movie too. There is, there is, I'm pushing you because I know you can do better, but there's also a whole lot of, I'm just doing this because I can, and you can't stop me. What I was going to say. Oh, and also even he wasted the three hours. I would have been practicing. by yourself. You might as well. You're playing with basically seniors in this upper echelon of orchestra. You kind of wasted your time too.
+Darius: I imagine he was nervous as **** because he doesn't know it. Like he gets there late. Yeah. And so he doesn't know if they left, if whatever. So he just kind of sitting there waiting on his, you know, punishment until people start filing it and he realized he was played. Let me ask you this though.
+Jordan: Yeah.
+Darius: Was it so I don't believe that he stole the, so when they go to play this event and he's an alternate and the core guy loses his sheet notes. Yeah. And I don't believe that like Miles Teller's character stole it, but I do believe, was it snake **** to admit you could play it by heart.
+Jordan: No, because you should be able to play it by heart. You're a senior doing this ****. What do you mean you don't know the ******* notes?
+Darius: I agree and that's why I love this movie because Miles Teller's character was just as competitive and just loved as much of this as everybody else.
+Jordan: And that's what I loved about it.
+Darius: Was just as cutthroat and seemingly enjoyed the aggressive instruction. He didn't, you don't see him cower too many times.
+Jordan: No, And it's just like. After that first day, no.
+Darius: He's just like, I'm going to match your psychopath.
+Jordan: Yes, they match each other's freaks.
+Darius: He is just like, no, I can play it by heart. Get this rookie up out of here. And he smokes it.
+Jordan: And first of all, yeah, first of all, you're really my op because we're in competition right now. He talked to him crazy that whole time that he was his understudy. And Why did you give me your notebook? That is, that's your responsibility. Also, why the **** don't you know that your ******* notes?
+Darius: Well, I mean, it just, it would have been very easy for them to make this. It was a realistic portrayal of this world. This world is very cutthroat.
+Jordan: Yeah.
+Darius: You know, it's a dog eat dog world. There's only one chord chair for drummer. Like you could have 4 trumpets, but there's only one drummer. Right. You know, there's only one drummer. And the drummer stands out. Generally speaking, the drummer gets famous. He's the quarterback. And so It would have been very easy for the people making this movie to make it very happy and we get it along and oh no, but it portrayed the cutthroat nature of the industry in an accurate way.
+Jordan: Correct. I also, I mean, I think we probably all agree. The professor took that notebook, right? We all think that.
+Darius: Yeah, I would. I think he wanted a pretext to fire the core and bring the ultimate.
+Jordan: Tanner, yeah.
+Darius: Eddie, you know, He's a dictator, but even dictators have to have allies. And so you need a pretext to remove a core member for a rookie that doesn't **** *** the rest of the band. And so having him admit that he doesn't know his bars, his lyrics, the rest of the band is like, okay, get him the **** ** out of here. We need professionals. So I believe he stole that for sure.
+Jordan: Yeah, it even it's like that scene where he's like, someone's out of tune here. And he tells the one kid, get out. And he's like, he should have known it was you. But he should have known. And that's just as bad.
+Darius: Yeah. He just, you know, we'll get to it in later segments. But like, you know, there is excellence has its costs, you know, and we'll get to that a little bit later. Do you have anything else for Aquan?
+Jordan: Yeah. So the first date he has with the NPC girlfriend. I did like that scene though, because it showed like the different communication styles between men and women, where he's like, she's talking about, she goes to Ford, he's like, oh, what are you studying? She's like, I'm undecided. He's like, oh, what do you want to do? She's like, I don't know. And then he's like, what do you want to do? She's like, I don't know. And he's just, she gets, you can tell she gets frustrated, because I think she, no one wants to be, wants to say they don't know what they want to do with their life, But he was genuinely interested in her life and was asking questions because he was genuinely interested in her. And it's kind of funny because there's that whole thing on the internet you see where people are like, oh, guys never ask me questions about myself. And it's like, here's a guy who's asking questions. He was kind of met with a prickly response.
+Darius: So yes, I get it. But to defend the women for a bit, When they ask, when they say guys never ask them questions about themselves, I often listen to men talk to women and yeah, they just, they did just, it's just a monologue most of the time.
+Jordan: Yeah, I believe that.
+Darius: It's like they'll ask a question and it's just like, you know, it's just, it's a valid complaint that often men are just, you know, speaking and not really conversing.
+Jordan: Yeah, that's very true. You can tell when a guy, it just has the monologue written in his head like a teleprompter and he's just waiting for you to shut up.
+Darius: Yeah, it's just like what they're saying is not input at all. It's just, you know, you have you have the script and you're just spitting it out. And she's just her words are just a speed bump to the end of your script.
+Jordan: Yeah.
+Darius: Want to get an act to? Act to the pressure. Practice becomes obsession as the drummer pushes past comfort, relationships, and confidence while trying to survive a competitive room ruled by fear, precision, and impossible expectations. And let me just say, you know, generally speaking, I've come to believe that school just should be harder. Like we've gotten a little too lax as far as like grading and passing kids and accommodations and da, da, da, da, da. This is ridiculous. Why are you throwing things?
+Jordan: No, that's because you'd had to fight me, dog. I'm sorry.
+Darius: Well, I do fight. Like you said, he matches freak because they got to fight.
+Jordan: You think you go throw a chair at me and survive?
+Darius: Just. I don't like men who cannot keep their composure. Right. And so, like. you can be angry but just losing your composure and throwing things is just you're not in control and that's not leadership you know?
+Jordan: So no not at all that's that's abuse of power and abuse of people yeah so okay so they do a good job in this movie of showing why Miles Teller his character is the way he is you know like why he delved why he just loves music so much is He didn't feel seen at home. Like when he goes back home for that weekend dinner with his family and they're just ignoring everything he says, you know, they're like, I mean, okay, your drumming is cool, but like Bobby got a touchdown and you just got a teacher of the year award and whatever. That's one of my favorite scenes in the movie, that dinner scene where he's just like **** talking to his brother. Like you're never going to the league.
+Darius: Yeah. I'll be honest. That's the scene when I went and swapped my laundry out. I was like, okay.
+Jordan: Oh, really? I love that scene.
+Darius: I thought it was just filler where they're just like, okay, like there's two characters in this movie and they're not on the scene at the same time in this one. So it was it was it definitely showed because it's funny because he's the excellent one right of the of the family. Like he's a he's a striver and the achiever. It's just not in a I was going to say not in a traditionally masculine way, but playing drums is pretty dope, it's not like he's playing a flute, and.
+Jordan: I think maybe because it was a jazz drum.
+Darius: Yeah, but I mean, I don't know. I thought it was pretty like, well, the skills translate, you know, like he can do, he can play more than one of the other music.
+Jordan: So I think it's one of those things where, because I'm guessing because his brother was a football player, that's considered very masculine, obviously. And then you're an arts kid. they probably placed a higher premium on the you know the athlete over the the musician.
+Darius: Yeah that's true that is probably true um what else you got Frank too?
+Jordan: Um let's see oh so okay so what did you think about the breakup scene?
+Darius: Uh the with the NPC I didn't think much about it at all uh what did you think about it?
+Jordan: Well, I feel like that was the one scene where he he I don't want to phrase this where he overly succumbed to the of his teacher, where he's like, I'm just going to be an ******* to you because that means that I'm great, you know, was like, you could have just said, hey, I don't think I'm going to have the time to give you what I think you want or need. We should see other people call it a day. And he kind of went on a full reign about how she would ruin his life and he's better than her. She's just normal and she doesn't get it.
+Darius: But that would betray the character though, right? Like he's an obsessive. He is a psychopath. It doesn't make sense for him to handle a breakup gently. And nor did it make sense for him to even have a girlfriend at all.
+Jordan: Well, that too.
+Darius: You know, his soulmate was damn conductor Fletcher.
+Jordan: And.
+Darius: So They were married at that point. And so I don't think I think it would have betrayed his character if he was gentle in breaking up with her.
+Jordan: That's a good point. I didn't think of that. I say. Oh, so the there's a scene where he's auditioning for the role again with the other kid from his freshman class. No, all three of them. They're auditioning against each other. And he's screaming at him and he's I think that was the scene. Was that scene through the chair? I can't remember.
+Darius: All the yelling. He threw a lot.
+Jordan: Yeah, he threw a lot of **** in this movie. Did you think he had the part the entire time and Fletcher was just testing him?
+Darius: Yes, I don't. I think Fletcher knew. It's a bit of movie magic that Fletcher wouldn't have heard him play before. But right from the moment he heard him play, he saw it. You know, I don't think I think someone someone's ear as good as Fletcher's just knew and like the so you see it in like we're jumping a little bit ahead like the the scene before the car crash right right he shows up late and Fletcher is like you can't play and he's like yes I am and no one else would even get another opportunity Fletcher Fletcher would have been like get the **** out of here.
+Jordan: Get the **** out of here Fletcher was.
+Darius: Like what is it trying to find a way to get to yes that's what he was doing yeah it's just like yeah well you go get him now and if you're one minute late 5 minutes late 10 minutes late 10
+Jordan: minutes late and also and because he wasn't he was the only one he ever let speak back to him yeah like I don't think he would have ever let anyone else argue back and forth with him like that no he was he.
+Darius: He knew it. He knew he was him. And he couldn't give that away because he wanted to keep him focused. But the way he was always looking for yes, I don't think it was ever a competition. I think it was his job from the moment his ears perked up when he walked past that room or when he walked in that room and had him play.
+Jordan: Yeah, I think so too. Also, it's kind of interesting watching this movie because the first time I saw it come out in 2014. I think I saw it probably that same year. So I would have been 22, I think, around the same age as a character. And I was like, this professor is * ****. Like, he's just ruining this guy's life and whatever, and then, watching it now, though, it's as a full adult, it's like he really did believe in him and he really did want to see him do well. Did he take it overboard? Absolutely. Was he was he insane? Yeah. Should he have gotten his *** and curb stomp for show? But he did really believe in that kid. And he deserved it. Let me just say.
+Darius: You're feeding down the highway 60 mph, you get T-boned. You don't just crawl out and walk.
+Jordan: Into the floor with a concussion.
+Darius: He's just like, oh. the car flips, he lands on his head, gets T-boned at 60 miles an hour. And he just like kicks himself out of the car and just like walks into there with like, and wobbles into the arena. He has like a 111 gash on his forehead. And I was like, you know, he, he would, he might survive that, but he ain't walking anytime soon.
+Jordan: You know, no, He got T-boned on the driver's side and it was speeding.
+Darius: No, not at all. It was, Nine times out of 10, that's a fatality.
+Jordan: So, but I was going to say, let's be honest. Yeah, he wouldn't, she probably should have died.
+Darius: But it was, it was, it was great cinema. And it gave him, it gave him, and he shows up and he ***** up and then they get to fight. And so.
+Jordan: Yeah.
+Darius: Bleeding all over the drum set.
+Jordan: Dropping his sticks.
+Darius: Yeah, just ****. Well, because he was half dead, you know, he was like.
+Jordan: Yeah, but I'll say he was his brain was bruised. Um, but just think about that, though, right?
+Darius: How nice are you that you show up late bleeding out of your head? And he's just like, ready.
+Jordan: And the two. My favorite scene is like when he, before he, he like, he's looking around looking for, uh, uh, Mouse Teller. Then he sees him. Then he sees the blood and he's like. And he's just, all right, **** it.
+Darius: I got to win.
+Jordan: By the way, by the way, how trash were the other drummers if he was was let a concussed human performing in a concert in a competition concert?
+Darius: So I'm not big. I don't know instruments like that, but I imagine it's just like, right, like basketball where the hot, the top 10 players are so much better than the top 20 players. And it's like, right, you could be an all-star and be nowhere near an all-NBA player, you know, and I just think that, you know, maybe he was first team all-NBA and they were just like fringe all-stars, you know, it's.
+Jordan: Like, yeah, when I say trash, I mean trash by comparison that I think I think he was like basically like young LeBron and then the other guys were like Danny Granger.
+Darius: Sure. I was gonna say like The other dudes are like LaMelo Ball and he's like Shay. And it's like LaMelo Ball and 99% of the gyms he walks into is the best basketball player in that gym. But when he plays against Shay, he's like 10 times, like Shay's five times better than him. So it's just, you know, it gets lonely at the top. The peaks are high and you know, the last five miles of a mountain, the summit are the hardest five, you know. What else you got for act 2?
+Jordan: That's all I had for act 2. Although I did like that his main message to the kid they never said verbally was you need to be comfortable being uncomfortable like the second whenever he whenever he saw Miles Teller getting comfortable or getting like smiling too much on the drums and getting a little cocky or overconfident He's like, no, I gotta, I gotta let another fire under your *** now. So let me tell you, suck again. Let me embarrass someone in front of you so you stay on your ****.
+Darius: You know, in a sick and twisted way, it's good leadership. Act 3, the reckoning, the relationship between student and teacher reaches his breaking point, fight we mentioned earlier, forcing both to confront whether greatness is earned through inspiration, cruelty, control, or something more complicated. This movie makes me miss Sea Grace. I know we just had a whole segment about downtowns.
+Jordan: Yeah.
+Darius: You know, places that you could just pop in there, have two drinks, hear some good music and pop out. But I just start with my actual question. So obviously this is almost a caricature, right?
+Jordan: Right.
+Darius: You know, like he is. He's playing it up. But I do think. we lose something as a society when we stop chasing excellence and we started accept like he's like, the thing he said, like the, what do you say the worst 2 words are that's fine.
+Jordan: Good job.
+Darius: Good job. It's like we do, we have started to too easily accept pretty good. And it does rob us of excellence in a little bit. You know, this movie just reminds me that, you know, life is about trade-offs. And A lot of people who wanted to move things in a more, gentle parenting, more understanding, more like they pretend like there's no trade-offs. And you could say the trade-offs are worth it.
+Jordan: Right.
+Darius: But, you know, we ain't no Michaels Joe Jack, you know, like, you know, like the parenting.
+Jordan: No beyoncé. We have no more Beyonces.
+Darius: I don't think gentle parenting is making great musicians. Yeah, that's true. I don't know. There are trade-offs. And you could say for the greater population, it's better to take a more gentle, holistic approach. But Miles Teller as a drummer doesn't reach these heights with a teacher that, you know, was, you know, one of these new school teachers. So.
+Jordan: Yeah, it's like, hey, good job for your first day, whatever.
+Darius: You're a little out of tempo, but you know, work on it when you get home. We'll pick it up tomorrow. You know, like maybe that's not good for everybody.
+Jordan: Not for everybody. Yeah. I think some people, if someone's really, really self-motivated, you can do that with them. I think, the importance of leadership is knowing how to talk to people, knowing when to say what to someone, knowing who, how to treat someone. You know, it's like they always say in sports, you know, some guys need a pat on the head, some guys need a kick in the *** you know, and Miles Tel's character need a kick in the ***. Like, that's just the truth.
+Darius: I would argue though that people who need a pat on the head typically don't achieve greatness. You know, it's Anecdotally, obviously I haven't done any research, but like the people who are motivated by hyper-competitive, challenging environments tend to have more, tend to achieve on the other end. And you know, we spoke another segment about how we always overcorrect for things. Like this guy is outrageous, but I do think, you know, We've overcorrected a bit. It's time to, like, I read somewhere that like a lot of schools don't even give homework anymore. And it's like, oh, is that a thing?
+Jordan: I don't know that ****. That's crazy. That's kind of important.
+Darius: The homework, the tests, we need to grade these papers. We need, like, the school should be hard.
+Jordan: Yeah.
+Darius: School should be hard. We're not just passing kids along. They're supposed to challenge them. It's not just like it's not the DMV where we just you get your ID, you get, you know, like we're supposed to be doing something here. So that's true.
+Jordan: That's very true. I was going to say, like, honestly, like my dad was not this bad, but he was a lot. He reminded me a lot of my father, the character that J.K. Simmons played in this movie. Like that was a lot of kind of how my dad parents, you know, not so much the vulgarities and stuff like that, but just the That's not good enough. Like, no, that's not good enough. You got to be. Why? did you get A? What's up with that? Like, if you brought home a 90, you could brought home a 97 in your interim. If he saw a zero, what the hell? Like, you know what I'm saying? So like, my dad was on us hard about stuff, stuff like that. And I do as a kid, like, you hated it and it was miserable. And you know, you felt like they meant your parents hated you, of course, you know, because you're young and you don't know any better and you don't have any perspective. But as an adult, I definitely see what they were trying to do, you know, both of them. And I see like, I do see the difference, too, in myself and other people where I'm like, they can't, they can't handle criticism. They can't handle a disagreement. They can't handle, you know, competition or conflict, you know, **** like that. Like that is really, really important. And I think that you have to, it sounds like a bad thing, but you have to inflict a certain level of discipline, a certain level of combativeness on a young person for them to be ready for the world.
+Darius: Yeah, I mean, listen, structure is good. And failing is good. Like if you, learning how to do hard things is good. And I just think that, we've sort of strayed a little farther away from that than, I'd like as a society. And I think it reflects in, when they put the, when the astronauts went to the moon a couple of months ago, it was a year ago, maybe.
+Jordan: Yeah.
+Darius: People were wondering why they were like, let me, obvious reason we're going to the moon. People were just like, well, why is this capturing, you know, fracturing through it and capturing monoculture? And I just think people just miss when we chased excellence. You know, like that was a shining example of excellence. And we like the math and the engineering that went into that. And, you know, we sent the best of our best. to the moon and we got them back here alive and it went away without a hitch and we got pictures and we just, I think people like to see us chase excellence, us as a species. So yeah, for sure.
+Jordan: I think that's the draw with, art, the arts, that's the draw with sports, like there's a reason people loved Michael Jordan. It wasn't just because he had cool shoes. It was He was literally walking excellence every night. Kobe, same thing. Bronson, whoever you love. Joe Montana, Brady, Mahomes, whoever you love, whatever. The fact that you knew that they laid it out on the line, they didn't leave any stone unturned in terms of their effort or their pursuit of greatness. We just made the joke about the time Brady sacrificed his family to try to win another Super Bowl. But he really did sacrifice his family to try to win another Super Bowl. You know, like that's not a sane thing a human, a normal human being would do. That's also why no other normal human, no other human beings have seven Super Bowls.
+Darius: You know, that's my biggest problem with these new athletes in general. And a lot of these athlete podcasts is like in wrestling, there's a term called K fame. I think it's how you pronounce it. And it's like basically don't break character.
+Jordan: Okay.
+Darius: You know, like even if you're like, Even if you're in the mall, don't try not to break character. Don't break character in interviews because like yo</t>
+  </si>
 </sst>
 </file>
 
@@ -7492,7 +7689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7517,7 +7714,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7534,6 +7730,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7853,7 +8053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -8507,7 +8707,7 @@
       <c r="E33" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" t="s">
         <v>154</v>
       </c>
     </row>
@@ -8623,6 +8823,23 @@
       </c>
       <c r="E39" s="9" t="s">
         <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="4">
+        <v>2014</v>
+      </c>
+      <c r="C40" s="7">
+        <v>5</v>
+      </c>
+      <c r="D40" s="8">
+        <v>5</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -8637,7 +8854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -8953,6 +9170,14 @@
         <v>152</v>
       </c>
     </row>
+    <row r="40" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EDCBC4-A91B-449B-8618-89F067AAE858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB789B41-965D-47B7-B68C-03AA97336FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="159">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7617,6 +7617,9 @@
 Jordan: Okay.
 Darius: You know, like even if you're like, Even if you're in the mall, don't try not to break character. Don't break character in interviews because like yo</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PO9gS2D0P7o&amp;t=1s</t>
+  </si>
 </sst>
 </file>
 
@@ -7730,10 +7733,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8550,6 +8549,9 @@
       <c r="E25" s="9" t="s">
         <v>133</v>
       </c>
+      <c r="F25" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB789B41-965D-47B7-B68C-03AA97336FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E06A207-53AE-4C7B-AFE6-7B54716F3AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="160">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7620,6 +7620,9 @@
   <si>
     <t>https://www.youtube.com/watch?v=PO9gS2D0P7o&amp;t=1s</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Dr80QihOZjY</t>
+  </si>
 </sst>
 </file>
 
@@ -7692,7 +7695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7717,6 +7720,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8809,6 +8813,9 @@
       <c r="E38" s="9" t="s">
         <v>147</v>
       </c>
+      <c r="F38" s="10" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="39" spans="1:6" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E06A207-53AE-4C7B-AFE6-7B54716F3AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498EC633-9F79-4032-8D87-A995AF3D650A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="166">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7623,6 +7623,374 @@
   <si>
     <t>https://www.youtube.com/watch?v=Dr80QihOZjY</t>
   </si>
+  <si>
+    <t>Blackening, The</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: Reunion at the Cabin | Act 2: The Game Begins | Act 3: Monoculture or Fragmentation?&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius break down The Blackening, examining its horror-comedy premise, Black cultural references, friend-group dynamics, and larger questions about identity, community, and whether Black culture still operates as a shared experience.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 covers the Juneteenth cabin setup, the dated Twitter-era feel of the movie, Jay Pharoah’s performance, and the social rules of group vacations. Act 2 explores the game’s Black-culture trivia, Spades traditions, generational differences, and the film’s horror logic. Act 3 shifts into a larger discussion about monoculture, changing neighborhoods, cultural identity, and whether the movie successfully communicates its central idea before ending with ratings and final verdicts.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Is Blackness still a monocultural experience, or have modern life and changing communities fragmented that shared identity?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Black culture has never been completely monolithic, but modern media and changing social environments have created even more distinct Black experiences than previous generations shared.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Integrated neighborhoods and economic mobility expanded opportunity, but also weakened some shared cultural experiences that once connected Black communities across class lines.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Has the Black experience become less monocultural over time, and is that cultural fragmentation ultimately a good thing or a bad thing?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Black identity&lt;/li&gt;
+      &lt;li&gt;cultural fragmentation&lt;/li&gt;
+      &lt;li&gt;community&lt;/li&gt;
+      &lt;li&gt;Spades and traditions&lt;/li&gt;
+      &lt;li&gt;stereotypes&lt;/li&gt;
+      &lt;li&gt;representation&lt;/li&gt;
+      &lt;li&gt;friendship&lt;/li&gt;
+      &lt;li&gt;belonging&lt;/li&gt;
+      &lt;li&gt;modern Black culture&lt;/li&gt;
+      &lt;li&gt;nostalgia&lt;/li&gt;
+      &lt;li&gt;monoculture versus individuality&lt;/li&gt;
+      &lt;li&gt;social change&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Jordan: Hey guys, welcome to The Out the Trunk Pod with Jordan and Darius. This is our movie review segment. My name is Jordan. That's Jordy B Riding on all socials.
+Darius: And I'm Darius. That's Deez All Up in the area on all socials.
+Jordan: And today we're going to be reviewing The Blackening.
+Darius: All right, we're going to go with Act 1, Reunion at the Cabin. Some college friends, 7. 8 surprise reunite for Juneteenth at a secluded cabin expecting games and celebration. Their weekend turns unsettling when an ominous discovery reveals someone has already carefully planned their arrival there. Classic bait and switch using the known actors to draw you in then send them home.
+Jordan: Right, just kill them off right away.
+Darius: Scream did this. And a few others did it where it's like, Hey, we only need you for like 10 minutes.
+Jordan: Yeah, yeah, you get two scenes, bro.
+Darius: You'll be home before dinner, so.
+Jordan: Yeah, right. You only get the lines for real.
+Darius: Yeah. So that and the shrooms in Molly made me feel, oh, man, when my kickbacks used to just have booze and maybe we.
+Jordan: Yeah, we never really did that in college. I mean, people did, but I didn't. So, yeah, I'm with you on that. Also, is it just weird? Did you feel that this movie came out 10 years ago?
+Darius: It was very resistance Twitter coded. Like it was the whole linking for Juneteenth is just not as real.
+Jordan: Yeah, it felt very right. Yeah, exactly. Yeah, it's actually wrote this down. I think I can't remember. So somebody said like, we're missing out on like black moves. Our black moves are very different now. And somebody made a great point and they said it's because A lot of black movies now, they're just explaining our blackness to white people.
+Darius: Yeah.
+Jordan: And this movie kind of does that a little bit.
+Darius: It's very, you remember when like Oscar so white was like the peak of Twitter? It just feels like it was written during that time where it was just like, you know, where there's just a certain kind of, I have it in here, like a blavity. Yeah, I'll get into it later. But yeah, it's very much they literally play a blackboard game where it's like, name that black tune. And it's like, yeah, very cringe. What else you got for act one, man?
+Jordan: It's funny you brought up the first scene that they had two people that we know, Ivan **** famously, of course, of Insecure, and Jay Farrell from SNL and his impressions. He's Jay Ferro is a great impressionist, and he was in this movie for 5 minutes and he was terrible in every minute of this movie. He was saying.
+Darius: Because he wasn't trying that. He was like.
+Jordan: He's just not believable as an actor to me.
+Darius: I don't know why. Oh, well, yeah, because he's not good. He's not. Yeah, he's not. I just don't see the talent impressions. Don't impress me. And he's not funny.
+Jordan: He's not as good for comedy. Correct. Yeah.
+Darius: And I don't I don't get I understand why impressions are important for like an SNL because you need the skits and the different things like that. But I think having good characters, original characters is more important than just, okay, so you can sound like Chris Rock, but like, why is that funny? I don't get it.
+Jordan: Yeah it's like like I love impressions and like Eddie is one of the greatest ever obviously and he one of the greatest impressions ever but he also had great jokes you know uh that's the difference there um and I think Jay for me Alicia Farrow he does his impression so much that when he's being himself that feels like a bad act like I feel like a bad impression uh so maybe that's probably just what it is but yeah he wasn't great no he wasn't um.
+Darius: What's the most amount of people you would go on a cabin vacation with? Assuming, let's just say a four bedroom cabin.
+Jordan: Four bedroom cabin vacation.
+Darius: Yeah, you're not renting a McMansion or anything, just a regular old cabin in the woods.
+Jordan: So there's four, four, four rooms in a cabin, probably seven people. I'm assuming there's some couples there.
+Darius: So yeah, okay. So if there's couples, the numbers different, but just like I mean, so I would say 6, two couples and then, two singles. Two singles. But I'm too old to be sleeping on anybody's couch. I need my own room. And I don't share rooms with people I'm not ******* with women I'm not *******. So I don't share rooms with dudes at all. And I don't share rooms with women I'm not *******. So it would be It would be, you had that to clean up that people. You had to make that not gender neutral. And so, yeah, I had to clean that up. That sounded a little too riding the fence. No pause. But let's just move on.
+Jordan: You know what's funny? It's funny because somebody was talking to me about they have a beach house. I know it's a friend of mine. And there was something like, yeah, we should go there. And I'm like, Yeah, sure.
+Darius: Just you and him.
+Jordan: No, no, it was a girl. Well, it's a friend. No, not a family does or something like that.
+Darius: Why are you here? I can't say I'm wax, so I have to look.
+Jordan: Okay, fair enough.
+Darius: Fair enough. We move right along. What did you said your answer was seven. My answer was six. It was fun though. My family and I are planning a cabin like retreat for Christmas. Nice. But we're going to do it.
+Jordan: We're kind of trying to plan something like that too. Yeah.
+Darius: We're not going to do it on Christmas though, because why pay? None of us still believe in Santa Claus. We're all grown. So it's like we're going to go like 2 weeks before and get the same vibe, but for like half the price.
+Jordan: That's smart.
+Darius: You were not flying on Christmas, booking a hotel on Christmas, going grocery shopping on Christmas. Like the youngest is 22. It was my niece. None of us believe in Santa Claus. So why don't we just move this up two weeks and save ourselves a bunch of money and a bunch of hacks. That's smart.
+Jordan: Yeah. I'm with you on that. Yeah, we're trying to we're thinking about trying to take a trip this year for Christmas too, but we're trying to get everybody on the same page and all that. You know, we got a big family, so it's tough to.
+Darius: Yeah, my sister showed us the cabins and they look dope and we're going to, we're going to, it's in Minnesota. So mom and pops and my nieces don't have to fly in, but like my sister and I will fly in and, hit the grocery store, buy up anything we think we might need at the liquor store, get some games and I'll cook, take turns cooking, breakfast, lunch, dinner, things like that. So I look forward to it.
+Jordan: The 3 squares. Yeah. So it sounds fun. Okay, so the one thing that I thought was a bit unbelievable about this movie in the first act was the one thing. Well, several actually. The first guy who pulls up to the house He didn't have the code. And I'm like, you are out in the country, you know, you black and you don't have the code to get into the house that you're renting for the week. Come on now. Like, that's not even logical.
+Darius: So I have had now wasn't in the middle of nowhere. It was we were we were taking a cruise out of Miami. But you never fly in the day of the cruise. You fly the night before because flights can get you don't miss your boat. And so we got a family Airbnb in Miami the night before and my flight got in early. And so I just wasn't thinking, I don't do Airbnbs. So I just caught an Uber to the address and I got there and I couldn't get in. So I have not, I wasn't in the middle of nowhere, but it has happened to me. So it can happen if you're not used to Airbnbs.
+Jordan: Okay. So, okay. So what, in the first actor so far in this movie, did you find not believable? Like were some of the things that we were like, we wouldn't do that.
+Darius: Major party foul inviting someone that they're not telling anyone else. Yeah, no one cares if you invite your dude. No one cares if y'all, whatever, y'all, everybody grown. But I need to know, like, I'm supposed to be in the woods in a cabin with these people. I need a full attendee list. You can't just bring people on me.
+Jordan: You can't just have no surprises.
+Darius: Yeah, and like, I'm probably gonna be cool with it, but it is really poor for him to do that to somebody.
+Jordan: Yeah. I had that happen once. A friend invited me, hit me up in a group chat of like four people to come to a kickback. I see on social media, it's like a big party. I'm like, cool. I **** with everybody there. I walk in, the first people I see are two people I really, really don't **** with. And I'm like, none of y'all thought to text me. Hey, yo, code red or anything like?
+Darius: Yeah, yeah. I think it's a bit different when you're like on a vacation and you literally can't leave, right?
+Jordan: That's fair.
+Darius: And, you know, but it's still poor form, you know, if you know, I have at least a heads up, you know, if you know I have.
+Jordan: Right. Let me like be mentally prepared and ****.
+Darius: But yeah, I'm at this point, man, I'm just kind of a go with the flow dude. So yeah, I don't know. I probably I would find it to be poor form, but I wouldn't make it a problem on the cab.
+Jordan: I hear you. So yeah. Did you find him to be annoying though? The, I forget what his name, Dwayne, who just like made it such a big deal that she brought her ex to the thing.
+Darius: Yes, 100%. He was being a big baby.
+Jordan: Yeah.
+Darius: Until he got high, which, could have done without. But he was just being like, ultimately, he.
+Jordan: Was like, did you want to, yeah, I was like, dude, do you want to date him or do you want to date her? Like, I don't want that. What's the real reason behind you acting like that? Because most friends would not.
+Darius: And I understand the frustration that she probably was like ******** to him about whatever dude did.
+Jordan: For sure.
+Darius: But like, man, I don't know, dude, everybody grown. And at a certain point, you got to just accept that grown people going to do what grown people want to do. And you can't keep With 2 grown people want each other, ain't nothing you can say to keep them apart.
+Jordan: It's nothing you can say, nothing to do.
+Darius: Nothing to say, you just got to let it run its course.
+Jordan: Ain't no spell you can catch.
+Darius: Yeah, it's like a cold, man. Ain't no medicine. Just let that run its course.
+Jordan: Right.
+Darius: We want to get into Act 2.
+Jordan: Yeah.
+Darius: All right. Act 2, the game begins. forced into a twisted game built around stereotypes, to say the least, and friendship. The group must answer questions, confront old tensions, and cooperate while searching for a way to escape the cabin alive. Is it just me or does every large party have a random person no one seems to know?
+Jordan: Yeah. Every, all the time.
+Darius: If you ever go to, if there's 20 or more people at the function, kickback, whatever you want to call it, there's always one where you're like, who is that? And they're like, oh. So you don't know who this is?
+Jordan: Yeah. And you walk in and you're like, did I, did I meet them and forget? And he's like, it's like his wife, husband.
+Darius: I'm so and so. It's like, what's up, man? How's it going? Yeah, cool. Yeah, dude. And they, it just, you just, no one ever actually confirms who they are, who they're with. Yeah. But you know, that's how you know it's good vibes. Cause you know.
+Jordan: That's true. You want to be inclusive and you got to have friends who know how to meet new people. That's incorrect. Okay, so the spades, the first spades conversation, that was the one realistic thing in this movie where people will chess at you for not playing or not playing well or not knowing how to play, but they're not actually willing to teach you how to play. And it's like, how is anyone supposed to learn?
+Darius: It's if you can play, no, you can play spades. It's not, you know, But it is true that I don't recall someone teaching me how to play. It's just I just know. So I don't remember anyone. I remember someone sitting me down and teaching me how to shoot dice. Because doing that wrong can get you harmed. Like literally.
+Jordan: You will be out of here.
+Darius: So you know that requires strict instruction, but.
+Jordan: Correct.
+Darius: Spades, I just kind of, I don't remember, I probably did some dorky **** and just like found a computer application and taught me that myself that way, but I don't remember learning how specifically.
+Jordan: Yeah, I learned how, because you only play it in like big parties and I don't really go to a lot of big events all the time. You just kind of get.
+Darius: That I can just throw caps when you say things. I wish I could just throw a bunch of caps right now.
+Jordan: Flag on the play.
+Darius: Yes. Five yard penalty. Repeat first down.
+Jordan: Okay, let me rephrase that. Of the events I've been to this year, spades weren't played at a lot of them. I put it like that.
+Darius: I feel like that's a recipe we're losing. I don't remember the last time a game of spades broke out in an event.
+Jordan: Really? Yeah. I mean, so it was played at Sed's birthday party. It was played at, I think, if we played it, they played at Friendsgiving. I think it was played at my cousin's graduation party this year. So that was a few months ago. So, you know, suck my aunts and you know older people you know of course so they know how to play of course.
+Darius: Maybe they get out enough.
+Jordan: That's probably true no I think I think we probably are losing the recipes a bit like I mean I don't I mean I don't know a lot of younger people I guess but I I'd imagine they may not know how to play Spades probably not it.
+Darius: Leads to a question I have later but it's it's more toward the end so okay um What is your most memorable game of spades? I guess I will replace the question I have there because it's bad, but what is your most memorable game of spades?
+Jordan: It's hard to say. So my parents were kind of like the host parents, they always like, we always had a bunch of cookouts and stuff like that at our house and all that stuff. So we'd have a lot of spades games at our house. I just remember my dad, Cussing out lots of people and get almost get into lots of fights with people **** over space. People accusing people of cheating and **** like that. You know how that goes.
+Darius: Reading it again, playing under the table.
+Jordan: Yeah.
+Darius: My most memorable one, 2014. I had moved to Raleigh in August, and so we had a family trip to Orlando. not Disney World, but Orlando. We did one day in Universal when, we didn't go to Disney. We were in Orlando. And so I had just financed the move from Southern California to Raleigh in August. So I had no bread like that. So I caught the Amtrak from Raleigh to Orlando.
+Jordan: And so how long has it trained?
+Darius: 12 hours? Like 20, 13, 13. And the way down, I just slept. the way back up, they're like, the long trains have a community car and like a bar car. And so I just walked back there trying to get a beer and there were two different game of spades being and played. And so I just sat down and played spades with people as we took the train up the coast basically. And at different styles people would get off and then people would get on and some people would join and people, and I'd hear the stories like one of the dudes playing was on the train back from, he just got out of prison. And so you get out of prison, they give you like 100 bucks and he just bought a train ticket to his hometown because no one picked him up. And so he was just exchanging stories, talking ****. The plan was do some drinking. We ain't really do any drinking. We were just, and we did that. **** it must have started the train. We did that all through the night. I don't think I stopped until I got off the train at like 8am. And so that was a really great experience, man. Just playing fades with random people taking the train up the coast and just hearing everyone's story. When you're dealing with people who are taking a train from Orlando to Raleigh, You get some interesting characters and these it was fun, man. I'll by contrast, my story was kind of boring, but.
+Jordan: The lure of Florida.
+Darius: Yeah, it was just I heard about a divorce and the guy who got out of prison. He's like he's excited to get home and we were just playing spades. It's a friendly game of spades up and down the East Coast. So that was my.
+Jordan: That's dope. That sounds really fun.
+Darius: It was a good time. You got anything else for Act 2?
+Jordan: Yeah so one of my favorite scenes from the movie is where they're they're playing the game all together and it's the question about how many black people were on friends and it's funny because I actually knew the answer and I was like literally thinking it as they were saying the names you know And I like every person that said, they were like, I don't really watch Friends, but I know the mom for Fresh Prince was on one episode. And, you know, I don't really watch Friends, but Gabrielle Union was a love interest. And, you know, it's one of those, I feel it's one of those like lies that some people tell us just sitting it seemed like ultra poor black. It's like, I never saw Friends. It's like, okay, I think people haven't seen it, but.
+Darius: My answer would have been zero. But. I can't say I've never watched an episode of Friends because there's been, you're in a hotel room. Right, there's eight channels.
+Jordan: It's on every channel.
+Darius: Of course, I've watched it, but I couldn't tell you what happened on the episode. But yeah, I've certainly watched the episode. In the episodes I've seen, there were no black people in that. No, right, yeah. My answer would have been zero, but it would be because It wouldn't have been because I didn't watch the show at all. So.
+Jordan: Right. But it's just funny. Also, I did like the fact that the answer, the correct answer was I didn't watch Friends. I watched Living Single.
+Darius: Oh, that was very corny. I would do the white things like the black. It is black.
+Jordan: Yeah. Well, you listen to that weird **** that rock and roll.
+Darius: Yeah. Oh, my God. It's like. You'll tell someone you like a show and they'll be like, hey, black people on it. It's like, I want black shows too, dude. Everything I watch doesn't have to align with my worldview. It just feels like a very boring way to go through life. But I know people who like, if the show is not primarily casted with black people. They just won't watch it. But that just feels like a very boring way, a very unimaginative way to consume content. So.
+Jordan: Right.
+Darius: That's not to say you shouldn't watch anything black. I watch a lot of black ****.
+Jordan: You need to watch. Yeah.
+Darius: I don't know. I just don't I don't filter my content through. Does it meet my racial quota? I think that's a weird way to go through life. I'm trying to I have all the questions here. And yeah, none of them are that good. Name the actor who played O.J. Simpson's lawyer.
+Jordan: Oh, keep getting. Oh, no. Courtney B. Vance.
+Darius: Yeah. So I don't really. That's just me reading a list. So you got anything else right to.
+Jordan: OK, so yeah, they have the first guy who's coming up the stairs and they're trying to save Molly from the guy and. For some reason, they have like the smallest dude and a woman blocking the door. I'm like, Why don't you all get together to block the door like that? I didn't get that as they sit there to talk about the Adderall that that girl took. That was pretty dumb. Also, I feel like the guy who whoever wrote the movie has never done drugs before because Adderall doesn't make you spacey. It makes you super aware and attentive. So I didn't get that either.
+Darius: Yeah, I mean, I thought that was odd as well. The whole I mean, Adderall is literally attention ADHD medication. So I thought that was strange, too. You know, I wasn't I don't really did pick. I expect people to do **** **** in scary movies because that's like the premise.
+Jordan: Right, for sure.
+Darius: I so call a man boy because I don't I've been watching snowfall. But he The movie would have ended. He's armed. He should have just, we're always going to sit in this room and I'm going to guard the door with my gun. And the first, when the bad guy walks through the door, I'm just going to shoot him and we're going to go home. You know, but that's what the one armed person should do. Everyone get behind me. We're going to block off all walls. We're going to check off the entry point. And when he walks through, we'll shoot him and the movie's over. But that would make for a very boring movie. And then we get to act three where they just run through the woods. So You got anything else for that one?
+Jordan: Yeah, that's pretty much it. I mean, I did. I did write down who's the blackest because that scene was pretty kind of funny, but it wasn't much to say about it because I mean, I remember seeing that scene on Twitter and it went viral. I thought it was really funny back then. It didn't necessarily age great, I guess. Also, it was clear as day that The weird dude was probably not going to be conventionally considered quote unquote the blackest.
+Darius: It couldn't have made it more obvious he was the bad guy. So heading into actually turning the tables with trust strained and options narrowing the friends combine their strengths, challenge assumptions and seize control of the night, discovering what solidarity requires when every choice carries consequences for everyone. I have here the twist was, you know, the guy The weird guy was the bad guy and they were mean to him earlier. And I just went like, this is, I blamity blacks like fever dream. Oh my God, the cool kids are mean to me. I was just like, they say I talked white. Oh my God. 40 years old still because you're teasing 8th grade. It's like, I just, I allow space for that because it did happen. I was there, but my God, people, like it just, it was a lot. So what else you got? What do you have factory?
+Jordan: Yeah. Yeah, they did the one thing you're never ever supposed to do in a horror movie split up. It did work out in their favor, of course, in this movie. Yeah, I did write down the weird kid because, you know, one of my things growing up was always, no matter what happens in school, Always, always, always be nice to the quiet, weird kids because you want to make sure that you make it home.
+Darius: a more charitable interpretation of that would be nice to them because it's, like being a kid is stressful and, a lot of change should be nice to everybody. And, it's good to welcome people and, be friends to everybody. So we'll go with the charitable explanation for that. So so it was, I was alluding to it earlier with spades, are we losing that? This movie made me think like that quiz that they had and that trivia that they had and the spades thing is like, is blackness still a monocultural experience?
+Jordan: That's a great question. I feel like that's really all this movie was trying to say. They just didn't say it well. No, it's not. I mean, it never was. I don't think it ever was. Well, let me rephrase that. After, well, in the US, obviously slavery was a monolithic experience. Reconstruction, Jim Crow, all that was monolithic. But I feel like around, say, I don't know, the 70s or 80s, that's when you started to see different archetypes of black people, I feel like. On a broader scale.
+Darius: I think housing used to be much more segregated. So black neighborhoods used to have people of all socioeconomic backgrounds. And I think now you're like, and they created a monoculture experience because like the doctor lived in the same neighborhood as the UPS.
+Jordan: The maid or the bus driver.
+Darius: And who lived in the same neighborhood as you know,
+Jordan: The drug dealers.
+Darius: The drug dealers. And so, because there's only so many places you could live and as a black person, so we all, up through the 90s, we all kind of shared, regardless of our socioeconomic status, the same experience. And I think that is no longer true. Like there are rich black suburbs now. You know, and like black neighborhoods and bad neighborhoods are almost entirely low-income people now where it used to not be the case. It used to be even in the low neighborhood or low income neighborhoods, like the guy who, had a good government job still stayed in that neighborhood. it just, that was just his city. That was his neighborhood. And so I think that fracturing of where we live, the sprawling out of where we live has sort of weakened the ties of a monocultural blackness, if you will. So I just want to say that that's, our experience is fractured. But since we all stayed in the same neighborhoods, we still had the, I'm sorry, our professional lives fractured, our incomes fractured, but our experiences didn't fracture because we all lived in, we all went to the same block parties. We all, Thanksgiving was at the same place. And so it's families now where the well-off such and such don't even come home for the holidays anymore. And so I do think it has fractured. And whether that's a good or bad thing, I don't know. But Yeah, I would say it has fractured a little bit. It's no longer monocultural.
+Jordan: So yeah, that's very true. Yeah, I think the movie tried to say that and just didn't do a great job because each person was very different. You know, you had the the super pro black light skinned girl. You had the dark skin, like you had the baddie, you know, you had the dude who was like in the street **** but, you know, was in school and I guess got his life together, married the white girl. You got the dude who was, I think he was like a personal trainer or something like that, whatever. Then you got the, you know, basically, essentially Kelly from Insecure, knockoff, who was like the funny loud girl, you know, they trying to fit every, check every box.
+Darius: Yeah, but it's still, you're still dealing with a selected group of people because all these people went to the same college. And most black people don't go to college at all. So it's still, you're still dealing with the same. It's still like, obviously people go to college and they go off and do different things, but you know, they're not there. I doubt most of them live in black neighborhoods primarily. Right. And so, you know, it's just, I do where you live shapes A lot. And you know, I think, The fact that we no longer all live in the same neighborhoods. And look, you know, I get it. I'm not in a rush to move back to the projects either, but it does. I am a little bit intentional about where I live. Like I live in an apartment complex that's still primarily black. And so it's what I prefer. But I do think. You lose connection to your culture when when you, you know. aren't seeing a wide range of it, if you will.
+Jordan: Yeah, that's very true. I think, like, even for me, like, you know, I'm in a predominantly white neighborhood, so we don't really talk to the most of, or they don't really talk to us, somebody like that. A lot of them in my neighborhood. So I have, you know, my close friends from where we hang out at, and then I have my friends who live, you know, in other cities. They're mostly black, you know what I'm saying? I mean, I have white friends, of course, but by and large, I almost have to go other places to see my black friends, because Raleigh is not segregated, but there is so many different archetypes of black people that you see around that can make it hard to find a good circle of people.
+Darius: I hear you, man. I just, you know, it's important to me that like, when I get home from my jog and I wave at my neighbor, she says, how you doing, baby? And when I go and check the mail, the fellas are at the park shooting ball and offering a shot if they're out by the grill and things like that. So it's just, look, am I, you know, Mr. Social with the neighborhood? Am I outside throwing block parties? No, but it's important to me that the waves are friendly.
+Jordan: Yes, yeah, exactly. You know, yeah for sure it's like you know in my neighborhood it can be broad daylight and I'm walking Charlie and somebody might steal across the street you know what I mean
+Darius: that is fair what else you got for act three
+Jordan: oh yeah so yeah we guys we talked about it but did you feel like that the motive was really **** **** for his revenge plot on all these all these people He met them one night at a party.
+Darius: I don't know, man.
+Jordan: Drove home drunk and tried to kill everybody.
+Darius: You know, I, yes, it was paper thin. But the way I see grown people carrying on about, oh, like if I have to hear one more anime kid talking about how mean they were to him in 6th grade, there's a Comic-Con in every ******* city, dude. Go to that and stop ******** at me. I just, I grow, get over it. You know, like these people deeply, deeply feel a way about it. And I think they, I, you know, It seems silly to me, but the way these people be carrying on, who knows? You got anything else for act three?
+Jordan: Yeah. No, that's all I got.
+Darius: All right, what do you rate it, man?
+Jordan: I gave it 2 1/2 stars.
+Darius: I gave it three. I found, I saw it in the theaters when they came out and it was a much more enjoyable first watch than a second watch. And so I'm going to factor in that theater because if you ask me leaving the theater, I just had a four. But it's three. The ending was stupid. I just like endless chase scenes. Honestly, I fast forwarded through like 20 minutes of them running around the woods.
+Jordan: Yeah, you really could have.
+Darius: And I didn't miss a thing. So I'm going to give it a three. And yeah, I'm with you.
+Jordan: The acting was good or pretty good for most of it. Just the script wasn't great.
+Darius: Paper thin. So with that, all right. Thank you for listening. My name is Darius. That's these I love the area on all socials.
+Jordan: And I'm Jordan. This Jordan be writing on all socials.
+Darius: Please rate, like, and subscribe. We're at Out the Trunk Pod on all socials, Gmail, website, Google, all of the above. Reach us out, rate, like, subscribe, all of the above. Thank you.
+Jordan: That's a wrap. Thanks for coming to the movies with us.
+Darius: All right, y'all.</t>
+  </si>
+  <si>
+    <t>American Psycho</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: The Perfect Surface | Act 2: The Mask Slips | Act 3: Reality Unravels&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius break down American Psycho, examining Patrick Bateman’s obsession with status, consumerism, masculinity, and identity while debating the film’s satire, symbolic meaning, and ambiguous ending.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 explores Bateman’s luxury routine, Christian Bale’s performance, the movie’s meme legacy, analog filmmaking, and the corporate world’s obsession with appearances. Act 2 focuses on capitalism, homelessness, office culture, friendships, dating, and status without meaningful accomplishment. Act 3 unpacks the unreliable narrator, whether Bateman killed anyone, Fight Club comparisons, white-collar masculinity, and the hosts’ sharply divided ratings.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Did Patrick Bateman actually kill anyone, or was the entire story a fantasy shaped by an unreliable narrator?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Bateman serves as a metaphor for capitalism, patriarchy, and white male privilege, making the murders less important than what they represent about harm, power, and impunity.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The film belongs to a recurring 1990s and early-2000s tradition about comfortable office workers confronting boredom after becoming one of the first broad generations of middle-class men in corporate jobs.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Is American Psycho primarily a murder story, a satire of capitalism and masculinity, or an unreliable-narrator character study?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Capitalism&lt;/li&gt;
+      &lt;li&gt;consumerism&lt;/li&gt;
+      &lt;li&gt;masculinity&lt;/li&gt;
+      &lt;li&gt;status obsession&lt;/li&gt;
+      &lt;li&gt;identity&lt;/li&gt;
+      &lt;li&gt;conformity&lt;/li&gt;
+      &lt;li&gt;office culture&lt;/li&gt;
+      &lt;li&gt;wealth and privilege&lt;/li&gt;
+      &lt;li&gt;unreliable narration&lt;/li&gt;
+      &lt;li&gt;social satire&lt;/li&gt;
+      &lt;li&gt;alienation&lt;/li&gt;
+      &lt;li&gt;the boredom of modernity&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Jordan: Okay, everybody, welcome back to Out the Junk Pod with Jordan and Darius. This is our movie review segment. My name is Jordan. That's Jordan to be writing on all socials.
+Darius: And I'm Darius. That's Steve's I love the area on all socials.
+Jordan: And today we're going to be reviewing the cult classic American Psycho starring Christian Bale.
+Darius: All right, act one, the perfect surface. Patrick Bateman, Christian Bale's character, navigates an immaculate Manhattan routine of work, status, fitness, and nightlife while subtle cracks expose the emptiness, competition, and unease beneath his carefully constructed identity and social world. Ladies and gentlemen, this is the OG Lux Maxer. That's the first thing I thought in that opening scene, which makes sense because he's a psychopath.
+Jordan: Right.
+Darius: Life is for living and you should not be trying to, maximize your sleep score every ******* second of the day. So. Yeah. What you got for act one, man?
+Jordan: So, okay, so there's the opening scene where they're showing like the food and there's like the. they're setting up the plates with all the garnish and all that stuff, whatever the servers are listing the specials for the night and every single item that they listed sounded disgusting like it was like shoot they didn't even go together you know which is kind of a great way to open the movie considering the opulence and decadence and the the under creepy underbelly of his psyche you know throughout the course of the film I thought that was a great way to open the movie I also want to say that This movie has like extreme meme meme life. You know, there's the the oh my God, it's got a watermark. You know, there's the where he's walking through the office with his headphones on, where his music blasting people put people make that post all the time on Twitter about them going to work with their music. The workout routine, you know, that the creepy obsession with You know, I use this scrub and this, this mask and, you know, all that stuff. So we had a lot of great cultural relevance considering what it was, the way it was critiqued at the time.
+Darius: You know, let me just say I have been to a fancy restaurant or two, and it's a lot of this stuff is good, but I've never left and wanted to go back. Yeah, just. The vibes. It was always like for work and I wasn't paying for it. So, but I'd be probably be ****** if I did pay for it. But how was the movie received at the time? I don't actually have that information.
+Jordan: I think at the time it was critics liked it. I think audiences didn't really **** with it that much compared to what the legacy that it has now, I'll say. I remember, I think I read somewhere that While they were shooting the movie, people thought that Christian Bale's performance was like weird. Like people on the set thought like he's bombing this movie. They didn't really get what he was doing. And then of course, after the fact, now everybody totally understands the vision that he had and what he was trying to say through the character performance.
+Darius: I must admit, I thought some of the scenes were a bit hokey, but I, you know, it was released in 2000, probably filmed at night. It looks like a movie that was filmed a little bit older. So I don't really think. I think it was bad. I just thought it's cool. I don't understand the cult following behind it, but I enjoyed it. It's fine. When you watch a 90s or 2000 movies, what's the first thing that stands out as different to you?
+Jordan: The fact they shoot on location. It's not a green screen and There's real people that are just walking around, you know, in the background, things like that. I'd say the color palette for sure. They just seem more colorful then. There's just a grittiness to 2000s movies and 90s movies in particular that I consider this basically a 90s movie came out in 2000 shot 99. You know, there's just a grittiness that those movies tend to have, you know, that make things feel real and grounded, even though the stakes may be super high. Like in this movie, everything's very heightened and extreme, but it still feels real, you know?
+Darius: Yeah, the you definitely can movies back then and for good, we're just more analog. You could feel the characters. This would have been CGI to death if it was made today.
+Jordan: Right.
+Darius: And I don't like CGI graphics for the most part. They're necessary at places, but I like for sure. What's the opposite of CGI? There's a word for it. Practical. Yeah. So first thing I've noticed when I watch a 90s or 2000 movies is the cars on the road are junk. If you want a sign of how much richer society is than it was 20 or 30 years ago, you will look into a run-of-the-mill, working class You'll see a bunch of high, you'll see a bunch of 40, $50,000 cars.
+Jordan: Correct.
+Darius: That's a new thing. That is not what it used to be. These cars are junk on the road.
+Jordan: Yeah, I remember I was, I took an Uber a couple weeks ago to get a haircut and the guy was driving a Lexus and he's like, yeah, it's like a cheap little like Toyota, whatever, you know, and he's like, but you know, in the Porsches, some of them, people's dream cars, but I don't really get why they own $60,000, like, you know, and I'm like, dude.
+Darius: It's, you know. Yeah, people. Yes, people are. What is it? Living standards have increased for sure.
+Jordan: Yeah, 100%.
+Darius: You know, the childhood home I grew up in, I don't think had three TVs in total. I have three in my living room, so. Right. So that was a home with four or five people in it. So.
+Jordan: Yeah.
+Darius: What else you got for act one?
+Jordan: Oh, so I don't know if you notice or not, but this movie was actually the inspiration for the music video Love Lockdown by Kanye.
+Darius: I did not know that. I don't remember.
+Jordan: So if you ever go back and watch it was the. That music video was, no, that was live action. It was Heartless, that was animated. But basically the background is all white. It's very like a sterile apartment. He's wearing like a white suit and ****. You know, he was like, he said, you know, it was, he loved that movie. And he felt he feels like Patrick May, which I kind of, he's pretty out there. So I kind of get it. And so that's kind of what made him want to use that as the muse for the music video.
+Darius: When people go crazy and they're like, there are no signs. Maybe listen to someone when they say they feel like Patrick bait me.
+Jordan: You bait me. Right. And this was like 20 years ago.
+Darius: Yeah, that was it. There's always signs. But don't just go crazy overnight.
+Jordan: No. Even the fact that Patrick Bateman in the movie, he's like he had all these quotes by like Ted Bundy and **** like that. Like, you know, you don't just no one, no normal person just drops those quotes.
+Darius: Yeah, it's almost always, almost always. It's always just when people say there were no signs, it's just the family lying about ignoring the signs. Right. There's always signs. What else you got for?
+Jordan: I'm going to say. Oh, so. Obviously it's a spoof and it's a lot of satire in this movie. The whole thing is satire. But I love the fact that he's talking to his girlfriend and she's like, he's like, I have to work out. I really need to focus on my job. She's like, why you hate that job? And he just takes his headphones off and goes, because I want to fit in. You know, and it's not very often you hear people just say that out loud. So I thought it was kind of funny that he just had that awareness to just blurt out. Also, if you like, he's into looks and big brands and all that stuff, whatever, but everybody that's in his life, they all look and dress and talk and act the exact same. It's like a uniform.
+Darius: Yeah, I mean, there's, well, yeah, that's true. That is very true. They all eat at the same bland *** restaurants too. So I was going to have a rebuttal, but actually not think about it. It's true. They are all like that. You know, one of the bits in the movies is like everyone forgets whose name is who. because they're all the same person. And so there's a lot of there's a reoccurring theme in 90s movies of just like upper middle class dudes bored to death by their cubicle jobs. And I think that was because like, I don't know, maybe that was like the first generation. I don't know for sure. So fact check me later people. But maybe it was like the first generation of middle class to upper middle class dudes who had office jobs. Because before office jobs were just for rich guys. And You know, it's a lot less exciting than working in a factory. Sure. But ain't none of them people running back to the factory. So I think. Right. Every you know, it is a remarkable achievement to have a boring cubicle job that pays well. So everyone. Yeah, that's that's very true. So I but it's funny to watch how many night like Fight Club and right.
+Jordan: I was going to I brought that I wrote that down.
+Darius: They're just about dudes bored with their, you know, comfortable cubicle, well-paying jobs and, you know, nice apartments. Yeah, like the boredom with modernity. And it's like, all right, man, you can go start a subsistence farm and move into the woods if you want to. I mean, there's nothing stopping you. Yeah.
+Jordan: Or, you know, when that recession or depression hits and you, you know, working three jobs to make half what you were making.
+Darius: Be careful what you wish for. The boring is good, you know.
+Jordan: So yeah, absolutely. Okay, did you know that Christian Bale, to prepare for the movie, he actually did do the morning routine every day?
+Darius: I did not know that.
+Jordan: Yeah, I mean, it makes sense because have you read the book?
+Darius: No, I have not.
+Jordan: It's so extreme. Like I think you'd have to do that every day just to memorize it, to even act that on screen, to be honest. Like it's like it was like 15 things he does every single morning to get dressed or to get ready for the day.
+Darius: I do remember reading up. I own the book. I just haven't gotten read it, but I remember reading a passage and it's just literally him talking to himself about his morning routine. So it's a memory. Yeah. Anything else right? One.
+Jordan: Oh, yeah. So the business card scene, that's one of my favorite scenes in the movie. One, because they all look the same. Like they're all just eggshell, different verses of eggshell with an engraving or whatever, you know, and like. Most like normal guys, usually they compare like their houses or their cars or whatever. And these guys are just comparing like business cards. I thought that was kind of funny. It was a very like subtle way of **** **** measuring, basically.
+Darius: I don't think it was subtle.
+Jordan: Well, not subtle, but it was a more unconventional way of **** measuring, as I should say.
+Darius: They there's nothing dumber than a business card. I've had the same stack of business cards for ******* 10 years now. And it's like, When would you ever, how could, it's not possible to hand one out and not look like * ****. It's just, nobody has ever looked cool handing you their business card. It's just so stupid. That's funny. It's true, man. Heading into act 2, the mask slips. Fateman's obsession with appearances intensifies as professional rivalries, consumer excess, and private impulses collide, blurring performance and reality, while his increasingly unstable perspective reshapes every relationship and encounter around him. Everyone in this movie is obsessed with status, but nobody's actually accomplishing anything or building anything. They're just talking about status. I just don't, you know, I get that like if you look at the average office worker during work it's gonna look like they're doing nothing but it's just remarkable to me that these nobody ever does anything in this movie they're just yeah existing as rich archetypes like there's nothing there's no there there you know yeah what what you got for act two.
+Jordan: Yeah that's funny you say that I because I feel like I mean the movie is a lot of making a lot of, trying to make a lot of statements about masculinity and, I think obviously I'd say white privilege as well, white male privilege in particular, of course. But I think it's also obviously clearly a lot about capitalism. And there's the scene where he walks through the homeless guy and he was like going to help him. Then he starts asking those. we hear people all the time, those bootstrap questions, why don't you just get another job? Why don't you just ask for a job? Like, whatever. And **** like, if it's just that easy for a homeless person to just get a job, it's like, okay, well, you have to have a suit for the interview. You have to have a way to get to the job. You have to be able to fill out the application. They have to give you an application. Where are you going to call the street? Correct. Right. You're going to give them 911's number. Like, you know, yeah.
+Darius: Yeah, every boomer is like, well, just showed up and asked for a job.
+Jordan: It's like, yes, and they'll give it to you.
+Darius: Although I must admit, that sounds more efficient than this. The new thing we have where there's like 90 rounds of interviews and yeah, you know, so I don't know if there's got to be something in between that. But yeah, for sure. Telling a homeless person to just go get a job is, is you don't understand how anything works.
+Jordan: No.
+Darius: Then you'd ask that like, okay, so if a homeless person walked into your office tomorrow, you handed them a W-4 form to fill out.
+Jordan: You'd call the police.
+Darius: Right. You know, like there's things, you know, I've read memoirs from homeless people and they're like, it's once you become homeless, it's a race against time before you start to look homeless. And it's like, you lose your housing and then a buddy lets you crash on his couch. or maybe even his spare bedroom. And then, he's like, all right, your time's up. And then you get a couch. And then that only lasts for so long. And then it's like, you just run out of couches. And then once you can no longer get a daily shower, it starts to wear and you can't brush your teeth and you start to build plaque up and you start to look homeless. And it's like, if you don't get out by the time you start to look homeless, it's just a dead spiral at that point. Right. And one of the misnomers is that people are homeless because they do drugs. And it's like, no, most people.
+Jordan: They do drugs because they became homeless.
+Darius: Correct. It's like, if you ever gone camping and you have to sleep outside while you're camping, most people have a drink or two to take the edge off because sleeping outside is difficult. Now imagine if that was your life. Like you had to sleep on the concrete. And not just you have to find a place to sleep. Yeah, you'd want to get high. Yeah, right.
+Jordan: Like if I was if I was homeless, I would 100% do drugs, hard drugs, like the hardest drugs possible. Yeah, it's like or even like, well, I mean, I think Patrick Bamon, of course, is a walking metaphor for capitalism. And I got like this thing where people are like, whenever if you heard someone say like when a homeless person asks them for money, they say like, oh, I'll go into the store and buy them some food so they don't use them on drugs. And it's like, well, who are you to say what they what they can and can't use that money for. You know what I mean? Like, if you're going to give it to them, then it's theirs.
+Darius: I mean, who are they to say the person who's giving the money? I mean, I don't know. Like, I really, you can't just like you can't tell.
+Jordan: I think that's very self-righteous.
+Darius: Yeah, but I mean, they could just say no.
+Jordan: Yeah, for sure. Right. See, that's my thing. It's like, I'd rather you not rather you say no, but you could just say no as opposed to you trying to finger wag someone who's in a ****** situation.
+Darius: Yeah, I hear you. No, I mean, I wouldn't do that. I would just give, I would just give the buddy, I have a homeless guy on the corner a beer every Saturday, so I get it. But I'm not also going to tell people that they're wrong for not wanting someone to spend their money on drugs.
+Jordan: I mean.
+Darius: That's a perfectly normal sentiment.
+Jordan: I mean, if you tip your server, you're spending money on drugs. But they're working. They're providing a service to you.
+Darius: Know, I don't really. Someone just straight up asks you for money. You have every right to ask, well, what are you going to spend it on? I don't know. I don't think that's, is it what I would do.
+Jordan: I just, I just think that's just really, I always felt that was in really poor taste.
+Darius: You know, when you ask someone for some bread, you can't be too picky about how they give you the bread. You know, sometimes you got to be in shape with you begging, you know, so it just kind of goes both ways. Where are his friends? Did Patrick Bateman have any actual friends in this movie? Other than hookers? Yeah.
+Jordan: Well, I was going to say that the three guys he gets drunk with and does coke with, I guess.
+Darius: I thought those are coworkers, right?
+Jordan: Oh, yeah. I mean, I guess, yeah, they were coworkers, but they were hanging out socially, you know?
+Darius: I mean, I don't.
+Jordan: Do drugs in bathrooms with my coworkers.
+Darius: Fair. But it's fine to have a amiable social relationship with your coworkers. It's even fine to go out happy hours, have drinks. They can't be your only friends. That's not healthy.
+Jordan: Yeah, that's true.
+Darius: You know, you need some sort of personal life outside of work.
+Jordan: Yeah.
+Darius: And it's definitely a giant red flag if your only friends are coworkers.
+Jordan: Yeah, always, every single time. Yeah. Those people usually the ones who snitch on you at work too. So, yeah. Heads up for people.
+Darius: I'm not one of those don't make friends at work people. We spend a lot of time there, of course, but always be cognizant of the fact that you were talking to a coworker.
+Jordan: They are the police.
+Darius: Not even that. Like they could be cool straight, but you know, you still are talking to a coworker. And so, you know, Be invited to the Christmas party. Go to the kids softball game. That's fine. But never lose sight of the fact that you're talking to a coworker.
+Jordan: Correct. Ever, ever.
+Darius: Never, ever. You can. You can be great friends with them. Never lose sight of that fact, though. What else you got for act two?
+Jordan: Yeah. So, okay. So there's that one scene where the guys are all talking at whatever bar restaurant they're at and they're talking about how. They just want a girl who's attractive because they said there are no girls with good personalities. And I love the tone deafness of that coming from 4 boring *** dudes.
+Darius: You have seven different eye creams and you think you think she's not interesting. I don't even like women with seven different ice cream ice creams. So yeah. Also, you know, There are no women with good personalities, man. Some of the greatest, best personalities, best friends I have are women, man. They're women, yeah. They're funny, they're smart. I prefer the cup, I prefer talking to women way more than talking to men. Yeah, that's not even.
+Jordan: They have way more interest. No, yeah.
+Darius: Way a way wider range of interest, man. I can't tell you how many times we'll be sitting at the bar and so it'll come up and I just, I preemptively roll my eyes because they're gonna talk. Yeah, I love sports. I really, really do. But if that's all you have to talk about, that's all you have to talk about. You know, I watch. I would say I'm in the 95th percentile of how much sports I consume. And even I get tired of it being the only subject of conversation.
+Jordan: Because there's a, you know, just Nick's guy, great dude, but good Lord, it's like a He's like Bumblebee from Transformers, you know, where he just didn't have he can't talk. He just has like those preset references.
+Darius: Yeah, it's his Mass Effect. If you ever played that video game, there's a character called Rex and he just says Shepherd, who's the main character's name? And no one's going to get that joke with me. So let's move on. What else you got?
+Jordan: Plus, I also just the irony of the guy saying that because Everywhere. I mean, if you're on Twitter, you or social media, you see if you hear girls talk all the time about how boring they find men to be or the lack of interesting things men have to say about things or think about things or, you know, girls always say like they meet dudes and they don't read a lot and **** like that, you know?
+Darius: Yeah, I mean, it just depends. I think a lot of women should keep sight of the fact that you are talking to a man like he's not going to like He's not going to be in pottery class with you, you know, like you're not, you know, we we like different things. We are different genders. And, you know, though, most men haven't read Pachinko, if that's, you know, like I read it. It's a great book. But like, I wouldn't walk up to a male friend and be like, man, you pick up Pachinko this, you know, like it's yeah, you know, you have to just like when I tell men all the time, like when they say like, I want a girl who's into sports and plays video games and likes anime. I'm like, you want to date a man. You want to date a girl. She's going to send you selfies that you're going to be like, what's this for? She's a girl. Just ******* say you look great. Oh, yeah. She's going to want to show you her nails. You're not going to give a **** but she's a girl. Just you have to be girls and guys like different things. And if you want to date the opposite sex, you're gonna have to have a little give and take there.
+Jordan: Yeah, you're gonna have to share your food occasionally at restaurants, even though you don't give a **** what she ordered.
+Darius: Yeah, you know, you just, you know, you're gonna have to wake up on a Saturday morning when you don't feel like it hit that farmer's market. If you want, if you like women, you're gonna have to do girly **** that you don't feel like.
+Jordan: You're gonna have to spend 2 hours at Target on a Saturday.
+Darius: Yeah, man.
+Jordan: We're gonna go to Target tomorrow. At some store on a Saturday.
+Darius: You hear dudes talk, it's like, man, you sound like you want to date a man. It's like, her Instagram is all selfish. She's a ******* girl. What are you?
+Jordan: Yeah. Or they'll be like, she got feelings and ****. Yeah, it's like, you
+Darius: expect her to be **** *******?
+Jordan: Hopefully.
+Darius: Yeah, it's fair enough. What else you got for act 2?
+Jordan: Way upfield. Yeah, that I know everybody has different flavors and things like that whenever their routine is for like dating a girl, seducing a woman, whatever. But like throwing on some Phil Collins to have a threesome hookers is ******* diabolical. I love Phil Collins, but that's insane.
+Darius: I'll never forget the time. Speaking of like, you know, girls like girl stuff, I'm not going to use his name because it's a bit of I mean, he would take the joke when I leave him out of it. But me and my boy, we were out in Minnesota and we had we met these girls just, you know, chopping it up and, you know, he's like, I'm going to go to the bar. I'm going to get us some shots. And this dude came back with four shots of real whiskey. And I was like, let me put a bug in here. Limit drops, green tea, coffee bombs, espresso martinis, redheaded slug.
+Jordan: Like, you know, you brought these golden, purple Gatorade, whatever.
+Darius: You brought a hot *** rail whiskey. He was like, what is on sale? I was like, man, let me, let me, let me holla at you. We'll be right back, ladies.
+Jordan: I'd be like, no, they ****** ** the order.
+Darius: This is not what he meant to say. Take those back, pay for them because you ordered them and get them something fruity. Yeah.
+Jordan: Something with a garnish on it, you know.
+Darius: You know, these, these, these pretty *** women who are giving us their time do not want to shoot hot. Yeah, not even ice in it. Just real whiskey in a hot *** class.
+Jordan: That's nuts. Or like, yeah, give them like a what's called like a buttery ******. Those are pretty good. Or a rumchata.
+Darius: Lemon Drive ain't never been gone wrong. Yeah. Cinnamon Toast Crunch. Vodka bomb.
+Jordan: Any sort of like bomb.
+Darius: And it's not going to be good. It's not what we drink. I get that, but it's not for us. Yes. Yeah, it's for the hoes, man. Oh, so I managed to start with the lead his name out of it, so that's good.
+Jordan: Yeah. Okay. Speaking of that, what else?
+Darius: I go ahead. Sorry.
+Jordan: I ran into dirty feet guy last weekend.
+Darius: Dirty feet. Oh, yeah, yeah. I don't want to have to spend time editing this section. So let's move that conversation off camera. man. All right. Let's go to act three. We're stalling. Act 3, reality unravels. As consequences seem to close in, Bateman searches for certainty and recognition, but contradictions multiply, identities blur, and the polished world around him resists offering clear answers or meaningful accountability. Only one observation question for this section. I'm confused and I didn't want to Google it because I'd want to see if you have the answer and you know. Did he kill these people or not?
+Jordan: Okay. I don't really know. I don't think he did.
+Darius: Okay.
+Jordan: Because the dude said he hung out with Paul Allen. So I'm going to assume he did not kill Paul Allen. In fact, he didn't kill Paul Allen. And remember, he went there and the apartment was clean and being sold. That kind of leads me to believe he didn't kill anybody. I think. Remember when he's the assistant was in his in his office and she read that she found the journal
+Darius: yeah there were all drawings of the killings that he did
+Jordan: right yeah so yeah I think so for me I think usually most people draw or doodle and they're like fantasies and **** like that or or you you're repressing something if he had been killing these people he wouldn't have been repressed so I think that was what he was thinking about I don't think he actually did those things. Also, I just think like, if you're running around a limo, you have your driver and these women are like not returning ever.
+Darius: Yeah.
+Jordan: You know.
+Darius: That I just assume was a plot hole. Like why is this driver an accomplice to murder? But it would make sense if he hallucinated the whole thing. Now that you've explained it, I kind of think it's almost obvious that he, I wouldn't say almost obvious, but
+Jordan: Yeah, it was pretty ambiguous ending, but I don't think he killed anybody.
+Darius: Yeah, I'm with you. Now that you've explained it, that makes the most sense to me, is that he hallucinated the whole thing. And you know, he might even be Paul Allen and Patrick Bateman.
+Jordan: That's kind of what I think,
+Darius: to be honest with someone else. So I mean, yeah, I agree.
+Jordan: Because they kept the one guy was like, Bateman's a dork. He would never, you know, and I don't know. He just, he kept like, people kept calling him different names, but nobody ever called anybody else different names. So it was, I don't know. I think he, I think it was something similar to Fight Club, but not all the way. And this came out, this book was written before Fight Club, but I think it was something in that kind of ballpark, to be honest. I don't think he actually killed anybody.
+Darius: Fair enough. I would tend to agree with that. was not where I was leaning, but you explained it in a way that makes sense to me. So I agree.
+Jordan: I think, yeah, I think he is essentially capitalism slash America. And, you know, the murder shows showed what he did. You know, capitalism does harm women. It does harm homeless people. It does harm poor people. You know, it harms people who benefit from capitalism, you know, and patriarchy also. But I just I don't think like even the thing that made me think it wasn't real was when he was at the ATM machine. And it said, like, feed me the cat.
+Darius: Yeah.
+Jordan: You know, that for me, it was like, that's okay, your capitalism, your America, you know, your your patriarchy, your your white male privilege, things of that nature. That's what I mean. That's that was a giveaway to me that he didn't really actually hurt anybody.
+Darius: I tend to agree. What else you got for that rhymed bars.
+Jordan: Like even like the ending, I love the ending monologue where he says, I do not want better. I don't want a better world for anyone. You know, he kind of it was very like droll and very downtrodden. I thought that was a great way to end the story because he doesn't really talk a lot. A lot of his talking in the movie is just the voiceovers or the fantasy or whatever the case may be. Like there's a scene where he says, I work in murders and executions, but he really said mergers and acquisitions. That's what it was acquisitions. Yeah. You know, I think That was like the first time he was actually honest in the movie. I thought that was a pretty cool way to end it. So I wanted to ask you, so there's this thing I saw on Twitter where it's like, they're called like quote unquote unofficial trilogies, where they're movies that are not actually trilogies, they're not related to each other, but they just kind of have similar tones and themes. So I think this movie is kind of one of those situations where it's like this, I'd say this, Wolf of Wall Street and Fight Club are kind of like an unofficial trilogy where they're all about greed and excess and they're all kind of the same archetype of dude and just shows them like raveling into self-destruction because of their boredom or greed or insatiable appetite for sex, **** addiction, whatever, things like that. What do you think?
+Darius: I think Wolf of Wall Street is a bit of a stretch, but I definitely see Fight Club and American Psycho as like cousins. I had a question that I scrapped, which was like, what is your favorite movie or novel with an unreliable narrator and Fight Club was on there. So I guess in a way that kind of answers the question for me where it's kind of they're twins or not twins, they're cousins. So yeah, for sure.
+Jordan: Definitely.
+Darius: Especially when you get to the ending that we now believe is similar and that he hallucinated most of this. So yeah, I think so too.
+Jordan: You made a great point where you said like, the 90s men who worked in offices were kind of the probably the first generation of middle class guys to have office jobs. And I think you're right, because they would have been born in 70s, probably, 60s, maybe. So the dads would have been born in the 40s, sex, you know, would have been down to kind of like, right. Or like, essentially, like Don Draper, like they could have been his sons, essentially, you know what I mean? Like he had the he was the big exec who was the outlier. And in theory, his generation of dudes would have had the kids who would have had the easy life.
+Darius: We'll see. Yeah, but I don't really count. I thought about adjusting it. That's why when I brought it up, I made the caveat middle class because Don Draper and his cohorts were like filthy rich and so filthy rich man had office jobs back then. But I think and again, I could be totally wrong fact check it later, but maybe like the men of the 90s were t</t>
+  </si>
 </sst>
 </file>
 
@@ -7695,7 +8063,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7720,7 +8088,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7737,6 +8104,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8056,7 +8427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -8813,7 +9184,7 @@
       <c r="E38" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" t="s">
         <v>159</v>
       </c>
     </row>
@@ -8849,6 +9220,40 @@
       </c>
       <c r="E40" s="9" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="4">
+        <v>2023</v>
+      </c>
+      <c r="C41" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="D41" s="8">
+        <v>3</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="4">
+        <v>2000</v>
+      </c>
+      <c r="C42" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="D42" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -8863,7 +9268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -9187,6 +9592,22 @@
         <v>157</v>
       </c>
     </row>
+    <row r="41" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>160</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498EC633-9F79-4032-8D87-A995AF3D650A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDD8EA4-1F80-4399-9E2C-06BAB9542DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="167">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7991,6 +7991,9 @@
 Jordan: You made a great point where you said like, the 90s men who worked in offices were kind of the probably the first generation of middle class guys to have office jobs. And I think you're right, because they would have been born in 70s, probably, 60s, maybe. So the dads would have been born in the 40s, sex, you know, would have been down to kind of like, right. Or like, essentially, like Don Draper, like they could have been his sons, essentially, you know what I mean? Like he had the he was the big exec who was the outlier. And in theory, his generation of dudes would have had the kids who would have had the easy life.
 Darius: We'll see. Yeah, but I don't really count. I thought about adjusting it. That's why when I brought it up, I made the caveat middle class because Don Draper and his cohorts were like filthy rich and so filthy rich man had office jobs back then. But I think and again, I could be totally wrong fact check it later, but maybe like the men of the 90s were t</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=VFWgJRJO-rc&amp;t=1s</t>
+  </si>
 </sst>
 </file>
 
@@ -8063,7 +8066,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8088,6 +8091,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8104,10 +8108,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9204,6 +9204,9 @@
       <c r="E39" s="9" t="s">
         <v>153</v>
       </c>
+      <c r="F39" s="10" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDD8EA4-1F80-4399-9E2C-06BAB9542DD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECE6132-7E91-4BAF-8193-9766ACFCC75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="170">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -7994,6 +7994,213 @@
   <si>
     <t>https://www.youtube.com/watch?v=VFWgJRJO-rc&amp;t=1s</t>
   </si>
+  <si>
+    <t>Tales From The Hood</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: Rogue Cop Revelation | Act 2: Boys Do Get Bruised | Act 3: KKK Comeuppance | Act 4: Hard-Core Convert &amp;amp; The Mortuary Twist&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius break down the 1995 cult classic Tales from the Hood, examining its four morality tales, dark humor, biting social commentary on systemic oppression and abuse, and whether its supernatural revenge fantasies still resonate today.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1 covers the Rodney King-inspired police brutality segment, examining rookie cop Clarence&amp;#39;s bystander guilt, the &amp;quot;Blue Wall of Silence,&amp;quot; and Darius and Jordan&amp;#39;s debate over whether freezing in the moment equates to lifelong complicity.&lt;/li&gt;
+    &lt;li&gt;Act 2 explores Walter&amp;#39;s drawings, mandatory reporting challenges in schools, David Alan Grier&amp;#39;s dramatic against-type performance, and how children weaponize imagination to cope with domestic terror.&lt;/li&gt;
+    &lt;li&gt;Act 3 shifts to the David Duke-inspired storyline, analyzing plantation politics, the symbolism of the American flag as a weapon of suppression, and why marginalized groups often look to supernatural folklore for justice.&lt;/li&gt;
+    &lt;li&gt;Act 4 tackles Crazy K&amp;#39;s rehabilitation, the double standards of street violence, the shocking revelation that the funeral home is Hell itself, and final episode scores.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Do we rely on supernatural retribution stories because it makes us feel better about the fact that most oppressors and abusers in real life just get away with it?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Horror is at its strongest when it subverts the expectation that Black characters must always take the high road; Tales from the Hood refuses to offer easy moral compromises, instead granting poetic, visceral justice to the aggrieved.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; In high-stakes moments of violence, people routinely overestimate their own heroism, but when survival gives way to silence afterward, failing to speak up transforms an eyewitness into an accomplice.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; The culpability of the bystander—is a rookie officer who freezes during a heinous crime just as morally and legally accountable as the perpetrators if he stays silent after the dust settles?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Police brutality and institutional corruption&lt;/li&gt;
+      &lt;li&gt;Bystander complicity versus immediate self-preservation&lt;/li&gt;
+      &lt;li&gt;The &amp;quot;Blue Wall of Silence&amp;quot;&lt;/li&gt;
+      &lt;li&gt;Domestic violence and child trauma&lt;/li&gt;
+      &lt;li&gt;Childhood imagination as psychological armor&lt;/li&gt;
+      &lt;li&gt;Systemic racism and political exploitation&lt;/li&gt;
+      &lt;li&gt;Plantation iconography and historical memory&lt;/li&gt;
+      &lt;li&gt;Patriotism redefined (&amp;quot;love it, so change it&amp;quot;)&lt;/li&gt;
+      &lt;li&gt;Supernatural retribution versus real-world impunity&lt;/li&gt;
+      &lt;li&gt;Community violence and accountability without anti-Black bias&lt;/li&gt;
+      &lt;li&gt;The horror anthology as moral allegory&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome back to Out the Trunk with Jordan and Darius. I'm Jordan, that's Jordan to be writing on all socials.
+Darius: And I'm Darius, that's Deez, I love the area on all socials.
+Jordan: And today we're gonna be reviewing Tales from the Hood, who came out in 1995. Tossing it to you for act one.
+Darius: All right, act one, we're gonna do something a little different this time. This movie is about like 4 short stories in one. So we're gonna do 4 acts. Each act is gonna be a different short story. So act one, Road cop revelation, corrupt white police officers murder a clean activist black councilman after he catches them dealing drugs, while rookie black cop Clarence stands by and does nothing. A year later, Clarence quits the force and watches in horror as the councilman's vengeful zombie rises from the grave, brutally kills the three corrupt cops, and drives Clarence into an asylum. Also, this is a spoiler review. So off the rip, fun fact about Darius, this is the third movie I ever saw in a movie theater. Oh, wow. We lived in Mississippi. And that I was spending the summer visiting, my sister and I were spending the summer visiting relatives in Minnesota. And we saw three movies that summer. We saw Friday, we saw Money Talks, and we saw Tales from the Hood. Did I have any business seen that at age 7? No.
+Jordan: None of that ****.
+Darius: But that's what kids did in the summer in the 90s. They went and saw movies they had no business seeing. Correct. Special place in my heart for this one. So what you got for that one?
+Jordan: Man, so one I love, I like, so I'm not a big horror movie like aficionado generally. I've gotten into horror the last couple of years. And what I really love about the genre is the way that it uses, the way that it spins themes and political statements and things like that on its head. I think that's really dope and the symbolism is always really cool. That's what I've really come to appreciate about these movies. But I just want to say that black cop was dumb as **** because what the hell did you think they were going to do when they told you to walk away and put his **** in the system? Also, like you couldn't hear them beating the **** out of him.
+Darius: Not sure the order of release, but in a previous segment we talked about like how you people overestimate how they're going to react in stressful situations. He's A rookie cop. It's probably his first.
+Jordan: I get it.
+Darius: Couple of years on the beat. I'm going to shoot him some bail on that one. Now he made now when they say, hey, we're going to take him to the hospital and he winds up dead in the river.
+Jordan: Come on, man.
+Darius: Come on, man. Come on, dog. I loved everyone thinks they would, be Captain America and break out the shield and smack people. I just think it's harder than it looks. It's kind of where I am. I'm not saying he's right. I'm saying it's harder than it looks.
+Jordan: I hear you. Well, see, I'm not even necessarily saying that he, I mean, do I like to think that I would have tried to stop it? Yes. Do I know that I would in that moment? I don't know. But I'm more so just like, you just really didn't know what they were going to do. Like, it's like, you know, it's okay, like Dark Knight, where he's like, when Harvey Dent was in Two Faces, he chased down all the cops that kind of had a hand in Rachel dying. And he's like, they're like, oh, I didn't know what they were going to do. He's like, okay, what exactly did you think they were going to do? You know, that's my main question to him.
+Darius: I mean, is in the 90s, I mean, this story was probably the 80s.
+Jordan: Yeah.
+Darius: And so it's based on the Rodney King beating, but which isn't a nice, but so you get, you know, government jobs police jobs are like one of the few tickets black people had to the middle class back then right so you get the job thinking you know it's a good job make a difference the money it can make a difference and then like obviously they didn't want him there right you know it just if they could have their druthers he wouldn't have been involved with it either and you just walk up on the worst thing you could do as a rookie cop it's tough but I did want to say Movie in general, this is one of the flashbacks, but the main story of the movie is 3 drug dealers go to a funeral home and the funeral home director discovered some drugs and they're trying to get the drugs for cheap, so on and so forth. It's really hard to overstate how violent the 90s were because none of these movies were all that unrealistic.
+Jordan: No, like not at all. Like none of it felt like, oh, that's cartoonish or anything. Like it all felt like, yeah, that's what would happen.
+Darius: It was like, people don't understand if you watch commercial, there was a whole commercial campaign about putting a crowbar on your steering wheel, because that's how often cars got stolen. Right. We used to get out of our cars, and this was late 90s, early 2000s, and remove our radios because you just didn't want anyone to bust your windows and take your radio out your car, because that was entirely possible.
+Jordan: I think somebody actually did steal one of my parents' radios out of the car one time. I think that did actually happen if I remember correct.
+Darius: But yeah. I had so many bikes stolen when I was a kid. My parents just stopped buying them. It was like, damn. Now I can just, when I go for a run, I just see kids' bikes laying around the neighborhood because like it's a safe neighborhood and no one's gonna steal your bike. That's not how it used to be. You had to have a lock with your bike and you had to lock it onto things because people just stole bikes.
+Jordan: Yeah.
+Darius: That's just what they did. And we're not, that's not even violent stuff. That's just regular crime. And it's just, we saw a little uptick in crime after COVID and the crime is bad and we should always push back on crime, but it cannot be overstated how much, how much worse things were in the 80s and 90s. Right.
+Jordan: Yeah.
+Darius: What else you got, Frank?
+Jordan: And it's a testament to how far we've come to, because like I remember I rode my bike to high school, freshman year of high school, because I just didn't feel like doing the bus. And I was like, I can wake up, ride 10 minutes, and save up some sleep or whatever. I remember the first day of school, I could not find the bike lock. Usually they're in the front, but it was like in the back. I had never been to school before. So I'm like, ****. So I just like left my bike in the bushes for the whole day. And I came back out and I was like, the whole day I was like, please God let my bike still be there.
+Darius: And it was like, you know, we got to the point where because the bike lock, you would put it on your front tire and lock it to the thing. We started locking our frame to it because we heard someone they just took the tire off and took the front. So we started. Now, I don't know if that actually happened, but we heard it happen. And that was enough. And we started locking our frame to the thing because we heard that the wood actually took it off the tire off. And so, yeah, I had so many bikes stolen. My parents just stopped buying new bikes.
+Jordan: It was crazy.
+Darius: At least for a year. They're like, you're not getting a new bike this year. You have too many. Like, it's my fault.
+Jordan: Get you a skateboard. Nicks can't do that. It's a long year.
+Darius: But yes, this story was loosely based on the Rodney King beating. So they beat the man up within an inch of his life. And to top it off, they objected him with something in a very 90s way. He would never pass any sort of investigation.
+Jordan: So the dude who never had done heroin, there's no needle marks on his arms. You check his system, obviously, the toxicology report. And then he just had two bricks in the mask.
+Darius: And he shoots himself with heroin and then puts it in his front pocket.
+Jordan: Right, because that's where they'll never find it. And then he crashes to the rivers.
+Darius: Also just like no one heard the beating. No one's like it was in a neighborhood and they were beating the **** out of him. And yeah. How do you explain the broken window in his car? You would head through the window. There'd be blood everywhere. It's a movie.
+Jordan: Yeah. That was my also my thing, too, because it's like, I've never done drugs or heroin or anything like that, you know, but like the idea that someone would do heroin, crash their car, and then fly off into the river. It just seems like there's like, that's like 4 murders in one. You know what I mean?
+Darius: You know, it's movie magic that would not pass. A rookie investigator would show up and be like, this story does not make sense.
+Jordan: Only an idiot would believe that.
+Darius: It's the 90s.
+Jordan: Yeah, true.
+Darius: You got any questions for Act Boy? Because I just have one.
+Jordan: Well, for one, so everybody's in this movie. Like everybody who kind of, like a lot of like young black stars were in this movie. Stacy from The wood you had, I think that his partner who in Boys in the Hood or in the wood was his man's in this one too. The bald guy. I think that was that the same dude.
+Darius: No.
+Jordan: So it was like crime when the cop pulled up.
+Darius: No, it's a different dude. So that dude is a minister society to do Kane stomped out.
+Jordan: Okay. Yeah.
+Darius: That's him. He recently passed. RIP.
+Jordan: Oh, man. I didn't know that.
+Darius: Joe Tory.
+Jordan: Yeah. Tory. Yeah.
+Darius: David Alan Greer, later on.
+Jordan: Came from Soul Food.
+Darius: Came from Soul Food. The white cop who was super duper, like cartoonishly evil, who was decapitated, he's known for something. I just don't remember what. I'll look it up. You can fill a buster.
+Jordan: The racist white guy, the racist politician in the last one, or the second to last one, he plays Sean's dad in Psych.
+Darius: Yeah. So it was.
+Jordan: Yeah.
+Darius: This is a sneaky launchpad.
+Jordan: Yeah, it really was. Okay. I came from Oisha was in it in the fourth. In the fourth one. The older lady with the lock, she looked really familiar, but I just can't place her. I can't place her anywhere in any sort of movie in particular. I'm sorry. First I thought she was Toni Morrison.
+Darius: I think Morrison with that got dead in this ********. Let me ask you this. One of my favorite lines is, so Clarence is reincarnated. He's a zombie. He kills everybody. And it gets to the end and he's talking to, well, Clarence was the cop, but the black guy was the counselman. Yeah, he's just like, are you satisfied now, brother? And he's like, where were you when I needed you, brother? When someone witnesses wrongdoing and doesn't come forward, do you consider them just as culpable?
+Jordan: I mean, that's what my parents said when we were growing up.
+Darius: Fair enough.
+Jordan: I mean, so I mean, it's hard to say because there is a difference between doing something and watching it.
+Darius: Yeah, I have one here by definition, they're not just as culpable, but there is something there, right? there's a reason why in the law, If you're the getaway driver for a bank robber, you can't just, you don't just get ticketed for speeding.
+Jordan: No, right, You were there for the planning, obviously.
+Darius: You were part of it. You didn't go in, but you were getting charged with a bank robbery.
+Jordan: Yeah, you were complicit. Then was it involvement? No, but I mean.
+Darius: That's why people don't understand in a lot of states, it's not all of them, but like according to like the actual statute of murder laws, If you agree to do one crime, you're agreeing to them all. So let's just say you are the gateway driver in that bank robbery and one of the people inside just killed somebody. You're on the hook for that murder, even though you didn't agree to do a murder. You were just like, we're just robbing this bank. Let's get our money. Let's go home. But if something goes on in there and they and someone dies, that's your *** that you're on the books for that murder.
+Jordan: Like, yeah, like think about it. If you host a party and something happens at that party, you're that's you. Like, that's you. You're going to get some culpability for that.
+Darius: It just depends. But if you don't agree to one crime unless you're willing to take them all, because it's people on death row who are like, dude, I just, I knew we were going to rob the liquor store, but the plan was not to kill anyone. And then they killed the clerk and now we all on death row for murder. And all I did was drive there and drive home.
+Jordan: Yeah, that's kind of how I judge it. Like if worst case scenario, all hell breaks loose and something horrific happens. Would you be on the hook for that? And if so, then maybe don't do that thing or be there for that event.
+Darius: I will shoot him some bail in the sense that like, he's not going to be Captain America in the moment.
+Jordan: Right.
+Darius: But to just quit the force and let them besmirch this man's name and not come forward with anything. And just, I just, you got to be.
+Jordan: You could have called in. Yeah, because you could have called in a tip and anonymous tip. There were things that you could have done.
+Darius: You are an eyewitness.
+Jordan: To at the very least, police brutality, at the very least.
+Darius: A murder. Well, he didn't have witnessed a murder, but you get it. You have material evidence.
+Jordan: Right.
+Darius: You know, it's just sometimes hard things are hard. You just got to do the hard thing. I'm sorry.
+Jordan: Yeah.
+Darius: I can't style you out for that. I can style you out for it in the moment. I can't style you out for letting them.
+Jordan: It's really the after the fact stuff. I think, honestly, like you just wait, you become a drunk, like, I don't know. I mean, I'm not saying in real life, you should do this in the scope of the movie. Revenge is a big factor here. Maybe hunt them down, at least.
+Darius: It's just, you get home, you sleep on it, you wake up the next day, you find out he's dead. You got it, you got to say something. You just can't.
+Jordan: Right.
+Darius: You know.
+Jordan: And also the cops were still so stupid. They put on gloves after they had done everything you could possibly do except for spit on the guy in terms of like leaving DNA, you know.
+Darius: My guess is they just didn't expect him to be, which they're right, much of an investigation.
+Jordan: True, which speaks to the privilege. And I will say I did like that they did a reference to Blue Wall of Silence, where when he's in the car with the cop and he's like, hey, don't go against the badge. We're all in this together. Don't say anything. He's basically trying to say, because it will **** ** your career. And I've had, I have, obviously I know somebody who's an officer, but I had a friend whose dad was in the police force and she's told me stories like he would report **** and he would try to say, hey, this cop did this or is doing these things. something is going wrong here. And his career suffered because of it. They were roadblocks in front of him, And then-
+Darius: That's any job though, right? obviously, the stakes are higher than the police, but nobody in any job likes the person who goes and tells management what's going on. Obviously, the stakes to the police are just way higher.
+Jordan: Correct. But even like you saw the **** in Charlotte that just broke a couple of days ago?
+Darius: I have not. I saw it break. I'm not well versed on it, so I can't really speak on it.
+Jordan: Okay, cool. We'll wait.
+Darius: I've been seeing past the headlines. So yeah, no, I mean, yeah, you got to say something in that in that situation. So yeah, yeah. Anything else for this one?
+Jordan: I did like that because a lot of times in black movies when there's when race is a fact is a character in the story, they always try to subliminally tell us to take the high road and be the bigger man. And I like that this movie didn't do that.
+Darius: No, he hunted him down.
+Jordan: Yeah.
+Darius: I'm the one on the cross.
+Jordan: Yeah.
+Darius: That was, that was, yeah. He got his revenge and the dude ended up in an asylum forever. They didn't actually explain how he died, but you know, the movie. done movie, but a movie nonetheless.
+Jordan: So yeah, true.
+Darius: Heading into act 2, story 2, if you will, boys do get bruised. A sensitive young boy named Walter insists to his teacher that a monstrous creature attacks him and his mother at home every night. When the teacher visits their apartment to investigate, he discovers the monster is actually the mother's violently abusive boyfriend who savagely beats the teacher before Walter uses a drawing ritual to fold and burn the abusive man alive. David Alan Greer. one of the underrated black actors of our time. He's a character actor. He never really got his like star vehicle, but to this day he's still working, still on stage, 70 something years old. And you know, he's one of our icons. So just wanted to give him a little quick shout out here because this is a role way outside of his normal scope. Normally he's a bit funnier, a bit lighter, but his range is incredible and shout out to him.
+Jordan: Yeah, he's one of the he's the definition of literally, like, if your goal is to be a working actor, he's someone you should look into or his career you should study for sure.
+Darius: Looked him busy for 40 years.
+Jordan: So literally got to respect it. So obviously this one has the kid from Soul Food in it. I think the my first takeaway slash question is When he tells the teacher what happens at home and he tells him like, when his dad hit you, he says, my dad's dead, and then he says, there's a monster attacking me. I don't understand the concept of telling a child you don't believe what they're saying. I think that's one of the most dangerous things a teacher in particular could ever do.
+Darius: I agree. But so I mean,
+Jordan: You at least got to placate to get more information for sure.
+Darius: Well, I mean, it's tough because kids have imaginations and he didn't say his mom had a boyfriend. And so look, I think there's a little bit of what's called hindsight bias. Like we know what happened. So we're judging how we would have reacted, but we didn't have the information that he had at the time. And so he did. In short order, go check it out. one bruise can be a kid, climbing a tree, fell down, hurt himself. Oh, a monster did it. Kids have imaginations. Okay. It also, you have to be a bit discerning with these things when you're a mandated reporter. He didn't say, my mom's boyfriend is hitting me. He said a monster did it. And, you know, okay, once I keep my eye, he kept his eye on them. Weird. Keep his eye on him. Bring him to the nurse. You can still you could sense the skepticism second time. All right, let's play the home a visit. I don't think. Yeah, I'm not going to come. Obviously, you'd like him to go on the first visit, but, you know. Right. It's kind of like when people get mad that like a loved one, like true crime, someone will go missing for real and then people will get mad at the police, like, wait 48 hours to do a missing persons report. And it's like, do you know how many times someone calls the police saying their spouse didn't come home and they was out with someone they had no business being with? It's like, if the police mobilize every time, some husband or wife didn't come home when they were supposed to, they'd never get any work done. So you have to have, and it looks bad when it actually is the missing thing. But you didn't see the thousands of times when the husband was just in a motel with his mistress, Right. so you have to kind of weigh the, weigh the, you have limited resources. he went in on his off, it's like he can go during school day, he has to get off work, go over there. And so he didn't, he jumped at the second one, not the first one. I'm not going to get down on him too hard about that. So.
+Jordan: Okay.
+Darius: But schools are usually the first line of defense against abuse at home because that's why it's a lot of these schools have strict attendance policies because one of the first signs that something's wrong at home is absences. That's what I was saying to school. My parents couldn't wait to get me to school so they can go about their visit. It was an 8 hour babysitter, baby.
+Jordan: Correct. Yeah. Usually it's because they, can't literally cannot be seen at school because of what they look like physically.
+Darius: Why are you trying to avoid mandatory reporters? You know, it's like.
+Jordan: Right, exactly.
+Darius: So. But tell us you got fract too.
+Jordan: Yeah. Okay, so there's a scene where the climax scene where it's revealed that the boyfriend is actually the monster that the kid was drawing. He starts beating the mom, beating the kid. And It just felt like the teacher took forever to notice what the hell was happening. Everyone's screaming in the house. There's no way you can't hear that outside.
+Darius: Where were the, I mean, if he was beating him like, well, maybe this night was just bad because he.
+Jordan: Bad.
+Darius: Yeah.
+Jordan: But the neighbors, yeah, for sure. You wonder, makes you wonder.
+Darius: It's tough, man. At first I thought, because I hadn't seen the movie in a while, and I just remember thinking.
+Jordan: I'd actually never seen it.
+Darius: Really? Yeah, I'd never seen it before. I just remember thinking that the monster was his his bomb's boyfriend drunk and like, yeah, it was like a right. But he just clearly.
+Jordan: Oh, okay. Gotcha. Like a doctor. Mr. Hyde.
+Darius: Yeah. Like he just he never once mentioned boyfriend. He just said, you know, the monster. And so I did like the sort of the way they I like when movies or TV shows sort of use a child's imagination to explain a real world event, like the same lot with the dog. I don't want to say it's cool because it's obviously about a very serious thing, but it was creative, if you will.
+Jordan: Yeah, it was a good window into how kids view things and how kids view adults, A man may not be scared to us, but to a child, it's Godzilla. It's like we said earlier, we're aliens to an ant. So, and then also the kid doesn't view him as a human because he's harming him and his mother. So in his mind, that is a literal, he is literally a monster.
+Darius: And it's also a way to compartmentalize, right? Like this is some supernatural thing happening and not just like the guy that, you know, the mom's boyfriend beat the **** out of me.
+Jordan: Right.
+Darius: Yeah, that's just that was a rough one.
+Jordan: But it was it was.
+Darius: Long and the short of it is that they triumph though, so they did. Anything else rag too?
+Jordan: Okay, so I did think Hearst trying to seduce the teacher was a little odd considering the circumstances of like this dude's coming home in a minute. You know his schedule probably I'm assuming he comes home the same time every night. He's beating the hell out of you and you're going to try to **** another dude which kid in that like I don't know I thought that was kind of odd. I didn't really get that.
+Darius: It felt very 90s lack of editing. I'm sure the budget for this movie was not great. Some of the ZGI was pretty solid.
+Jordan: Yeah, considering, yeah.
+Darius: That's just one of those things that probably slipped through the cracks. I get the director had to get any just to rewrite that scene. Yeah, because it doesn't make anything else.
+Jordan: It didn't make any sense. It wouldn't align with. I don't even think it would align with what. she would have really done that situation, to be honest.
+Darius: Given how violent he is, I'm surprised she let him in at all. Given how violent actually his character was.
+Jordan: Correct. Yeah.
+Darius: But maybe I mean, I'm, you know, projecting a bit here, but I doubt he lets her leave the house much at all. And so, yeah, that was probably her one chance to get someone in to see how bad it was. Because true.
+Jordan: Yeah. because I think just based on the way Alan Greer's character was, David Alan Greer's character was dressed, he probably made good money. I'm going to assume he probably wanted her to stop working so he could control her further, cycle of use, all that sort of stuff. So she probably, yeah, you're probably right.
+Darius: Yeah, that's, especially back then with the lack of communicate. There's no cell phones. There's no social media. A lot of abused women were very isolated. Like, you know, that's probably the only she probably doesn't get to leave. Well, it's fictional, but I doubt she got to leave the house very much. So correct. I don't really I had a I don't really have a good question for this section.
+Jordan: Yeah, this is pretty straightforward. There's not a lot of.
+Darius: You know, it's listen, you know, Kids are often explaining things without knowing that they're explaining it. And so, listen to them. Heading into Act 3 with the KKK comeuppance, creative title, a racist former Ku Klux Klan grand wizard running for state governor sets up his campaign headquarters inside an antebellum plantation mansion once inhabited by murdered slaves. He ignores local folklore about vengeful spirits trapped aside decorative dolls, leading the tiny wooden dolls to come alive and rip him to pieces in a bloody, agonizing massacre. This was loosely, not even loosely, is basically based on David Duke, literally a former KKK member who ran for government of Louisiana and was paralyzed. I just wanted to note that of like Bush 41, so he ran in 1991 and Bush 41 Herbert Walker Bush like came out like the sitting Republican governor or state president of the United States came out against him and said, you know, this is not, you know, Republicanism. So different Republican Party than today.
+Jordan: Yeah, very different. There are no good Republicans today.
+Darius: What you got for this one, this story?
+Jordan: I thought it was kind of spot on. in terms of the way things have aged changed nowadays, where it was a controversy that a racist politician was like residing on a plantation. And now like celebrities just get married on plant white celebrities get married on plantations.
+Darius: I, you know, I think they did that back then too.
+Jordan: I mean, well, yeah, I'm sure. Yeah, for sure.
+Darius: It's just so insane.
+Jordan: You would never say you can't.
+Darius: Really discuss it in the micro level, right? you have to expand out because you see it often in racist hiring practices. And the owner of the business will go, well, just find me the person and I'll tell you why we didn't hire them. And it's like, if you look at any individual hiring decision, you can come up with a reason it's not racist why you didn't hire a black guy. Because that's easy. There's reason or that reason. But if you have to jump back and go, okay, but in 10 years, you've never hired once. Something's going on here. Yes, correct.
+Jordan: Like how have the Dallas Cowboys never had a black head coach? Like, you know what I mean?
+Darius: It's just like, yes, if you look at every, it's almost like a card trick when they try to make you think about it at very, very narrow ways. Correct.
+Jordan: It's like, because they're so good at it. You'll be like, damn, you know what? And you're like, wait, hold the **** **.
+Darius: It's just like, yes, if you pull up the rap sheets of every single person in Angola, I would be like, that person belongs to prison, that person belongs to prison, that person belongs to prison. But you scan it back out and you're like, Okay, but it's built on a plantation and the vast majority of its occupants are black.
+Jordan: Yeah, that's not.
+Darius: Something's going on here. You know, you have to do it that way. So I didn't really, I thought the story was kind of wack. All the four was my least favorite. There's just no complexity to it. Like they literally just run that black guy and kill him. Yeah. So I have a cool question to end it, but what you got for act three or story three?
+Jordan: Story 3. So I did like that. The one thing to the creepy, the obviously the red flag was him being living on the plantation. The other part was him having to leave the essentially a deer's head on the wall, which is the painting of the black slaves that were, you know, killed and slaughtered. I did like that he tried to, he kept trying to use the flag to kill them. He kept using the flag to try to stab the painting. He kept trying to use the flag to smother them, you know, which that's what I always, you know, There's the dichotomy between our views, white people's views on patriotism and black people's views on patriotism. By and large, a lot, I hear, I'll say, not all, but I hear a lot of white people say, like, if you don't like to hear, leave, go back to Africa. That's what they're trying to say, right? Whereas, you know, you love your wife. So because you love your wife, you tell her, hey, this behavior that you're doing, you're better that you can correct that. for the sake of our relationship. And a wife would tell her husband the same thing. it's like Max Hellman said, he said, it's not, it shouldn't be America, love it or leave it. should be America, love it, so change it. And I think that's how black people feel about this country. And I think that people use the flag to try to smother us in a way, you know, like, oh, no, you took a knee, that's disrespectful. So you're destroying our unity when they really just make peace and quiet, or quiet for them, rather. So yeah, I love the symbolism there with what they did with the flag.
+Darius: That was pretty dope. Yeah, he's just in the other three, four stories, there's just like at least one complex character, a little bit lost here and there.
+Jordan: Yeah.
+Darius: He's just like a cartoonist racist.
+Jordan: It's just a lot of tropes. Yeah.
+Darius: He's like, he walks out and he's like, Because he's talking to his advisor, black advisor, and he calls people spooks. And then he walks out and he's like, at least I had to deal with spooky journalists like you. Yeah, spooky. Right. Stupid.
+Jordan: Yeah, it makes me think of there's that this TikTok went viral. And it's something like, young white men's sense of humor is just like racism. Where it's like, and there's this TikTok and this guy was like, all the white boys you went to high school with and it was like them being like, that's what this particular story felt like. It just felt like him wanting to tell them how badly he viewed them as nothing. When in real life, a lot of them do, you know, are very blatant, but for the most part, You'd be hard pressed to hear them say it to a black person. You know what I mean?
+Darius: No, I hear you. It makes sense. This is rural Louisiana in the 90s though. So yeah, maybe he wasn't right.
+Jordan: It's Louisiana. I can't forget what state it was in. That's right. You're right. You're right. I'm tripping.
+Darius: They didn't say the state, but it's based on David Duke, who was in Louisiana. But I got a question, man. So yeah, this retribution story is like, it's like supernatural, right? It is not atypical to have some supernatural, like one of my interesting ones is I read Wright Thompson's book about the Emmett Till murders and Emmett Till</t>
+  </si>
 </sst>
 </file>
 
@@ -8066,7 +8273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8091,7 +8298,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8108,6 +8314,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8427,7 +8637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -9204,7 +9414,7 @@
       <c r="E39" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" t="s">
         <v>166</v>
       </c>
     </row>
@@ -9257,6 +9467,23 @@
       </c>
       <c r="E42" s="9" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="4">
+        <v>1995</v>
+      </c>
+      <c r="C43" s="7">
+        <v>3</v>
+      </c>
+      <c r="D43" s="8">
+        <v>4</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -9271,7 +9498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -9611,6 +9838,14 @@
         <v>165</v>
       </c>
     </row>
+    <row r="43" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ECE6132-7E91-4BAF-8193-9766ACFCC75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7054A44C-6F27-43A3-81FC-25F057051703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="171">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -8201,6 +8201,9 @@
 Jordan: It's Louisiana. I can't forget what state it was in. That's right. You're right. You're right. I'm tripping.
 Darius: They didn't say the state, but it's based on David Duke, who was in Louisiana. But I got a question, man. So yeah, this retribution story is like, it's like supernatural, right? It is not atypical to have some supernatural, like one of my interesting ones is I read Wright Thompson's book about the Emmett Till murders and Emmett Till</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1VJUNF119Dw</t>
+  </si>
 </sst>
 </file>
 
@@ -8314,10 +8317,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9434,6 +9433,9 @@
       <c r="E40" s="9" t="s">
         <v>156</v>
       </c>
+      <c r="F40" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7054A44C-6F27-43A3-81FC-25F057051703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0BA6D9-85BD-48BA-8D9E-EAB64F9E6AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="172">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -8204,6 +8204,9 @@
   <si>
     <t>https://www.youtube.com/watch?v=1VJUNF119Dw</t>
   </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=beNSfjBX-Vc&amp;t=220s</t>
+  </si>
 </sst>
 </file>
 
@@ -8276,7 +8279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8301,6 +8304,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9453,6 +9457,9 @@
       <c r="E41" s="9" t="s">
         <v>161</v>
       </c>
+      <c r="F41" s="10" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0BA6D9-85BD-48BA-8D9E-EAB64F9E6AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1090AE-FEE2-45BC-9707-A26D67EBF560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30660" yWindow="16080" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="178">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -8207,6 +8207,403 @@
   <si>
     <t>https://www.youtube.com/watch?v=beNSfjBX-Vc&amp;t=220s</t>
   </si>
+  <si>
+    <t>Do The Right Thing</t>
+  </si>
+  <si>
+    <t>That Awkward Moment</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The Block Wakes Up&lt;/li&gt;
+    &lt;li&gt;Act 2: Tensions Rising&lt;/li&gt;
+    &lt;li&gt;Act 3: The Breaking Point&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius review Spike Lee&amp;#39;s seminal 1989 film Do the Right Thing, examining its stifling Brooklyn setting, complex racial dynamics, debates over economic validation, and the tragic escalation of neighborhood conflict under extreme summer heat.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1 covers the morning routines on the Bed-Stuy block, Ruth E. Carter&amp;#39;s iconic costume design, Buggin’ Out’s protest over Sal&amp;#39;s Wall of Fame, and Darius and Jordan&amp;#39;s debate over begging white-owned businesses for validation versus patronizing Black establishments.&lt;/li&gt;
+    &lt;li&gt;Act 2 explores the stifling impact of weather without air conditioning, the multi-ethnic fourth-wall racial slur montage, human tribalism as an evolutionary defense mechanism, and the subtle friction of gentrification and outsider perception.&lt;/li&gt;
+    &lt;li&gt;Act 3 examines the late-night confrontation at Sal’s Famous Pizzeria, Radio Raheem’s tragic death at the hands of the police, Mookie’s decision to throw the trash can, and whether the film represents a polished masterpiece or Spike Lee&amp;#39;s necessary first rough draft.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Does persistent community tension stem primarily from systemic racial bias, or does bad-faith communication and a lack of basic conflict resolution turn minor slights into avoidable disasters?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Racism in cinema is often portrayed as an explicit family heirloom taught at home, but Do the Right Thing shows how external social friction and peer pressure can cultivate racial prejudice in individuals even when their parents don&amp;#39;t preach it.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Human prejudice is rooted in evolutionary tribal skepticism developed over millennia; when individuals choose to interpret every mundane daily interaction in bad faith, explosive conflict becomes an inevitable self-fulfilling prophecy.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Demanding institutional validation versus economic self-reliance—is it worth boycotting a neighborhood pizza joint to demand Black representation on the wall, or should that energy be spent supporting and patronizing Black-owned enterprises?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Extreme heat and psychological irritability&lt;/li&gt;
+      &lt;li&gt;Institutional racism versus evolutionary tribalism&lt;/li&gt;
+      &lt;li&gt;Economic self-determination and Black entrepreneurship&lt;/li&gt;
+      &lt;li&gt;The search for validation from outside establishments&lt;/li&gt;
+      &lt;li&gt;Conflict escalation and the absence of de-escalation skills&lt;/li&gt;
+      &lt;li&gt;Generational divides in the workplace and community pride&lt;/li&gt;
+      &lt;li&gt;Police brutality and accountability in pre-camera eras&lt;/li&gt;
+      &lt;li&gt;Gentrification and neighborhood boundary anxieties&lt;/li&gt;
+      &lt;li&gt;Evolution of artistic style: early prodigy rough drafts versus polished masterpieces&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The Pact&lt;/li&gt;
+    &lt;li&gt;Act 2: Hidden Feelings &amp;amp; Unrealistic Lifestyles&lt;/li&gt;
+    &lt;li&gt;Act 3: The &amp;quot;So...&amp;quot; Moment &amp;amp; The Fatal Flaw&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Jordan and Darius review the 2014 romantic comedy That Awkward Moment, examining its portrayal of modern commitment phobia, male friendship dynamics, the friction between casual hookups and emotional honesty, and the career trajectories of its star-studded ensemble cast.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1 covers the initial singlehood pact formed after Mikey&amp;#39;s sudden divorce, the charm of on-location New York winter filmmaking, the discrepancy between the characters&amp;#39; professional maturity and juvenile relationship logic, and Jordan and Darius ranking the Oscar-caliber dramatic peaks of Efron (The Iron Claw), Jordan (Sinners), and Teller (Whiplash).&lt;/li&gt;
+    &lt;li&gt;Act 2 examines the unrealistic lifestyle-to-physique ratio portrayed in male-led rom-coms, the psychology of taking a casual relationship public, and the deceptive comfort of &amp;quot;spinning the block&amp;quot; with an ex-spouse.&lt;/li&gt;
+    &lt;li&gt;Act 3 explores the disastrous dildo costume party, Jason&amp;#39;s unforgivable refusal to attend Ellie’s father&amp;#39;s funeral, the realism of post-breakup cognitive spirals, and the hosts&amp;#39; diverging final ratings.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; In modern dating, why is making a relationship known publicly or socially still treated as the ultimate threshold of commitment, and does hiding a partner reflect personal boundary protection or cowardly deception?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Romantic comedy tropes often rely on grand apologies and cinematic speeches to erase egregious mistakes, but genuine romantic maturity requires understanding that presence during life&amp;#39;s darkest moments matters far more than charisma.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Hollywood routinely exaggerates male conversational aggression while sanitizing romantic accountability; letting a protagonist magically win back a partner after abandoning her in grief rewards emotional cowardice instead of holding men to adult standards.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Defining the relationship timeline—does two months of consistent dating indicate a committed partnership, or is it still strictly exploratory probationary territory?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Commitment phobia masked as personal freedom&lt;/li&gt;
+      &lt;li&gt;Emotional maturity versus chronological age&lt;/li&gt;
+      &lt;li&gt;Unrealistic physical standards and lifestyle portrayals in media&lt;/li&gt;
+      &lt;li&gt;Male camaraderie, wingmanship, and emotional vulnerability&lt;/li&gt;
+      &lt;li&gt;The politics of public relationship acknowledgment&lt;/li&gt;
+      &lt;li&gt;Grief, emotional abandonment, and relationship &amp;quot;fatal errors&amp;quot;&lt;/li&gt;
+      &lt;li&gt;The psychology of breakups and rebound patterns&lt;/li&gt;
+      &lt;li&gt;The evolution of early 2010s rom-com tropes&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome back to Out the Trunk with Jordan and Darius. I'm Jordan, that's Jordan B. Riding on all socials.
+Darius: And I'm Darius, that's Deez I love me Ary on all socials.
+Jordan: And this is our movie review episode. Today we're going to be reviewing Spike Lee's classic, Do the Right Thing.
+Darius: All right, act one, the block wakes up. The neighborhood wakes into a heat wave as Mookie starts deliveries. Sal opens a pizzeria and familiar block personalities establish the film's humor, rhythm and early cultural tensions. I must admit, this is my first time watching this movie. So it came out when I was one years old. And so I'm going to use that as my excuse for having not watched it.
+Jordan: So yeah, it came out right before I was born. I actually never seen it cover to cover before either. So I mean, I'd seen bit to pieces. I obviously had no climactic scene and all that, but I'd never seen it front to back like that.
+Darius: Also wanted to add that life without air conditioning seems, well, was so trash. I went through it for a while.
+Jordan: ******* miserable.
+Darius: It's ******* awful. People are like, why is there's been a population boom in the Sun Belt and people like returning to the South and it's like, because it's habitable now. You have air conditioning. Yeah.
+Jordan: You don't die. Don't dehydration.
+Darius: Birmingham, Alabama and Jackson, Mississippi look like appealing cities when it's not sweltering hot inside your home. So, you know. Correct. Not so bad. But what you got for act one?
+Jordan: So act one, first I wanted to shout out Ruth Carter. She did the costume design for this movie. She's a legend. She did Black Panther, Black Panther, Wakanda Forever. She did Malcolm X with Spike Lee as well. If it's a classic black movie, there's a good chance she did the costume design, basically. She actually had an exhibit of her wardrobes from all her movies at the museum over there by state a couple of years ago. It was really, really good. So I wanted to shout her out. Not enough black women in film and television, so I wanted to give her flowers. Also, I want to say, man, Spike Lee was really young when he made this movie. You kind of forget that because he's such a legend now, you just forget just this is a really early in his filmography to have a classic like this that he wrote, directed and produced himself.
+Darius: I mean, legends are legends for a region. He's literally a film prodigy, you know?
+Jordan: Right.
+Darius: These are my top five filmmakers, you know, after the big three, you know, Nolan Tarantino, Scorsese, you really I mean, Spike Lee, I mean, he's four, I guess. So.
+Jordan: Yeah.
+Darius: Absolute legend. So there's it's interesting to watch this movie through 2026 eyes. It's sort of like how my own little evolution about these things because I'm watching Juan Carlo Esposito. I butchered his name, I'm sure. Character Giancarlo Giancarlo, his character. And I'm just like, Why are you complaining about not having a picture in that restaurant, man?
+Jordan: Right. What did you?
+Darius: What? Also, just like, how many black restaurants did you walk past to complain about this white restaurant? I just, it just, you know, if it's going to feel like a stress, it just reminds me when people complain about Grammys and then skip the BET awards. It's like, how many black restaurants they walk past on their way to this pizza shop and then they get there and be like, why ain't no black people in here?
+Jordan: Right.
+Darius: I just don't understand. Like, why do you need it that? Why do you want them to validate you so bad? You know, that black, those black restaurants would love your business. You know, BET Awards would love for Jay-Z and beyoncé to show up and treat their awards the same way that they treat the Grammys. Right. It's just like, go where the love is at. Why are you begging these people for approval? I don't get it. You know.
+Jordan: Yeah, I'm with you on that. Also, it's just like one, obviously the movie's about racism and racism. We'll talk about that later as it gets deeper into the plot. But it's like you're in this establishment, you screaming and hooting and hollering. You know, he like he did have every right to throw you out. You know, he said, hey, don't come back for like what? I think he said give him a week, whatever, you know, which is Pretty reasonable considering how he was acting and it's not a bar and he wasn't drunk. You know what I'm saying? Like you just in there screaming and ****. It's early in the morning. People just trying to eat pizza.
+Darius: Also just like, it is his restaurant. You can put whatever **** it is. You are local to go somewhere else. You are not obligated to eat here.
+Jordan: Right. Like we're going to, I have several points I'm going to make about racism and especially Italian racism in this country. But The old Italian dude, the middle-aged Italian man in 1989 is not gonna have Muhammad Ali on his ******* wall. Like, you know what I'm saying? Like, he had everyone I would expect him to have on his wall, given his age.
+Darius: Yeah, it's just, I don't, I just don't understand. The pizza couldn't be that good, you know? I'm not. Well, there's that too. It's just like when people, and I'm not gonna lie, I used to do this, but jumping through all the hoops to get into a club.
+Jordan: Correct.
+Darius: I'm not begging you to take my money.
+Jordan: That you know they don't want you in.
+Darius: It's not even that. I'm not begging you to take my money.
+Jordan: Yeah.
+Darius: Ain't nothing in that club. Ain't nothing in that pizza that I haven't seen before or eat before. And so the idea that I have to prove myself to you to ultimately give you my money.
+Jordan: My money.
+Darius: So I got to beg the bouncer and do this and do that just to get in there and buy a $12 cocktail.
+Jordan: Right.
+Darius: I'm not doing it. I'm not doing it. If I can't, I will wait in a reasonable line. I will show my ID. I will walk in. If it's more hassle than that, I'm not going to be able to do it.
+Jordan: Like, yeah, No, it gets to a point where it's like, you know, everybody talks about like fantasize that Julie Roberts scene in Pretty Woman where she's like, oh, you make commission. And she like bought a bunch of ****. And I'm like, you. You just paid her bills. You didn't hurt her in any way. And also you didn't prove your point because she's still going to be judgmental and condescending and whatever the case may be.
+Darius: You know, I think the exception, you know, like that's it.
+Jordan: Right, exactly. Yeah.
+Darius: The next black person that walks in there is going to get treated just as poorly.
+Jordan: Correct. Yeah. I really wish us to get out of this cycle of like prove our way out of racism or earn our way out of racism. You know what I mean? Like you can make a lot of money and have a good job and be in a nice neighborhood. And they may be nice to you, but they only nice to you most likely because they just like you. That it doesn't change the fact that you're black. You know what I mean?
+Darius: Or just, I don't think it's healthy to go through life that skeptical of everybody. But when you enter an establishment, the establishment makes it clear they don't want you there. You just leave. I'm not begging to stay. This is not. That's a classroom, a school. This is not a courtroom. This is not a voting booth. Like it's a ******* bar. It's a ******* pizza place. There's 1000, there's five within walking distance. I would just go to one.
+Jordan: There's pizza everywhere.
+Darius: I would just go to one that wants me there, you know? Correct. We talk about classrooms. We talk about courtrooms. That's a whole different conversation. Yeah, different conversation. A pizza joint. Let's go to a different one.
+Jordan: That ain't a civil rights issue. You were allowed in the restaurant. They gave you food. You know what I'm saying?
+Darius: It's like, oh, don't go to the, don't go to that club. They do, do, do. Okay, I'm not. Why you keep going back?
+Jordan: Yeah, right, exactly. Yeah. You know, like it's certain spots on the strip on Glenwood, I'll never go into again. And I don't care to. And the music ain't even good. So what am I mad for?
+Darius: If you make me feel like I'm bothering you. I'm not like you hear about restaurants in Atlanta where it's just like you got to text this promoter and do this and we don't do takeout. Remember when Keith Lee was in Atlanta in every restaurant? It was like, it's like, you're not doing me a favor letting me buy $30 chicken and waffles. No, you know, I'm not like that's the thing with like the baby's new restaurant. There's like a bouncer at the door and he'd be talking to people crazy.
+Jordan: Oh, I didn't know that.
+Darius: Listen, man. The waffles actually do look good, but if you make me feel like I'm honored to buy your waffle.
+Jordan: Nah, and I heard actually, and I heard it wasn't good. The people I know in Charlotte said it wasn't good. Somebody said they got their **** their food in a ******* pizza box. So, you know.
+Darius: The pictures look good. The waffles look good. The soul food. Looks a little hit, but like there's a no, they definitely look like dessert. They don't look like breakfast waffles, like cookies and cream waffle. I'm not, I don't really want that at 10 a.m. Correct. To me, that's just a slice of cake, which is nothing wrong with cooking and cream slice of cake.
+Jordan: Yeah.
+Darius: But you know, you know, it's I bet you like I've heard the batter is very cake. Like it's much more cake than waffle, but you know, I like cake. If it's good, it's good. You know, I feel you.
+Jordan: Yeah. But and also like if you recently just like kind of are resurrecting your career after basically a self cancellation because of your rant, maybe tread lightly with the community. I don't know. That's just me.
+Darius: You know, it's just I don't understand this. And I primarily like black restaurants in Atlanta. Most of it's black-owned this idea that you're trying to pitch exclusivity.
+Jordan: Yeah.
+Darius: And like, make me feel like it's not a nightclub and I don't even do exclusivity with the nightclubs. So I'm certainly not going to do it for shrimp and grits at 3:00 in the afternoon.
+Jordan: Like, yeah, man, that's my thing. It's like we that's a problem with us that we have, I think, too, is like we talk about the **** that other ethnic groups do to us with their business commercially and stuff like that. And then we turn around and do the same **** to each other. And I'm like, well, what was the point of you getting a business if you were just if you wanted to discriminate? against your own people, essentially.
+Darius: I mean, as long as the rules are posted and it's clear, I just won't be there. Like there's this restaurant, Kitchen and Cocktails, that's, they have a few different restaurants across the city. They got this long list of ****. Listen, bro, you're not going to give me homework to come spend, to come eat fried chicken and collard greens.
+Jordan: Yeah, it's ******* crazy.
+Darius: But people go, but I'm just not, like, If I can't show up in a shirt like this and some jeans and some J's, I'm not going. Yeah. Like, I'm not going to go nowhere looking crazy. I'm going to be presentable. But if this shirt, some jeans and some J's can't get me in, it's not the spot for me. You know? Right. Yeah.
+Jordan: I had an experience like that in North Hills. We were trying to go to 60 Vines. We went to the Virgin in Charlotte the time for our friend's birthday. And the food was mid. So I'm like, they were giving us a hard time looking me up and down and ****. And crazy. A little group of white people walking in right before us had no had no reservation at all, whatever. It's like, all right, you just saved us 100 bucks on mid food. Thanks. And I'll never go back again.
+Darius: Yeah, it's just especially when you're dealing with a business with a lot of competition. There's we probably have too many restaurants. There's 5 on every corner, bro. I don't need to be here. You know, I'll just go to another one. But let's get this back to the movie. What else you got for act one?
+Jordan: Yeah, it's funny. There was the old guys were talking from like the red wall and they were talking about like the Earth is getting hotter and it's going to be more water and we're dry and dry and they're like, you crazy. And it's like he was right about global warming. Spike Lee was 30 years ahead of his time on that.
+Darius: Yeah, man, we still burning fossil fuels, so it's going to keep. Well, we've gotten a lot better about We've actually made quite a bit of progress on climate, but it's still, hot as ****. We basically, we get like 2 days of winter in Raleigh now, and I remember when we actually got like 2 weeks of it at least, so.
+Jordan: Correct.
+Darius: You got anything else for Ag1?
+Jordan: Yeah, also I want to say, first of all, man, inflation is crazy because $1.50 for a slice of pizza, you feel like you're robbing them today. Also the fact that it was more expensive to get extra cheese than the slice of pizza itself is crazy.
+Darius: A dollar 50. I don't think you can get a candy bar for that anymore.
+Jordan: Yeah, it'd probably be like a dollar 80.
+Darius: Honestly, a slice of pizza for a buck 50. I told you, Louis, when I was at the Sixers game last week, I don't mean to date the pie, but I went to the halftime. You know, you file out. Yeah, I'm hungry. I ate since breakfast, basically. And I popped into this little spot and I saw a slice of pizza and a soda combo was like, no, it was a slice of pizza and a Coors Light. I'm not going to lie on them. Slice of pizza and a Coors Light. They wanted like 30 something dollars for it. And I turned around. It just gets to a point.
+Jordan: That's ridiculous. Yeah, man. I'm not, I feel you.
+Darius: I went, I left, found a spot in Chinatown, got some salt and pepper calamari and some shrimp dumplings. And that was like, $18 combined and that's much better than a slice of pizza of course like so.
+Jordan: Yeah that's that's that's nuts yeah I had to I've been like shopping a lot for events and stuff for work and the price of the **** that I had to pay for is crazy um I uh I had to get like 24 packs of sodas for for property man and they're like $9 now what the ****?
+Darius: Dude I had to pull up on a function Two or three months ago, and somebody told me to grab sodas. So I walked into Harris Teeter and I just grabbed 412 packs because I figured there was 20 something people there, 2 sodas in there. Just shy of $40. I didn't look because I'm like, how much can ******* sodas be? I don't buy sodas. And yeah, it was like $38 for 412 packs.
+Jordan: Yeah, man.
+Darius: I didn't.
+Jordan: Yeah, I had to scoop up some desserts for a Halloween party for a property for a coworker who couldn't make the event. And I was like, how do people fit at the event? And they're like 85 to 100 people. And I'm like, ****. Okay, so I have to, I'm at, you know, grocery store and I'm like, okay, counting like, okay, this should probably feed, you know, that **** was like 80 bucks, dude.
+Darius: Yeah.
+Jordan: It was cookies and cupcakes and whatever, covered in icing.
+Darius: Junk food. All right, what else you got frag one?
+Jordan: Yeah. So I will say one funny scene in the movie is where the white dude scuffs up Giancarlo's Jays with the bike. And then they're like ranting at him and ****. And then he's like, they're like, you need to get out of this neighborhood. You don't even belong here. And he goes, I was born in Brooklyn. Everybody's like, oh, because he had on the bird jersey.
+Darius: Yeah.
+Jordan: And if you do, it's like a betrayal to be a Celtics fan if you're from New York.
+Darius: Yeah, the late 80s for sure. Yeah, it was. Yeah, it makes sense. I didn't catch that. But yeah, it I mean, basketball was broken down pretty strong on racial lines back then. Correct. Strike me that a white dude for Brooklyn would be a bird fan. So right. Heading into act two with the tensions rising, small confrontations intensified through clashing opinions, personal grudges, and debates over representation. Mookie moves between work, family and community as frustration spreads across the block. Circling back to the air conditioning from act one. How much of the tension is movies? Because everybody was just stupid, hot and uncomfortable.
+Jordan: I think that's. Yeah, I think it's.
+Darius: Yeah, there's a reason crime goes up in the summer, man. And it's just. Yeah, when you hot and sweaty and there's no escape, not thinking clearly you're there's sitting in a hot *** house.
+Jordan: Yeah.
+Darius: It's one of the most irritable things you've ever done in your life, man. You really do be ready to swing on somebody.
+Jordan: But you can't. There's no relief.
+Darius: No. There's nothing you can do. No, it's not like the winter where you can just grab an extra blanket. You just got to sweat and it never breaks. Yeah, man.
+Jordan: Yeah, I 100% believe it was due to the heat. I also think it was kind of a metaphor too for the tensions rising as well. Yeah, I think there's a it's It kind of gave me shades of like 12 angry men. I remember it was in the summertime. They're in that hot *** courtroom. The fan wasn't working. They're losing their ****. They finally get the fan working a little bit and the tie kind of starts to break in terms of their voting and ****. It reminded me a lot of that as well.
+Darius: Yeah, I mean, I mean, It's there's a lot of studies that go into just like how much the summer changes. It's a little different now with air conditioning. But no, man, it was you ask any police station, they'll say that summer brings out the crazies. So also just like idle time, the kids aren't in school, they don't have anything to do. Right. You know, it's just idle, idle times. It was a devil's playground or some **** like that. So what you got for that too, man?
+Jordan: Yeah. So I love the scene where it's every, it's like the close up where they're like breaking the 4th wall and it's each demographic giving a racist rant against another demographic because it does show just how pervasive racism is in every community and against everybody. It's no one's immune to, you know, the disease that is hatred slash race racism. So like they kind of showed that because I feel like a lot of times in movies we We do tend to I don't know the exact term. I don't want to make seem like I'm attacking us, but like as if we don't have any prejudice as well. So I like that it kind of showed that and I like that it showed that other minorities and people of color have have have prejudice against other communities as well, because that is important. And that is a thing that I feel like nobody really talks about enough. So I'm glad they showed that.
+Darius: I tried to stay away I mean, I call things racist when they're racist, but to me, this is more like tribalism more than anything. And it just.
+Jordan: Fair, that's fair.
+Darius: Evolutionary response because, you know, when we were cavemen, outsiders could, they brought disease, they brought warfare, they could have killed you. And so we've evolved to be skeptical of people outside of our tribe. And so, no, I mean, anyone, there's no race or ethnicity of people who doesn't have some problematic skepticism of outsiders. And so, you think about yourself in a prehistoric times, that unfamiliar looking tribe across the sea could be here to murder you and probably is. If they didn't murder you, they could bring diseases that you haven't, that you have an immune system to fight back from. And so it's in that world is perfectly rational to be highly skeptical of outsiders. And we're not from an evolutionary standpoint, that far removed from that world, you know, right. Technology is advanced in much faster, but for millions and millions and millions of years, we live that way. And for the last, what, 300, we have it or 10,000 right. And so, no, you mean just that's why I'm just a bit more. I want to say understanding, but just a lot less hardline about these things than I used to be, because, you know, if everyone behaves similarly, it's almost not even a personality trait at that point. every single human tribe of people, race and ethnicity of people shares some problematic aspect, problematic skepticism of outsiders. So like how do we balance what's the right one and what's the wrong one? Obviously all of it's wrong and we have systems in place to mitigate those things, but that natural impulse it it's so but much it's only but so much people can fight back against that so.
+Jordan: Right but and also even to your point about when you made earlier about how many black restaurants or soul food spots did Giancarlo's character walk past on the way to go to the pizza spot well the Italians don't live in that neighborhood so it's like how many Italian how many open locations did they walk past they could have possibly inhabited to so it's like in the same token the you know the What's the name? John Tutoro. He's like, you know, the big racist in the movie, right? And he's like, I hate being here. It's a disease, whatever. It's like, but you can make the case that you're the disease because you're the foreigner there. You don't belong in that community, but you're not native to that community. So and also, again, you had to leave your community because you couldn't handle the competition. So it's also that.
+Darius: It's funny because I always say that people like gentrification is just rebranded xenophobia. It's just like You don't belong in this neighborhood because it's like if a white person said that you would call it for what it is. Right. Or like when people my favorite like gentrification could play someone who live in a neighborhood of like when you start seeing white women jogging during the day, you know, you know how racist and xenophobic that is. They better start putting up good building shows. Yeah, it's just like, it's just, there are legitimate claims of gentrification, but the vast majority of it is literally just fear of outsiders. It's just rebranded progressive xenophobia. Yeah. Like if you just, if any other, if an Asian said that about a black person in his neighborhood, you would hear it for what it was. Right. When you see black kids hanging out during the day, you do it.
+Jordan: Right.
+Darius: People don't hear themselves. But what else you got?
+Jordan: That's true, which is also a big point of the movie, you know? I loved, well, this is actually kind of the next one, but I just, I love this, the scene, well, act one and act two, where there's the scene where basically the father, the Italian father talking to the sons about like work and their job and saying like, you know, I own this place. you think you can do better, whatever. But I, obviously provide for you, provide a life for you and our family through this place, and he was trying to judge the mayor, the drunk guy. And, he was glad to sweep up and clean up and, for a few bucks to be able to buy a couple drinks, whatever, get through the day. And I like that both of those men were perfect examples of just taking pride in what you do.
+Darius: Yeah.
+Jordan: And the way they, They carried it differently, but then they, verbalized it differently. But that was a central message in the movie as well. I think that was part of what the issues with Mookie was, because Mookie was like, he did his job, but he didn't care. He didn't really have too much pride and he didn't give a **** about coming back home and coming back to the store in time, you know, whatever. And I like the way that it showed that dichotomy between those characters.
+Darius: Nobody had a ******* job.
+Jordan: It was like 4 characters that had jobs. It was Samuel L. Jackson, all the people in the pizza shop, and yeah, that's it.
+Darius: No, in the 40s, between.
+Jordan: 40 and 60 years old. I was thinking that too. I'm like, where's everybody? What are y'all doing for the day? And also, I get all your work because you're not working.
+Darius: No, just hanging out. There's just the dude with the boombox. He has nowhere. Like, there's nowhere to be. He's just middle of the day. You don't adults don't get summer break. Where are you?
+Jordan: I don't know. Yeah, exactly. And also, I have a question about Radio Raheem. I couldn't tell. Was he supposed to be like, the neighborhood Debo like tough guy or was he just like on the spectrum? I couldn't figure it out.
+Darius: I just think he was like the loser guy who just kind of, you know, he just, he's that, you know, he's just, he's just, he just, he's just a list. Everyone has like that, family member that's just kind of listless and just kind of hangs out and just doesn't really have any business ever. Like, don't you have somewhere to be? No, not really.
+Jordan: No, not really.
+Darius: Not really anything to do. Do you have anything for that? You want to add an actor.
+Jordan: Oh, yeah. You know what? So they always say, like, racism is a learned behavior, and we assume that it's taught at home. But at least for act two, it appears that the the racist son just kind of got that on his own, or maybe probably from friends of his own age or whatever, because his father didn't seem to really have those ideologies and his brother didn't seem to either. So they kind of showed that we tend to stereotype and be like, oh, it's because they're parents. But I also know people who whose parents weren't racist and who their kids are, you know, so like, I like that they showed that they broke the kind of the trend with that you see in film.
+Darius: Yeah, I mean, I mean, **** after what, the 5th grade, your kids are outside your home more than inside your home. They're in school all day. So, you know.
+Jordan: Right.
+Darius: Obviously, it matters what environment the parents provide, but ultimately, for sure. You know, external factors matter a lot, too. So.
+Jordan: Yeah.
+Darius: All right. Heading into act three, the breaking point. A long day, the long day reaches a breaking point that as public disagreements become impossible to contain the neighborhood must face what has been building beneath ordinary routines. I'll be honest, this movie kind of loses me a bit here. It was hard to track what was going on. It was like all these characters are popping in and out. There's a fight on the street. I was just like, I watched the first hour Friday night and then I watched the second hour Sunday morning before football. And I was crying. About that last 30 minutes, I was like, I've seen Rosie Perez in her underwear. I'm good to go. We can go. I'm ready to tap out on this at this point. I've seen that.
+Jordan: Interesting. So for me, it was the opposite, because for me, honestly, the first hour and a half of the movie, nothing really happens. Everybody's just walking around the street. Like that's just really, it's Sesame Street. It's basically Sesame Street with racism. It's the first half of the movie. So the second-half, the third actor, I was glad like something finally happened. I mean, I kind of knew it was going to happen, but you know. and also for one, we kind of just know the fact that like Spiley's character is a deadbeat. Yeah. No one, no one ever talks about that when they talk about the movie, like your kids down the street, you haven't seen him in a week and you didn't, you didn't drop off no money for your baby mama. Like what?
+Darius: Also, he's like barely employed. He like delivers one pizza a day for this.
+Jordan: One pizza an hour.
+Darius: Yeah, he's out. Nobody here has any work ethic. It's just.
+Jordan: Yeah, bro. You're not. Yeah.
+Darius: Even the people in like the restaurant, they're still just kind of hanging out. Like they're not. True. It's just, that was kind of, I mean, look, I'm not from New York City in the 80s, but I get that vibe from a lot of movies back then. It's just like, when we watched Crooklyn, like there was like one dude on the block with a job and he was like the good guy on the block because he had to get up to go to work in the morning. And like that just made you like a standup gentleman. Right. None of these people have anywhere to be. And maybe they would run into less conflict and problems and chaos and they had stable employment, So maybe I'll do it.
+Jordan: Yeah, that is a good point. Cause it was like, yo, what is no, like the old lady who was watching Neighborhood, she was old. Presumably she's retired. All right, cool. The mayor, he was old, presumably he's retired. I'm gonna assume he probably was like fought like Vietnam or something like that, you know, whatever. Everybody else, I'm like, what are y'all doing? Like the dude who's like going off on him, who's wearing the purple, that weird rant he went on. And I'm like, you're just walking a bit on the street too. How are you any better than him? You're doing the same **** you're not doing ****.
+Darius: Maybe if you were in an air-conditioned office doing a job, you wouldn't be uncomfortable.
+Jordan: You wouldn't be tweaking on a ******* stoop on a homeless man.
+Darius: Yeah, maybe if you left the house for 8 hours every day to do something with yourself, you wouldn't be so irritable. And you know, you people find things to do with free time. And so maybe you need less of it, if you will. Right. So I'm out of things to say about act three, man. So you take it far from here. What you got?
+Jordan: All right. So we have the, it's the end of the day, they're clocking out, and then his friends want to get a piece of pizza at the end of the day, which is ******** because you know at work, I'm trying to go home. **** you. I wouldn't let him in. I wouldn't let him in. I'd be like, nah, **** that. You know what time we close, you live here every day. Then they come in there, it's all good vibes. Then of course, Radio Raheem and I forget his name, but the dude with the glasses comes in there with their protest at the end of the day. I don't even understand what they were doing. The day is over, so you can't boycott a closed business.
+Darius: They just wanted.
+Jordan: It wasn't a good point.
+Darius: Yeah, they just wanted to be annoying. That's all you. Everybody knows. who has the friend who is just like the super pro-black friend who almost seeks conflict everywhere they go. And it's like, I get it. This person probably isn't, you know, the most progressive on racial issues. But you're literally seeking conflict in every interaction you've had today. And I'm tired of you.
+Jordan: Yeah. Right. Right. Like that's my thing too, because it's like there are times, most of the time, yes, it's just somebody just being racist a lot of times in those particular, situations, right? You're not starting anything. You can just walk into a business and you can just feel the tension there. But it's like you, this character like was the tension in every situation, in every environment. And those situations make it really difficult. Like where you're, like you've ever been out in a spa and like maybe somebody's like fainted or they're just, out of control and it's like you need to temper chill get out chill out because they're going to they don't know that you don't have bad intentions so they're going to see your passion as something different because they don't they're not familiar with it so you got to like learn how to navigate those environments in those situations.
+Darius: I I can't tell that story but uh yeah there's some people who just if you interpret everything people say in bad faith</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome back to the Out the Trunk Pile with Jordan and Darius. I'm Jordan, that's Jordan B. Riding on all socials.
+Darius: And I'm Darius, that's these all up in area on all socials.
+Jordan: And today we're going to be reviewing That Awkward Moment, a 2014 rom-com about friendship, dating, and the messiness of figuring out where things are going. Toss it to you.
+Darius: Act one, the pact. Three friends respond to romantic uncertainty by agreeing to stay single, but new encounters quickly test whether their rule is confidence, denial, or fear disguised as freedom. Let me just say all three of all of these people too grown for this ****. A pact to remain single. Really, dude? Might be George's character is a doctor. So he's at least got to be 28 because you got to go to medical school. Like that's not, these aren't college.
+Jordan: I think his character is like, I think they're like 27, I think, something like that. Yeah.
+Darius: That's too old for this ****. It's all blood brothers. Let's be single. Dude, come on, man. People are getting married. Like people, this is, you are not in college. This is, these are grown men. That was, that was so childish. But I must say the line, I wasn't confused about the breakup. I just didn't know we were dating.
+Jordan: We were getting felt. Yeah, man. It's like that. Remember that there's that clip of Bow Wow where this girl's like, you cheated on me. And he's like, cheat. I got to be with you to cheat. And she goes, we're together. And he just goes, what?
+Darius: Yeah, it's, you know, that was funny, which is fine and not juvenile, but the idea that three men in their late 20s would make like a sink, like these. They moved like 20 year olds, but by death, like one's a doctor, so they have to be in their late 20s. Like you have to go to undergrad, you have to go to medical school, you have to do residency.
+Jordan: Residency, yeah.
+Darius: Unless there's, unless the writers just didn't think that through, which is entirely. I think that's probably what happened.
+Jordan: Honestly, I think the character's supposed to be 24, 25, but they, but because he's a doctor, he has to be older than 25 and they didn't think that through. I think that's what happens.
+Darius: All right, fair enough. I'll stall him out then. Let me just also say, having just left a big city, wandering around for three days, I must say, I get it. It is. I get why people pay the highest rent to live like that because it is. It's a great time, man. Philadelphia must be nothing. So what you got for act one?
+Jordan: Yeah, I'll say. Yeah, that's one. The first thing I wrote down is like, man, I feel like it would be so fun. One to just be like young and single in New York. And to experience a New York winter, wearing coats in the wintertime and the Macy's Day parade and the, lights and Rockefeller Center and all that kind of stuff. So I feel like that's, I think that's one of the things I love about this movie so much is that they made it in New York and they shot it there, and not only some soundstage with the ******* green screens.
+Darius: It was made, of course, from when he took over movie productions. Right.
+Jordan: Yeah. There's just a magic to to New York in the winter that is just beautiful, you know? So I always think the hallmark of a good rom com is it being in a cool city for sure.
+Darius: I, you know, I reiterate what you say. Yeah. One of my biggest regrets is not spending some time in my early twenties being young and single in New York City, you know? Yeah, that's the one thing I didn't get to do that I really wish I had because.
+Jordan: Yeah.
+Darius: I've been old and single in New York City and Philadelphia, and it's a great time. So being young and single out there seems better. So, yeah, yeah, yeah. What else you got for that one?
+Jordan: Yeah, actually, it's funny because I do love that scene where she's like, where he's like, I didn't know we were dating. And she's like, I need a man who drinks coffee out of a cup and not a cereal bowl.
+Darius: You know, a pack of cups is $10?
+Jordan: No, for sure. Yeah. He just really didn't give a ****. Also just funny because I've been in situations where like, in my mind, we're like taking it slow and in their mind, we should already be together. And there's that like push and pull there. And it's like, to me at least, like is 2 months a long time of dating? Like, I don't think that's a long time.
+Darius: Well, how old were you? How old, like now?
+Jordan: I just like.
+Darius: In my big age, two months of regular dating, we are probably in a relationship. In my early to mid 20s. Right.
+Jordan: Yeah, like I remember I had a situation where it was like, it was like 6 to 8 weeks and they're like, so where's it going? And they were like really aggressive about it. And I'm like, isn't that still just getting to know each other? I don't know. That's just me. So it's just interesting the way that people, different people view those those things and timelines and stuff like that.
+Darius: Communication is key, you know, make sure everybody's on the same page. So I have a question.
+Jordan: Yeah.
+Darius: Each lead actor went on to have three Oscar worthy performances. I don't remember if Miles, I know Oscar worthy will say Whiplash centers in Iron Claw. How would you rank them from worst to first?
+Jordan: Oh, that's tough, man, because I love all the.
+Darius: Performances, not the movies.
+Jordan: Okay. Oh, the performances.
+Darius: Oh, okay. I mean, yes, the performance is at the movies.
+Jordan: Yeah, I'm going to go. I hate it. I love all three of these guys. Like, for real. I'm fans of all three, but I'm going to go. I'm going to go Sinners, Michael B Jordan. I'm going Iron Claw, Zac Efron. Then I'm going Miles Teller for Whiplash.
+Darius: And that's worse. The first. I'll just match you and go best to worst. Iron Claw, Sinners, Whiplash.
+Jordan: Okay.
+Darius: I just thought Zac Efron was magnetic in Iron Claw.
+Jordan: It's ********. He didn't get nominated for an Oscar, bro. That's such ********. I still can't believe that.
+Darius: That's just a bias against wrestling because the Academy thinks wrestling is for yuckles and, you know, toothless NASCAR fans. But Yeah, I would rank Iron Claw 1, Sinners 2, Whiplash 3. Although, they're all excellent. We don't do the like. Right, exactly. Sinners was great. Don't get me wrong, but somebody has to win. And I just, I went into Iron Claw. I don't even like wrestling. I don't even know any of the characters. And it was more of a family drama than anything. And he was just magnetic. And he shared the screen with a lot of big name people and he owned it. And so.
+Jordan: Yeah. You know, was that your first was that one of your first time seeing him in a dramatic role?
+Darius: It was the first time seeing anything dramatic. I mean, has he done anything dramatic?
+Jordan: Yeah. Yeah. He's trying to think. There's one called The Lucky One. It was really, really good. I'm blanking. Charlie St. Cloud was really, really good. It was like a fantasy drama kind of thing about like grief and loss he was phenomenal in that yeah I think I think Isaac Efron honestly just like he's like the opposite of pretty pillars like he doesn't his acting is underrated because of how he looks I believe he's a phenomenal actor.
+Darius: Fair enough what else you got for act one?
+Jordan: That scene man with Michael B Jordan and his ex-wife where she introduced him to do she's ******* as his lawyer What would you do in that situation?
+Darius: Assuming. Well, this is a movie. So assuming this would actually happen, you know, what can you do?
+Jordan: I don't think for legal reasons, I should say.
+Darius: I mean, so look, you know, in my early to mid twenties, I might have reacted in rage and done what you want to do. But at this age, man.
+Jordan: Yeah.
+Darius: Yeah, I just, some LG's got to hold and she's got to live with that, and maybe it will come back, maybe it won't, but I'm not going to spend a week in a jail for what? I'm in jail and she's still laid up with the dude. So I whooped him up and she gonna nurse him back to hell while I sit in the jail cell. Okay, you won. Yes, but what does that cost?
+Jordan: You know, that's a good point. That's fair. That's fair. I also want to say whiskey does go great with ice cream, not like drinking whiskey and eating ice cream, but there's a really good ice cream spot. I'll tell you about off wax. They have like a whiskey flavored ice cream. It's phenomenal. Yes, I did want to say that. Also, one of my favorite scenes in the movie is where he brings the girl home, they hook up, and he sees like he thinks she's a ******. And then they realize they're at work together. Like peak awkwardness. I don't know what the hell I do in that situation.
+Darius: In his defense, a giant box of condoms on the bed stand is a bit distasteful.
+Jordan: Yeah, bro, for real. And the cash?
+Darius: Look, I buy in bulk as well, but the trick is to just leave the giant box in your closet or something and just have a couple on the bed stand. I get that it's cheap to buy in bulk, but you got to be a bit more cognizant of how things look. Correct. Yeah. What was I going to say? Well, that's what I thought. whiskey and ice cream. Yeah. I plan on this weekend. There's this European bakery that does those in Charlotte that does those viral fruit loose cakes. Okay. And I'm having a nice whiskey and trying those. I'm sure they'll be mid like that terrible cheesesteak, but I'm a sucker for a tourist or a viral food sensation. So we'll see how whiskey and ice cream goes to get our pastries go together then. So Okay. Anything else for act one?
+Jordan: Oh yeah. I just want to say they had a really cool job. I think that'd be like super fun to just like design book covers all day and like **** with like authors and kind of have those creative meetings. I don't know.
+Darius: You can only earn actual money doing that in movies. There's no, nobody would be homeless in a ***** that was their job in real life. I love movie jobs. Oh, what do you do? I'm a greeting card writer.
+Jordan: Right? Yes. Summer was 5 days summer. Yeah.
+Darius: A whole office. There's 50 greeting card writers here. This is the this is the whole company.
+Jordan: Okay.
+Darius: All right.
+Jordan: Yeah.
+Darius: That makes no sense whatsoever.
+Jordan: But you know, movies do give people a ****** ** idea of what they should do for a living. I do believe that for real.
+Darius: No, you know, vast majority of us are not going to have whimsical jobs. And that's OK. You know, it's it's I designed book covers. Not a real job. People don't even buy books like you. Right. Especially not physical copies. So no, not anymore. No. All right, man. What else you got for act one? Heading into act two, as feelings grow, the friends hide or minimize their romantic choices, creating tension between the image they protect and the relationships they may actually want. Old hobby horse of mine, I'm going to be a bit pedantic here, but I think it's important that people hear this. We call out discrepancies in female representation. And so we must do it to say that male representations. These dudes could not maintain those physiques, eating and drinking and living the lifestyle that they live. They're eating ******** all the time. They're eating ice cream. They're eating pizza. They're drinking beers. They're going out. I've never seen anybody hit the gym. Meanwhile, every time the shirt comes off, we got 6 pack of abs. It's not, that's not real life. And people need to, you have to keep reinforcing that.
+Jordan: That is true.
+Darius: That is fake.
+Jordan: And Miles Teller was the only one who looked like normal, like physically.
+Darius: No, he was, Miles Teller looked like a dude who works out five days a week. The other two just looked like dudes who like are obsessive about it. And either way, all three of them would not be able to maintain those physiques with the lifestyles portrayed on the screen. And I think it's important to continue calling those things out because it creates true mismatch, it's not good. But yeah, I was just drinking whiskey, eating ice cream, staying out late. And it's just like, again, all the shirts come off and everyone's ripped and it's just not how it works. So yeah. What you got for act two?
+Jordan: Okay. So yes, I have a question for you. Did you think that I forget her name, the tall girl already like was already in love with Miles Taylor's character.
+Darius: Yes.
+Jordan: Before they started hooking up.
+Darius: Yeah, for sure. Why does she look like Olivia Wiles to me for a while?
+Jordan: But she was in what if the Daniel Radcliffe movie we reviewed.
+Darius: That's probably where I remember her from.
+Jordan: She was the Adam Driver's wife in that movie.
+Darius: Gotcha. She's pretty, but.
+Jordan: Yeah, very pretty.
+Darius: Yeah, I think that she was into him and was just kind of waiting on him to, you know, come around on it. So.
+Jordan: Yeah, yeah, me too.
+Darius: Why is speaking of her, why is sharing relationship publicly so important to people?
+Jordan: Like on social media or just telling your friends?
+Darius: This movie had just been because she was like, demanding he tell all of his friends and she didn't even hang out with them. So I don't really understand why she would care. Right.
+Jordan: I mean, I think in her situation, she didn't want she wanted to believe. I think she needed that reassurance to know that it was real. Because I think she felt like if you just ******* me in private, then I'm just like another notch on your butt, another girl on your roster. And if you tell your friends about me, then I know that we're actually dating for real.
+Darius: As a very womanly understanding of male dynamics, because if you tell me you ******* somebody, I don't. That doesn't mean anything to me as far as dating them or not. Like, it doesn't make any.
+Jordan: It doesn't mean anything.
+Darius: But I understand why a woman would think that means something to us. It may mean something to them, but it does not mean the same thing to us.
+Jordan: So, right. Yeah. What else you got back to? Speaking of it not being the same thing, the scene where he's with that girl, Alana, and they're like, they're like mid throws of passion and she's like, so where's this going? And he's like, I think you're amazing. And he just waits to see if she's still going to keep ******* it. That **** was crazy.
+Darius: You know? Not unrealistic. We'll put it that way.
+Jordan: No, it's not. Yeah, no. Yeah. We'll have to talk at the bar about that.
+Darius: Not unrealistic. So, yeah. I mean, this is a nice little fun movie. There were some things that, you know, I just felt they were a little too old for, but to get all three of these dudes in the same cast is a feat in and of itself.
+Jordan: Correct.
+Darius: So I enjoyed it. Well, unless you got Frankie.
+Jordan: Me too. I love this movie. Okay, so there's Michael B. Jordan's character starts spinning the block with his ex-wife. They're kind of sneaking around and doing all the fun **** they never really did when they were married. I thought it was a really like realistic portrayal of spinning the block because when you're doing that with an ex, you kind of, and to spend some time, you kind of, it does feel new like you're dating a new person. So you do still have that honeymoon kind of feeling. uh up until you remember why y'all broke the **** ** in the first place um but I thought they did a great job of showing like oh yeah it's gonna feel new now things may be different even though they're not gonna be different.
+Darius: Yeah they always remind you in both ways why you broke up with the first place but it's fun for you know a good time uh yeah absolutely the words of Drake good time not a long time so yeah you want to head into act three or you got something else for act two um but.
+Jordan: Okay, so do you have the costume party in Act 2 or Act 3?
+Darius: It does. Whatever you want to do.
+Jordan: Okay, so for that, I did like the scene where they're all at the bar together and no one knows about the two friends hooking up.
+Darius: Yeah.
+Jordan: And she plays women for him and he fumbles on purpose. I thought that was really dope because he could have been an ******* and still done the thing and made her, you know, treated her like nothing or whatever, you know what I'm saying? And he chose not to do that and be a stand-up guy. I thought that was pretty dope.
+Darius: Early tell that he actually liked her or liked her. So yeah. we're not always the most vocal, but our behavior often reflects our, what we actually want. So correct. Act 3, the sole moment the characters face, whether staying undefined is protecting them or holding them back, pushing friendship and romance toward honest decisions without easy answers. Yeah, I definitely laugh out loud funny at the costume party. Yeah. You think maybe you'd ask a clarifying question before?
+Jordan: What's the theme?
+Darius: Also, even if it's a Halloween party, that might be a little much.
+Jordan: That is, that was excessive for sure.
+Darius: You know, it's a little much for a mixed.
+Jordan: It was clever, but that was nuts.
+Darius: It's a little much for, especially since you don't know anyone there.
+Jordan: You don't know her friends yet. You just met her, you don't know any of her friends.
+Darius: You show up and everyone's like Power Rangers and it's like, oh, you know.
+Jordan: Even if it wasn't, even if it was a costume party, you still look crazy as hell.
+Darius: Yeah, like it's like, well, there's like, it's like your girl's Princess Peach or something. Like something like, oh, I'm Yoshi. It's like, oh, I didn't know you said it was a costume party. Yeah, but like, why couldn't you?
+Jordan: You couldn't go Superman.
+Darius: Yeah, like was there, were they out of Batman? Why are we creative? But a bit much, even if you had the theme right.
+Jordan: Correct, absolutely. Yeah, that **** was crazy.
+Darius: Insane. And then her palm was there.
+Jordan: Yeah, when it fell into her drink and he's like, it's a cocktail.
+Darius: Yeah, oh my God. The most unrealistic thing in this movie, in a movie full of unrealistic things was him being able to recover from that. No, **** ***. Yeah, man. Don't try that at home unless you look like Zac Efron.
+Jordan: Like Zac Efron. That's the main message in this movie. It's like, don't do none of this **** he does in this movie unless you look like him. Pretty much.
+Darius: Pretty much, man. I was physically uncomfortable when he walked to that party. Because again, even if he had the theme right, that was a lot.
+Jordan: That was still crazy. And also like the door opened and you saw everybody right away. I had to turn around and went back home. home and change this into some other ****.
+Darius: I just would never.
+Jordan: Show my face again I just.
+Darius: Wouldn't wear that costume I would have more discretion.
+Jordan: Yeah well that that too that too yeah yeah for sure.
+Darius: You know if generally speaking going to the sex shop for your Halloween costume not a good idea in a party with a bunch of people you've never met before maybe rethink that one back to your great idea though yeah.
+Jordan: Yeah it was really clever for sure And I wonder, I think a funny scene would have been showing him, them showing him his friends, his outfit. Because at some point, one of them you had to believe would have been like, no, don't do that. That's stupid.
+Darius: You would think. That was really spectacularly stupid. What else you got for actually? What do you have for actually?
+Jordan: For actually, yeah. Okay. Yeah. So there's there. at the club and they get the call about Ellie's dad passing away and they're kind of telling him like, yo, well, one friend is telling him, go to the funeral. Don't be an *******. The other one's saying that that makes it look more serious than what it is. Which which friend would you have been in that situation?
+Darius: You gotta go to the funeral, man. You laid up with this woman every day.
+Jordan: Every day. Yeah.
+Darius: You got it. No, man, you can't just live with this woman day in and day out, got keys to the crib, talking all day, and then not be there when her dad dies. He **** *** wrong for that.
+Jordan: Yeah, man, you were getting on romantic ******* park dates and ****.
+Darius: No, he just, there's no, that's **** *** wrong. In fact, one of my notes here is that like, it actually ****** me off that he got the girl in the end, because that's just not, that's a fatal error. That's a fatal, yeah, that's just like, it's the most cliche dual. You showed up to a poem reading. Yeah. You just, No, the right ending to the movie was him being, sometimes you do just fumble the girl, it doesn't mean you live the rest of your life crying and staring out the window. Right. He fumbled the girl and the right ending would have been him actually fumbling the girl. Correct.
+Jordan: Yeah, that's true. And also for me, it was just the nonchalance about it afterwards where he just shows up to her crib and just like jokes around as if it was normal. Like you need to show up with like 1000 ******* roses and a horse and carriage and a billboard with her name on it and a ******* boom bop like boom box like the ******* 80s movie and **** to try to make up for what you did And even that's not enough.
+Darius: You just shouldn't show up. You should just hold that Well that also you just you fumbled and you need to move on with your life. You need to leave that girl alone It doesn't matter what you want. You ****** ** in the worst way.
+Jordan: So in like literally the worst way it Only would have been worse. It was if he had actually killed her father himself.
+Darius: Yeah you just met the dude clearly he died suddenly because he was in good health when you met him right and so yeah it you know throw on a black shirt like this and some slacks and sit in a boring funeral for a few hours and hold your girl's hand and like that's all you had to do she wasn't asking you yeah man you know make some grand gesture just show up.
+Jordan: Correct yeah and even the fact that like I wasn't invited it's like bro come on man she told you about it because she needed you there also just like knowing.
+Darius: You don't get formally invited to a funeral. You just, would you like me to go to the funeral with you? Yes, there you go. So.
+Jordan: Yeah, that was that was nuts. And I like that she was like upfront about it too. And she wasn't like a victim about the situation. She just straight up was like, you weren't there for me. And that's all that relationship really is. I mean, it's more than that, obviously, but at its base level, that's what it is. And I like that she held him accountable without being A victim in the situation.
+Darius: 100%. So we get to the, I don't know what kind of party, maybe it was Thanksgiving or whatever. And my son was ******* his girl in the bathroom. And they walk in on it because it just becomes a romcom and dude was like, don't hug me with no pants on. And I agree.
+Jordan: Don't hug me with no pants on.
+Darius: Don't hug me with no pants on. Don't even talk.
+Jordan: You're right. Respect.
+Darius: I'm reminded of the comic view bit where he was like, A naked man could break into my house and take my TV and he just, that's just his TV. He put on some pants so I could stop you. But like, do not hug me with no pants on. That was funny. Those 3 had great chemistry in this movie.
+Jordan: They really did. And I think Michael B. and Mike Teller are still close to this day, actually, which is pretty dope. Yeah, man, that scene was hilarious though, where he's like, yo, you're right, respect, respect.
+Darius: Yeah, it was funny. It was a good movie. I enjoyed that. was that. I enjoyed that scene. I enjoyed Michael B. Jordan finding out that, you know, when she was like, I don't love you anymore. That was good to hear.
+Jordan: Yeah.
+Darius: Then he bounced back and hit the girl back up and, you know, everybody didn't get a happy ending. So that was good. It's good that the movie didn't end with every cliche. So correct.
+Jordan: I will say I did also one of my favorite scenes in the movie is where Zach Efron's in the bar by himself after he fumbled the girl and he's like talking to that old dude and he's just like going on about like it's a perfect like monologue in terms of what your mind goes through when you're going through a breakup where he's like I'm just thinking about whatever what she's doing and who's in her house and who she's with and every other guy but me because like when you have a breakup and first hits and you're at your like most like vulnerable state you do really feel like every other guy in the world has a chance with her but you when that's actually not the case it's you but like it's just not you know just bad timing or whatever the **** but I thought that was a great, great statement he made there because it really does feel like that in the moment where you're like, down, the homeless dude on the street has a better chance to me when she wants to move you too. It's just not working right now. You know.
+Darius: That is true. And then you have all these grand plans before the breakup about how. your single life is going to be. It's never like you imagined it. You ain't going to have no hoes for a long time. You got to build that. You got to build up those muscles again. And it's always going to be easier for her to bounce back as far as dating because she's a woman. And you know, it takes once that hits you, it's rough. So what else you got for act 3?
+Jordan: Oh yeah, I like when rom-coms reference other rom-coms where Teller and Efron are talking to each other in the restaurant. And they're like, tell me what you love about her, man. And he's like saying all things he loves about her. And he's like, dude, you got to do a romantic gesture. Like you had me at hello and ****. Like, you know, I love that scene. I like when they show, I like that they didn't have them be like tough guys about like, oh yeah, like, oh, that's my ***** like, whatever, you know, and were honest and was like, okay, what do you love about this girl? Why do you want to be with her so badly? You know.
+Darius: Yeah, I mean, movies often. over index on just how rough and tumble male conversation is. Like when we don't just sit around calling women ******* and talking about our sexual exploits. Like, no, that's not, no, we really don't. I believe it or not.
+Jordan: Right, exactly. Yeah, no.
+Darius: You know, do we get mad at women? Sure, but we just like, there's not this like visceral anger you see in some of these movies.
+Jordan: Right, yeah.
+Darius: All right, man, what else you got for Act 3?
+Jordan: Do you think any of those couples ended up together?
+Darius: No, I think. Well, no, Miles Teller and his girl. Yes. Zac Efron made a fatal flaw, and I don't think that's that's that's short lived. And yeah, Michael B. Jordan is just bouncing back ******* whatever girls last, you know, responded to his phone calls. So no, right. You always circle back after a breakup to like.
+Jordan: The ones who hit you up when you were in a relationship.
+Darius: Yeah, you just, you need some layups. You need, you need to get super long. So you don't, you don't start with the high degree of difficulty. You start with, you know, you.
+Jordan: Start with your warm sales, then you make cold calls.
+Darius: Correct. That's a good way to put it. That's a great way to land the plane.
+Jordan: What do you rate it? I love this movie. It's one of my favorite rom-coms of all time. Three actors that I'm a big fan of. I'm going to give it 4 1/2 stars.
+Darius: Wow, that is a ringing endorsement. I enjoyed this movie very much. I will put it in my rom-com rotation and I'm going to give it a 3.5 star.
+Jordan: Nice.
+Darius: Very smooth, 90 minute, enjoyable watch. Three great actors having fun. I think it's important for actors to take a break from the super duper Oscar stuff and just have a little fun. And this was fresh off of Whiplash. Michael B. Jordan had right before Creed. Right before Creed. I mean, he had done the Chronicle. The Dude movie about the time Dude got shot.
+Jordan: Oh, Fruitvale.
+Darius: Yeah. And you know, The Wire and just like, you know, hey, let's just hang out for a couple for a couple weeks, film a rom com, you know. hang out in New York and it was a good time. It's light, light, nice little light, hungover Saturday afternoon in the summer with football's off movie to watch.
+Jordan: Yeah, for sure. All right. And it's a good cuffing season movie to all those who celebrate.
+Darius: It is not a romantic movie at all.
+Jordan: Oh, you know what? You're right.
+Darius: You're right. Not at all.
+Jordan: Get perpendicular.
+Darius: But I will say thank you everybody for listening. My name is Darius. That's Deez. I love your area on all socials.
+Jordan: And I'm Jordan. That's Jordan to be writing on all socials.
+Darius: Please rate, like, and subscribe. We're at Out the Trunk Pod on all socials. That is Out the Trunk Pod on all socials.
+Jordan: And for any of the move recommendations, feel free to reach out to us via e-mail. That's outthetrunkpod at gmail.com. Again, that's outthetrunkpod at gmail.com. That's a wrap. Thanks for coming to the movies with us. We'll be back next week. We're reviewing another film for you guys.
+Darius: All right, y'all have a good one.</t>
+  </si>
 </sst>
 </file>
 
@@ -8279,7 +8676,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8304,7 +8701,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8321,6 +8717,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8640,7 +9040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -9457,7 +9857,7 @@
       <c r="E41" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" t="s">
         <v>171</v>
       </c>
     </row>
@@ -9493,6 +9893,40 @@
       </c>
       <c r="E43" s="9" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="4">
+        <v>1989</v>
+      </c>
+      <c r="C44" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="D44" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="4">
+        <v>2014</v>
+      </c>
+      <c r="C45" s="7">
+        <v>4.5</v>
+      </c>
+      <c r="D45" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -9507,7 +9941,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -9855,6 +10289,22 @@
         <v>169</v>
       </c>
     </row>
+    <row r="44" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
